--- a/example1-metabolomics/results-A/report/normalized_data.xlsx
+++ b/example1-metabolomics/results-A/report/normalized_data.xlsx
@@ -608,73 +608,73 @@
         <v>24</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.652379038394408</v>
+        <v>0.968556057526809</v>
       </c>
       <c r="C2" t="n">
-        <v>3.78429074754196</v>
+        <v>1.18239859585372</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.5634247130715</v>
+        <v>0.924644671508796</v>
       </c>
       <c r="E2" t="n">
-        <v>-3.34759751753318</v>
+        <v>0.838649531070503</v>
       </c>
       <c r="F2" t="n">
-        <v>3.25377581273048</v>
+        <v>1.15682836733682</v>
       </c>
       <c r="G2" t="n">
-        <v>1.61437954661777</v>
+        <v>1.07781129467108</v>
       </c>
       <c r="H2" t="n">
-        <v>0.483022149439317</v>
+        <v>1.02328112920002</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.989670127159433</v>
+        <v>0.952299003011462</v>
       </c>
       <c r="J2" t="n">
-        <v>4.60391567616835</v>
+        <v>1.22190360381466</v>
       </c>
       <c r="K2" t="n">
-        <v>-3.97324991615303</v>
+        <v>0.808493782843469</v>
       </c>
       <c r="L2" t="n">
-        <v>-3.99796967572093</v>
+        <v>0.807302317986294</v>
       </c>
       <c r="M2" t="n">
-        <v>3.00538190264335</v>
+        <v>1.14485605774408</v>
       </c>
       <c r="N2" t="n">
-        <v>0.318576852604286</v>
+        <v>1.01535504919231</v>
       </c>
       <c r="O2" t="n">
-        <v>6.76964811437209</v>
+        <v>1.32628949329205</v>
       </c>
       <c r="P2" t="n">
-        <v>5.37532861746097</v>
+        <v>1.25908484772584</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.793433808483783</v>
+        <v>1.03824262516412</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.187314865758203</v>
+        <v>0.990971632261867</v>
       </c>
       <c r="S2" t="n">
-        <v>5.53002448751979</v>
+        <v>1.26654101623018</v>
       </c>
       <c r="T2" t="n">
-        <v>0.802551302188487</v>
+        <v>1.03868207819783</v>
       </c>
       <c r="U2" t="n">
-        <v>0.664602952538775</v>
+        <v>1.03203312150951</v>
       </c>
       <c r="V2" t="n">
-        <v>5.53991829684804</v>
+        <v>1.26701788681162</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.575144153254828</v>
+        <v>0.972278692900302</v>
       </c>
       <c r="X2" t="n">
-        <v>2.15882849820424</v>
+        <v>1.10405312726492</v>
       </c>
     </row>
     <row r="3">
@@ -682,73 +682,73 @@
         <v>25</v>
       </c>
       <c r="B3" t="n">
-        <v>-1.28821519068625</v>
+        <v>0.938319769072406</v>
       </c>
       <c r="C3" t="n">
-        <v>3.3051267633431</v>
+        <v>1.1582507204401</v>
       </c>
       <c r="D3" t="n">
-        <v>-1.88237210202196</v>
+        <v>0.909871311265531</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.97145254981312</v>
+        <v>0.857725727201505</v>
       </c>
       <c r="F3" t="n">
-        <v>3.15703543366421</v>
+        <v>1.15116005152157</v>
       </c>
       <c r="G3" t="n">
-        <v>1.37632663204536</v>
+        <v>1.0658990400906</v>
       </c>
       <c r="H3" t="n">
-        <v>0.119161403072439</v>
+        <v>1.00570549308245</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.16549198061169</v>
+        <v>0.944195802822282</v>
       </c>
       <c r="J3" t="n">
-        <v>4.40045525281779</v>
+        <v>1.21069546310485</v>
       </c>
       <c r="K3" t="n">
-        <v>-5.42607856312055</v>
+        <v>0.74019730459299</v>
       </c>
       <c r="L3" t="n">
-        <v>-4.50644380710046</v>
+        <v>0.78422976479876</v>
       </c>
       <c r="M3" t="n">
-        <v>2.57086715061429</v>
+        <v>1.12309409226077</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0907798185991521</v>
+        <v>0.995653427924741</v>
       </c>
       <c r="O3" t="n">
-        <v>6.49154276500563</v>
+        <v>1.31081752467816</v>
       </c>
       <c r="P3" t="n">
-        <v>5.18155133877589</v>
+        <v>1.2480946393503</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.0819407091189893</v>
+        <v>0.99607664783231</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.824618887715601</v>
+        <v>0.960516935532751</v>
       </c>
       <c r="S3" t="n">
-        <v>5.25853633707465</v>
+        <v>1.25178071020815</v>
       </c>
       <c r="T3" t="n">
-        <v>0.321919455014598</v>
+        <v>1.01541362535463</v>
       </c>
       <c r="U3" t="n">
-        <v>0.456786458320108</v>
+        <v>1.02187110852091</v>
       </c>
       <c r="V3" t="n">
-        <v>5.33994108805021</v>
+        <v>1.25567840049707</v>
       </c>
       <c r="W3" t="n">
-        <v>-1.37396915775834</v>
+        <v>0.934213836670579</v>
       </c>
       <c r="X3" t="n">
-        <v>1.46633197829146</v>
+        <v>1.07020853013645</v>
       </c>
     </row>
     <row r="4">
@@ -756,73 +756,73 @@
         <v>26</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.965102530560669</v>
+        <v>0.953773026167992</v>
       </c>
       <c r="C4" t="n">
-        <v>3.54515870651582</v>
+        <v>1.1698078220365</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.02536397693515</v>
+        <v>0.950886592637439</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.79926250110888</v>
+        <v>0.865919495297036</v>
       </c>
       <c r="F4" t="n">
-        <v>2.41033780806573</v>
+        <v>1.11545159115377</v>
       </c>
       <c r="G4" t="n">
-        <v>1.29715118985454</v>
+        <v>1.06213161007331</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.21531516022666</v>
+        <v>0.989686724506203</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.11895170958685</v>
+        <v>0.946403879628932</v>
       </c>
       <c r="J4" t="n">
-        <v>4.39498651858633</v>
+        <v>1.210513308538</v>
       </c>
       <c r="K4" t="n">
-        <v>-4.61521581971912</v>
+        <v>0.778938035937712</v>
       </c>
       <c r="L4" t="n">
-        <v>-4.19850442868396</v>
+        <v>0.798897890936425</v>
       </c>
       <c r="M4" t="n">
-        <v>2.73832437064371</v>
+        <v>1.13116165901229</v>
       </c>
       <c r="N4" t="n">
-        <v>0.382795343955929</v>
+        <v>1.01833532685671</v>
       </c>
       <c r="O4" t="n">
-        <v>6.47065617186956</v>
+        <v>1.30993479351791</v>
       </c>
       <c r="P4" t="n">
-        <v>5.26738303388735</v>
+        <v>1.25229980231139</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.305402784497943</v>
+        <v>1.01462833852379</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.354339892134212</v>
+        <v>0.983027646905237</v>
       </c>
       <c r="S4" t="n">
-        <v>5.14064213506886</v>
+        <v>1.24622910202038</v>
       </c>
       <c r="T4" t="n">
-        <v>0.683002980165478</v>
+        <v>1.03271482551491</v>
       </c>
       <c r="U4" t="n">
-        <v>1.13947860563912</v>
+        <v>1.0545793281201</v>
       </c>
       <c r="V4" t="n">
-        <v>5.3696589331087</v>
+        <v>1.2571986655588</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.702663532789551</v>
+        <v>0.966343463295968</v>
       </c>
       <c r="X4" t="n">
-        <v>1.60801100590035</v>
+        <v>1.07702133228078</v>
       </c>
     </row>
     <row r="5">
@@ -830,73 +830,73 @@
         <v>27</v>
       </c>
       <c r="B5" t="n">
-        <v>-1.00927357411425</v>
+        <v>0.951099859358375</v>
       </c>
       <c r="C5" t="n">
-        <v>3.36552162972092</v>
+        <v>1.16306231060317</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.812223071785667</v>
+        <v>0.960647119412049</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.43733428804534</v>
+        <v>0.881909134913522</v>
       </c>
       <c r="F5" t="n">
-        <v>3.09621569988949</v>
+        <v>1.1500142152382</v>
       </c>
       <c r="G5" t="n">
-        <v>1.51059680674799</v>
+        <v>1.07318966650603</v>
       </c>
       <c r="H5" t="n">
-        <v>0.420990282149718</v>
+        <v>1.02039732787411</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.904464871325361</v>
+        <v>0.956177927820972</v>
       </c>
       <c r="J5" t="n">
-        <v>4.39757571883329</v>
+        <v>1.21306618606543</v>
       </c>
       <c r="K5" t="n">
-        <v>-4.70749802589754</v>
+        <v>0.771917821450355</v>
       </c>
       <c r="L5" t="n">
-        <v>-4.00587656633667</v>
+        <v>0.805911962315303</v>
       </c>
       <c r="M5" t="n">
-        <v>2.67475047077174</v>
+        <v>1.1295938757901</v>
       </c>
       <c r="N5" t="n">
-        <v>0.222027477082963</v>
+        <v>1.01075741516882</v>
       </c>
       <c r="O5" t="n">
-        <v>6.84312647206405</v>
+        <v>1.33155514569579</v>
       </c>
       <c r="P5" t="n">
-        <v>5.36983671978147</v>
+        <v>1.26017303687984</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.290578133154177</v>
+        <v>1.0140787512356</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.206537504058318</v>
+        <v>0.989993086854488</v>
       </c>
       <c r="S5" t="n">
-        <v>5.36682822947733</v>
+        <v>1.26002727303269</v>
       </c>
       <c r="T5" t="n">
-        <v>0.993312643256831</v>
+        <v>1.04812682032123</v>
       </c>
       <c r="U5" t="n">
-        <v>1.10829382701783</v>
+        <v>1.05369775391274</v>
       </c>
       <c r="V5" t="n">
-        <v>5.57968231512914</v>
+        <v>1.2703402297884</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.894559525911521</v>
+        <v>0.956657850010816</v>
       </c>
       <c r="X5" t="n">
-        <v>1.96234813898585</v>
+        <v>1.09507739273611</v>
       </c>
     </row>
     <row r="6">
@@ -904,73 +904,73 @@
         <v>28</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.828852558311626</v>
+        <v>0.960227216578863</v>
       </c>
       <c r="C6" t="n">
-        <v>3.43179178434718</v>
+        <v>1.16467574361273</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.18956062718153</v>
+        <v>0.9429185122049</v>
       </c>
       <c r="E6" t="n">
-        <v>-3.44180855027845</v>
+        <v>0.834843598328167</v>
       </c>
       <c r="F6" t="n">
-        <v>2.53744459557374</v>
+        <v>1.12176017716404</v>
       </c>
       <c r="G6" t="n">
-        <v>1.4481045821532</v>
+        <v>1.06948781099796</v>
       </c>
       <c r="H6" t="n">
-        <v>0.503526748978642</v>
+        <v>1.02416190929623</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.29317999384142</v>
+        <v>0.937946300214876</v>
       </c>
       <c r="J6" t="n">
-        <v>4.52538795631673</v>
+        <v>1.21715234305344</v>
       </c>
       <c r="K6" t="n">
-        <v>-3.9545557598583</v>
+        <v>0.810239241965978</v>
       </c>
       <c r="L6" t="n">
-        <v>-4.37425318359094</v>
+        <v>0.790099912516926</v>
       </c>
       <c r="M6" t="n">
-        <v>2.61034619814646</v>
+        <v>1.12525838637037</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0445179808227575</v>
+        <v>1.00213621106897</v>
       </c>
       <c r="O6" t="n">
-        <v>6.46128171549007</v>
+        <v>1.31004689038617</v>
       </c>
       <c r="P6" t="n">
-        <v>5.31605129117021</v>
+        <v>1.2550926030681</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0207599659354373</v>
+        <v>1.00099617431436</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.650783309785377</v>
+        <v>0.968771932505211</v>
       </c>
       <c r="S6" t="n">
-        <v>5.25005213099349</v>
+        <v>1.25192561000358</v>
       </c>
       <c r="T6" t="n">
-        <v>0.65896338967694</v>
+        <v>1.0316205915241</v>
       </c>
       <c r="U6" t="n">
-        <v>0.838294209137673</v>
+        <v>1.04022584437833</v>
       </c>
       <c r="V6" t="n">
-        <v>5.3935039860791</v>
+        <v>1.25880919805125</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.891647125087724</v>
+        <v>0.957213997063082</v>
       </c>
       <c r="X6" t="n">
-        <v>1.36346624129759</v>
+        <v>1.06542641025036</v>
       </c>
     </row>
     <row r="7">
@@ -978,73 +978,73 @@
         <v>29</v>
       </c>
       <c r="B7" t="n">
-        <v>-1.86571909107103</v>
+        <v>0.910976573014892</v>
       </c>
       <c r="C7" t="n">
-        <v>2.6136577032593</v>
+        <v>1.12471157465436</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.95303396460036</v>
+        <v>0.90681031384675</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.27315829981986</v>
+        <v>0.843820127955362</v>
       </c>
       <c r="F7" t="n">
-        <v>2.2644407686513</v>
+        <v>1.10804856872339</v>
       </c>
       <c r="G7" t="n">
-        <v>0.438952563335833</v>
+        <v>1.02094477226452</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.21119354402741</v>
+        <v>0.942207484209394</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.52381586524469</v>
+        <v>0.927290602820339</v>
       </c>
       <c r="J7" t="n">
-        <v>4.26264071091359</v>
+        <v>1.20339336500755</v>
       </c>
       <c r="K7" t="n">
-        <v>-4.73241185784208</v>
+        <v>0.774191343430905</v>
       </c>
       <c r="L7" t="n">
-        <v>-5.56071353759707</v>
+        <v>0.73466864440177</v>
       </c>
       <c r="M7" t="n">
-        <v>2.50957514847689</v>
+        <v>1.1197452398184</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0820374278228387</v>
+        <v>1.00391444403436</v>
       </c>
       <c r="O7" t="n">
-        <v>6.34012491226609</v>
+        <v>1.30252123693475</v>
       </c>
       <c r="P7" t="n">
-        <v>5.09984990879377</v>
+        <v>1.24334108932223</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.349305808195227</v>
+        <v>0.983332753435304</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.943909520464983</v>
+        <v>0.954961033159914</v>
       </c>
       <c r="S7" t="n">
-        <v>5.13839802503718</v>
+        <v>1.24518042592346</v>
       </c>
       <c r="T7" t="n">
-        <v>0.225541737644699</v>
+        <v>1.01076180144664</v>
       </c>
       <c r="U7" t="n">
-        <v>0.459656884668265</v>
+        <v>1.02193268606528</v>
       </c>
       <c r="V7" t="n">
-        <v>5.29938645752652</v>
+        <v>1.25286204425161</v>
       </c>
       <c r="W7" t="n">
-        <v>-1.04153574461862</v>
+        <v>0.950302764356552</v>
       </c>
       <c r="X7" t="n">
-        <v>1.72677042697241</v>
+        <v>1.0823934437726</v>
       </c>
     </row>
     <row r="8">
@@ -1052,73 +1052,73 @@
         <v>30</v>
       </c>
       <c r="B8" t="n">
-        <v>-2.42878761543349</v>
+        <v>0.882821361427627</v>
       </c>
       <c r="C8" t="n">
-        <v>2.53463854448421</v>
+        <v>1.12228549422289</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.18296278305121</v>
+        <v>0.894681360631673</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.97224284368467</v>
+        <v>0.85660196564067</v>
       </c>
       <c r="F8" t="n">
-        <v>3.04269939545228</v>
+        <v>1.14679726233718</v>
       </c>
       <c r="G8" t="n">
-        <v>0.683293354378846</v>
+        <v>1.03296598866977</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.362127402540913</v>
+        <v>0.982528898060146</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.960385449918447</v>
+        <v>0.953665500099286</v>
       </c>
       <c r="J8" t="n">
-        <v>4.46588126046689</v>
+        <v>1.2154597144691</v>
       </c>
       <c r="K8" t="n">
-        <v>-4.52022641048376</v>
+        <v>0.781918363938614</v>
       </c>
       <c r="L8" t="n">
-        <v>-5.18991224376773</v>
+        <v>0.749608880097057</v>
       </c>
       <c r="M8" t="n">
-        <v>2.38800682323081</v>
+        <v>1.11521113936419</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.265563365122318</v>
+        <v>0.987187700817481</v>
       </c>
       <c r="O8" t="n">
-        <v>6.40668957573187</v>
+        <v>1.30909543406334</v>
       </c>
       <c r="P8" t="n">
-        <v>5.16990420042795</v>
+        <v>1.24942581718806</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.10440481253626</v>
+        <v>0.946717180397563</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.596742846479183</v>
+        <v>0.971209704016976</v>
       </c>
       <c r="S8" t="n">
-        <v>5.0988862426176</v>
+        <v>1.24599950376422</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0141498622441042</v>
+        <v>1.00068267047444</v>
       </c>
       <c r="U8" t="n">
-        <v>0.374711065034985</v>
+        <v>1.01807820995948</v>
       </c>
       <c r="V8" t="n">
-        <v>5.45013438324095</v>
+        <v>1.26294572773942</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.857971229604971</v>
+        <v>0.958606549218001</v>
       </c>
       <c r="X8" t="n">
-        <v>1.27106747506781</v>
+        <v>1.06132358190384</v>
       </c>
     </row>
     <row r="9">
@@ -1126,73 +1126,73 @@
         <v>31</v>
       </c>
       <c r="B9" t="n">
-        <v>-1.85625845559378</v>
+        <v>0.909167271411014</v>
       </c>
       <c r="C9" t="n">
-        <v>3.19938213730098</v>
+        <v>1.15655611343031</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.57874777043335</v>
+        <v>0.922746766588402</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.56600554058697</v>
+        <v>0.874437051519632</v>
       </c>
       <c r="F9" t="n">
-        <v>3.34764865883978</v>
+        <v>1.16381127376059</v>
       </c>
       <c r="G9" t="n">
-        <v>0.775477756035489</v>
+        <v>1.03794663417074</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.310320553579398</v>
+        <v>0.984815011867599</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.938016829452417</v>
+        <v>0.95409980338417</v>
       </c>
       <c r="J9" t="n">
-        <v>4.49296339602638</v>
+        <v>1.21985522731583</v>
       </c>
       <c r="K9" t="n">
-        <v>-4.59909565635069</v>
+        <v>0.774951377999539</v>
       </c>
       <c r="L9" t="n">
-        <v>-5.21547948087964</v>
+        <v>0.744789724340071</v>
       </c>
       <c r="M9" t="n">
-        <v>3.142804339616</v>
+        <v>1.15378757884085</v>
       </c>
       <c r="N9" t="n">
-        <v>0.512920713317605</v>
+        <v>1.02509886907184</v>
       </c>
       <c r="O9" t="n">
-        <v>6.88449164045562</v>
+        <v>1.33688043750923</v>
       </c>
       <c r="P9" t="n">
-        <v>5.27532391884706</v>
+        <v>1.25813865752134</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.138068376879038</v>
+        <v>0.993243867864422</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.1797346127961</v>
+        <v>0.99120500420997</v>
       </c>
       <c r="S9" t="n">
-        <v>5.50305090597656</v>
+        <v>1.2692820753746</v>
       </c>
       <c r="T9" t="n">
-        <v>1.08826682840284</v>
+        <v>1.05325241490959</v>
       </c>
       <c r="U9" t="n">
-        <v>0.587046193357446</v>
+        <v>1.02872606850072</v>
       </c>
       <c r="V9" t="n">
-        <v>5.64517791365595</v>
+        <v>1.27623680943914</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.119179452832354</v>
+        <v>0.994168163996838</v>
       </c>
       <c r="X9" t="n">
-        <v>2.29570781496161</v>
+        <v>1.1123364067367</v>
       </c>
     </row>
     <row r="10">
@@ -1200,73 +1200,73 @@
         <v>32</v>
       </c>
       <c r="B10" t="n">
-        <v>-1.9775094277565</v>
+        <v>0.904943734951395</v>
       </c>
       <c r="C10" t="n">
-        <v>2.77097993324548</v>
+        <v>1.13319734373038</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.75912803561764</v>
+        <v>0.915441039895415</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.02775793199524</v>
+        <v>0.854459677184308</v>
       </c>
       <c r="F10" t="n">
-        <v>2.1251705962991</v>
+        <v>1.1021541422963</v>
       </c>
       <c r="G10" t="n">
-        <v>0.511661666906716</v>
+        <v>1.02459490020226</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.13470676331089</v>
+        <v>0.945456145325136</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.43607384392018</v>
+        <v>0.930969827996261</v>
       </c>
       <c r="J10" t="n">
-        <v>3.97563784231026</v>
+        <v>1.19110365754597</v>
       </c>
       <c r="K10" t="n">
-        <v>-5.4578504213643</v>
+        <v>0.737648342421592</v>
       </c>
       <c r="L10" t="n">
-        <v>-5.43141663610391</v>
+        <v>0.738918979548617</v>
       </c>
       <c r="M10" t="n">
-        <v>2.5163724660794</v>
+        <v>1.12095869923008</v>
       </c>
       <c r="N10" t="n">
-        <v>0.303583776218906</v>
+        <v>1.01459287095762</v>
       </c>
       <c r="O10" t="n">
-        <v>6.46676185568231</v>
+        <v>1.31084869701852</v>
       </c>
       <c r="P10" t="n">
-        <v>4.73470064572732</v>
+        <v>1.22759080345658</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.185390851668473</v>
+        <v>0.991088506741645</v>
       </c>
       <c r="R10" t="n">
-        <v>-1.3469203238244</v>
+        <v>0.935255319896978</v>
       </c>
       <c r="S10" t="n">
-        <v>4.89055650403112</v>
+        <v>1.23508258861237</v>
       </c>
       <c r="T10" t="n">
-        <v>0.336884714894185</v>
+        <v>1.01619360307482</v>
       </c>
       <c r="U10" t="n">
-        <v>0.394344449972807</v>
+        <v>1.01895561661093</v>
       </c>
       <c r="V10" t="n">
-        <v>5.64257218384729</v>
+        <v>1.27123098860377</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.510059943917846</v>
+        <v>0.975482092505249</v>
       </c>
       <c r="X10" t="n">
-        <v>2.09620703201106</v>
+        <v>1.10076190203434</v>
       </c>
     </row>
     <row r="11">
@@ -1274,73 +1274,73 @@
         <v>33</v>
       </c>
       <c r="B11" t="n">
-        <v>-2.26079061761116</v>
+        <v>0.891296886001386</v>
       </c>
       <c r="C11" t="n">
-        <v>2.17622269489268</v>
+        <v>1.10463692738572</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.71494845697762</v>
+        <v>0.869460113059458</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.58068339221566</v>
+        <v>0.827833930331754</v>
       </c>
       <c r="F11" t="n">
-        <v>2.98912437326928</v>
+        <v>1.14372278660943</v>
       </c>
       <c r="G11" t="n">
-        <v>0.346971607112837</v>
+        <v>1.01668305497575</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.190612259455498</v>
+        <v>0.990834999929795</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.37272225249277</v>
+        <v>0.933996902526592</v>
       </c>
       <c r="J11" t="n">
-        <v>4.14246058174786</v>
+        <v>1.19917738570956</v>
       </c>
       <c r="K11" t="n">
-        <v>-4.0642214958247</v>
+        <v>0.804584498389743</v>
       </c>
       <c r="L11" t="n">
-        <v>-5.26114339513119</v>
+        <v>0.747034216353794</v>
       </c>
       <c r="M11" t="n">
-        <v>2.19980062758041</v>
+        <v>1.10577059924584</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.568633985372511</v>
+        <v>0.972658996169779</v>
       </c>
       <c r="O11" t="n">
-        <v>6.25858390533067</v>
+        <v>1.30092462098498</v>
       </c>
       <c r="P11" t="n">
-        <v>4.89234918740154</v>
+        <v>1.23523345651579</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.49138367139256</v>
+        <v>0.92829143575518</v>
       </c>
       <c r="R11" t="n">
-        <v>-1.65933913209194</v>
+        <v>0.920215817673225</v>
       </c>
       <c r="S11" t="n">
-        <v>4.91754080757562</v>
+        <v>1.23644471754025</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.788773201166506</v>
+        <v>0.962074283864442</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.00632927931549819</v>
+        <v>0.999695676209198</v>
       </c>
       <c r="V11" t="n">
-        <v>5.12990987740256</v>
+        <v>1.24665582644496</v>
       </c>
       <c r="W11" t="n">
-        <v>-1.39552082692719</v>
+        <v>0.932900703694004</v>
       </c>
       <c r="X11" t="n">
-        <v>1.14189610920197</v>
+        <v>1.05490453736238</v>
       </c>
     </row>
     <row r="12">
@@ -1348,73 +1348,73 @@
         <v>34</v>
       </c>
       <c r="B12" t="n">
-        <v>-2.43581736785159</v>
+        <v>0.883158049423952</v>
       </c>
       <c r="C12" t="n">
-        <v>2.35937986681958</v>
+        <v>1.11317537571883</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.52577077068797</v>
+        <v>0.878843140109701</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.22873484781906</v>
+        <v>0.845123167897937</v>
       </c>
       <c r="F12" t="n">
-        <v>1.98781996460251</v>
+        <v>1.09535228918374</v>
       </c>
       <c r="G12" t="n">
-        <v>0.392650233598875</v>
+        <v>1.01883475329199</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.2657507514499</v>
+        <v>0.939284123393476</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.22779947681554</v>
+        <v>0.941104580466182</v>
       </c>
       <c r="J12" t="n">
-        <v>4.13245715269228</v>
+        <v>1.1982268296323</v>
       </c>
       <c r="K12" t="n">
-        <v>-4.59642615754403</v>
+        <v>0.779517378841952</v>
       </c>
       <c r="L12" t="n">
-        <v>-5.90813092729513</v>
+        <v>0.716597167376015</v>
       </c>
       <c r="M12" t="n">
-        <v>2.29401730374574</v>
+        <v>1.1100400465004</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.191738813824106</v>
+        <v>0.990802620383602</v>
       </c>
       <c r="O12" t="n">
-        <v>6.17802339270271</v>
+        <v>1.29634910787442</v>
       </c>
       <c r="P12" t="n">
-        <v>4.84487366789247</v>
+        <v>1.23240021896649</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.14282956276281</v>
+        <v>0.94518044043386</v>
       </c>
       <c r="R12" t="n">
-        <v>-1.00911113344514</v>
+        <v>0.951594682452022</v>
       </c>
       <c r="S12" t="n">
-        <v>4.85301836505902</v>
+        <v>1.23279090601731</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0699742730277113</v>
+        <v>0.996643455023104</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0526685576603285</v>
+        <v>1.00252641971121</v>
       </c>
       <c r="V12" t="n">
-        <v>5.03277348649106</v>
+        <v>1.24141344861486</v>
       </c>
       <c r="W12" t="n">
-        <v>-1.49660557370503</v>
+        <v>0.928210416436551</v>
       </c>
       <c r="X12" t="n">
-        <v>1.1792123569233</v>
+        <v>1.05656477934051</v>
       </c>
     </row>
     <row r="13">
@@ -1422,73 +1422,73 @@
         <v>35</v>
       </c>
       <c r="B13" t="n">
-        <v>-2.27086798821491</v>
+        <v>0.889594870681349</v>
       </c>
       <c r="C13" t="n">
-        <v>2.33979526360348</v>
+        <v>1.11375623770203</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.57035663141944</v>
+        <v>0.875034322664441</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.4463502157303</v>
+        <v>0.832445239785091</v>
       </c>
       <c r="F13" t="n">
-        <v>2.28711730595267</v>
+        <v>1.1111951391455</v>
       </c>
       <c r="G13" t="n">
-        <v>0.346328850597221</v>
+        <v>1.0168378266528</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.27066427511655</v>
+        <v>0.938222805401775</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.60291938595173</v>
+        <v>0.922069216259248</v>
       </c>
       <c r="J13" t="n">
-        <v>4.20199405192554</v>
+        <v>1.20429267535878</v>
       </c>
       <c r="K13" t="n">
-        <v>-3.78714106383276</v>
+        <v>0.815876659906988</v>
       </c>
       <c r="L13" t="n">
-        <v>-5.46533593114906</v>
+        <v>0.734286130510518</v>
       </c>
       <c r="M13" t="n">
-        <v>2.05503715635253</v>
+        <v>1.09991185933273</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.100375944794932</v>
+        <v>0.995119919245382</v>
       </c>
       <c r="O13" t="n">
-        <v>6.51594032277745</v>
+        <v>1.31679218594048</v>
       </c>
       <c r="P13" t="n">
-        <v>4.90568569663239</v>
+        <v>1.23850477726761</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.933386716492059</v>
+        <v>0.954620576064563</v>
       </c>
       <c r="R13" t="n">
-        <v>-1.05567159918955</v>
+        <v>0.948675325896787</v>
       </c>
       <c r="S13" t="n">
-        <v>5.07231000614947</v>
+        <v>1.24660572304488</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.248956541810443</v>
+        <v>0.987896223234486</v>
       </c>
       <c r="U13" t="n">
-        <v>0.350020387092893</v>
+        <v>1.01701730188708</v>
       </c>
       <c r="V13" t="n">
-        <v>5.64962736473916</v>
+        <v>1.27467375604538</v>
       </c>
       <c r="W13" t="n">
-        <v>-1.01605869464985</v>
+        <v>0.950601227301488</v>
       </c>
       <c r="X13" t="n">
-        <v>1.76797581752325</v>
+        <v>1.0859555023801</v>
       </c>
     </row>
     <row r="14">
@@ -1496,73 +1496,73 @@
         <v>36</v>
       </c>
       <c r="B14" t="n">
-        <v>-1.39454921015205</v>
+        <v>0.932389862164701</v>
       </c>
       <c r="C14" t="n">
-        <v>2.6196458062177</v>
+        <v>1.12700492227071</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.46078303436774</v>
+        <v>0.929178732753145</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.39113201961406</v>
+        <v>0.835592102742072</v>
       </c>
       <c r="F14" t="n">
-        <v>2.11050005880132</v>
+        <v>1.1023206630775</v>
       </c>
       <c r="G14" t="n">
-        <v>0.69415973667761</v>
+        <v>1.03365405475463</v>
       </c>
       <c r="H14" t="n">
-        <v>0.094897325877794</v>
+        <v>1.00460078513981</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.64050485360956</v>
+        <v>0.920465510672136</v>
       </c>
       <c r="J14" t="n">
-        <v>4.40904649215887</v>
+        <v>1.2137581369571</v>
       </c>
       <c r="K14" t="n">
-        <v>-4.63434611104076</v>
+        <v>0.775318951053878</v>
       </c>
       <c r="L14" t="n">
-        <v>-5.13332185075717</v>
+        <v>0.751127751278993</v>
       </c>
       <c r="M14" t="n">
-        <v>2.80502952655187</v>
+        <v>1.13599264302877</v>
       </c>
       <c r="N14" t="n">
-        <v>0.615444898079969</v>
+        <v>1.02983782435665</v>
       </c>
       <c r="O14" t="n">
-        <v>6.69604348775502</v>
+        <v>1.32463567428281</v>
       </c>
       <c r="P14" t="n">
-        <v>5.17766502654013</v>
+        <v>1.25102208194662</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.0842806380299407</v>
+        <v>0.995913930098293</v>
       </c>
       <c r="R14" t="n">
-        <v>-1.30551472268061</v>
+        <v>0.936706406841803</v>
       </c>
       <c r="S14" t="n">
-        <v>5.16607887023238</v>
+        <v>1.25046036521462</v>
       </c>
       <c r="T14" t="n">
-        <v>0.81025310153017</v>
+        <v>1.03928246022237</v>
       </c>
       <c r="U14" t="n">
-        <v>0.785958351637724</v>
+        <v>1.03810460907381</v>
       </c>
       <c r="V14" t="n">
-        <v>5.60272691670507</v>
+        <v>1.27162981150781</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.638466591456933</v>
+        <v>0.969046044458388</v>
       </c>
       <c r="X14" t="n">
-        <v>2.28611865559795</v>
+        <v>1.11083495389594</v>
       </c>
     </row>
     <row r="15">
@@ -1570,73 +1570,73 @@
         <v>37</v>
       </c>
       <c r="B15" t="n">
-        <v>-2.12002538249201</v>
+        <v>0.898435584719669</v>
       </c>
       <c r="C15" t="n">
-        <v>2.8919853076452</v>
+        <v>1.13854683023891</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.96015265336239</v>
+        <v>0.906094634647757</v>
       </c>
       <c r="E15" t="n">
-        <v>-3.41848760797527</v>
+        <v>0.836229934832691</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9669450810021</v>
+        <v>1.09423077133429</v>
       </c>
       <c r="G15" t="n">
-        <v>0.717259628969196</v>
+        <v>1.03436187859921</v>
       </c>
       <c r="H15" t="n">
-        <v>0.309091976220276</v>
+        <v>1.01480772168669</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.43259610767206</v>
+        <v>0.931368375487297</v>
       </c>
       <c r="J15" t="n">
-        <v>4.02997764248423</v>
+        <v>1.19306482187991</v>
       </c>
       <c r="K15" t="n">
-        <v>-5.02173384374818</v>
+        <v>0.759422945712937</v>
       </c>
       <c r="L15" t="n">
-        <v>-5.07766282563474</v>
+        <v>0.756743546499397</v>
       </c>
       <c r="M15" t="n">
-        <v>1.91078923954683</v>
+        <v>1.09154050392095</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.57605285469321</v>
+        <v>0.972402938266376</v>
       </c>
       <c r="O15" t="n">
-        <v>6.10543320536469</v>
+        <v>1.29249402325886</v>
       </c>
       <c r="P15" t="n">
-        <v>4.71864740996595</v>
+        <v>1.22605704113972</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.662582933738947</v>
+        <v>0.968257527105256</v>
       </c>
       <c r="R15" t="n">
-        <v>-1.33774556304372</v>
+        <v>0.935912396603155</v>
       </c>
       <c r="S15" t="n">
-        <v>4.75407597426426</v>
+        <v>1.22775432337364</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.000304133867552792</v>
+        <v>0.999985429807266</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.000257570946198993</v>
+        <v>0.99998766050503</v>
       </c>
       <c r="V15" t="n">
-        <v>4.99308272562822</v>
+        <v>1.23920446031578</v>
       </c>
       <c r="W15" t="n">
-        <v>-1.45206080565347</v>
+        <v>0.930435876902414</v>
       </c>
       <c r="X15" t="n">
-        <v>0.911410744623712</v>
+        <v>1.04366310899972</v>
       </c>
     </row>
     <row r="16">
@@ -1644,73 +1644,73 @@
         <v>38</v>
       </c>
       <c r="B16" t="n">
-        <v>-1.13036473061501</v>
+        <v>0.946127317224263</v>
       </c>
       <c r="C16" t="n">
-        <v>2.9249882303037</v>
+        <v>1.13940364449285</v>
       </c>
       <c r="D16" t="n">
-        <v>-2.04758698681307</v>
+        <v>0.90241291044503</v>
       </c>
       <c r="E16" t="n">
-        <v>-3.65508899540194</v>
+        <v>0.825800076176086</v>
       </c>
       <c r="F16" t="n">
-        <v>2.41361699544346</v>
+        <v>1.11503191776596</v>
       </c>
       <c r="G16" t="n">
-        <v>0.881558010088659</v>
+        <v>1.04201466459421</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.49373453219275</v>
+        <v>0.976468830716458</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.42758024947674</v>
+        <v>0.931962157139206</v>
       </c>
       <c r="J16" t="n">
-        <v>3.86921481277962</v>
+        <v>1.18440506551071</v>
       </c>
       <c r="K16" t="n">
-        <v>-5.15913150073953</v>
+        <v>0.754118076042208</v>
       </c>
       <c r="L16" t="n">
-        <v>-4.71847770167342</v>
+        <v>0.775119441077806</v>
       </c>
       <c r="M16" t="n">
-        <v>1.64729230547642</v>
+        <v>1.07850922220791</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.489629183783938</v>
+        <v>0.976664489804646</v>
       </c>
       <c r="O16" t="n">
-        <v>6.13469824732419</v>
+        <v>1.29237700332631</v>
       </c>
       <c r="P16" t="n">
-        <v>4.653922975181</v>
+        <v>1.22180390922868</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.705612444892995</v>
+        <v>0.966370823171694</v>
       </c>
       <c r="R16" t="n">
-        <v>-1.72749539414708</v>
+        <v>0.917668334082932</v>
       </c>
       <c r="S16" t="n">
-        <v>4.64390611366128</v>
+        <v>1.22132651004199</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.602233720225048</v>
+        <v>0.971297807435231</v>
       </c>
       <c r="U16" t="n">
-        <v>0.128446363686993</v>
+        <v>1.00612169684456</v>
       </c>
       <c r="V16" t="n">
-        <v>5.03107860480509</v>
+        <v>1.23977897961218</v>
       </c>
       <c r="W16" t="n">
-        <v>-1.66021346552919</v>
+        <v>0.920874961022716</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02398015451084</v>
+        <v>1.0488024409631</v>
       </c>
     </row>
     <row r="17">
@@ -1718,73 +1718,73 @@
         <v>39</v>
       </c>
       <c r="B17" t="n">
-        <v>-2.21962274601345</v>
+        <v>0.893770426116347</v>
       </c>
       <c r="C17" t="n">
-        <v>2.93021239266056</v>
+        <v>1.14023789151557</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.62634348466816</v>
+        <v>0.874305059384755</v>
       </c>
       <c r="E17" t="n">
-        <v>-3.58953751418488</v>
+        <v>0.828207274746978</v>
       </c>
       <c r="F17" t="n">
-        <v>2.49489145453697</v>
+        <v>1.11940373947665</v>
       </c>
       <c r="G17" t="n">
-        <v>0.364478302683168</v>
+        <v>1.01744367363932</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.06108536982928</v>
+        <v>0.949217205088752</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.86994201143415</v>
+        <v>0.910505898617878</v>
       </c>
       <c r="J17" t="n">
-        <v>3.71394322367107</v>
+        <v>1.17774669447196</v>
       </c>
       <c r="K17" t="n">
-        <v>-5.50966529179912</v>
+        <v>0.736311318109988</v>
       </c>
       <c r="L17" t="n">
-        <v>-5.132539335958</v>
+        <v>0.754360299479197</v>
       </c>
       <c r="M17" t="n">
-        <v>1.81226701774227</v>
+        <v>1.08673381699837</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.65584449074768</v>
+        <v>0.968611746788413</v>
       </c>
       <c r="O17" t="n">
-        <v>6.25182316609197</v>
+        <v>1.29920783255745</v>
       </c>
       <c r="P17" t="n">
-        <v>4.43222448621694</v>
+        <v>1.21212312739773</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.871595787769521</v>
+        <v>0.958286042391736</v>
       </c>
       <c r="R17" t="n">
-        <v>-1.75412606941886</v>
+        <v>0.916048767644299</v>
       </c>
       <c r="S17" t="n">
-        <v>4.61447064286299</v>
+        <v>1.22084529948631</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.464581665567765</v>
+        <v>0.977765450252273</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.207865406075726</v>
+        <v>0.990051708763466</v>
       </c>
       <c r="V17" t="n">
-        <v>4.48391845852631</v>
+        <v>1.21459716433065</v>
       </c>
       <c r="W17" t="n">
-        <v>-1.58951969598571</v>
+        <v>0.923926712191292</v>
       </c>
       <c r="X17" t="n">
-        <v>1.11453393471246</v>
+        <v>1.05334080540309</v>
       </c>
     </row>
     <row r="18">
@@ -1792,73 +1792,73 @@
         <v>40</v>
       </c>
       <c r="B18" t="n">
-        <v>-1.99945083836405</v>
+        <v>0.904498832977043</v>
       </c>
       <c r="C18" t="n">
-        <v>2.89894455828976</v>
+        <v>1.13846431387032</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.43802816407712</v>
+        <v>0.883550757819728</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.3226989988961</v>
+        <v>0.841295606787601</v>
       </c>
       <c r="F18" t="n">
-        <v>2.69148647404892</v>
+        <v>1.12855534848183</v>
       </c>
       <c r="G18" t="n">
-        <v>0.530977028282893</v>
+        <v>1.02536142669299</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.280226959161529</v>
+        <v>0.986615324009108</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.70555140275536</v>
+        <v>0.9185365570108</v>
       </c>
       <c r="J18" t="n">
-        <v>4.03675421972156</v>
+        <v>1.19281031149717</v>
       </c>
       <c r="K18" t="n">
-        <v>-5.95603939808097</v>
+        <v>0.715517529894936</v>
       </c>
       <c r="L18" t="n">
-        <v>-5.21050339242514</v>
+        <v>0.751127086895108</v>
       </c>
       <c r="M18" t="n">
-        <v>2.21375418406112</v>
+        <v>1.10573708741585</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.962369939297909</v>
+        <v>0.954033652367286</v>
       </c>
       <c r="O18" t="n">
-        <v>6.16235047561952</v>
+        <v>1.29433665021125</v>
       </c>
       <c r="P18" t="n">
-        <v>4.69866454428807</v>
+        <v>1.22442559667836</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.24051630123578</v>
+        <v>0.940748353394899</v>
       </c>
       <c r="R18" t="n">
-        <v>-1.2843799862521</v>
+        <v>0.938653261568379</v>
       </c>
       <c r="S18" t="n">
-        <v>4.61385076944982</v>
+        <v>1.22037457710776</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.439771663646826</v>
+        <v>0.978994878845702</v>
       </c>
       <c r="U18" t="n">
-        <v>0.072440872367218</v>
+        <v>1.00346004398732</v>
       </c>
       <c r="V18" t="n">
-        <v>4.33346667232153</v>
+        <v>1.2069823956264</v>
       </c>
       <c r="W18" t="n">
-        <v>-2.4699233469881</v>
+        <v>0.882027325919346</v>
       </c>
       <c r="X18" t="n">
-        <v>0.819480523205625</v>
+        <v>1.03914142064266</v>
       </c>
     </row>
     <row r="19">
@@ -1866,73 +1866,73 @@
         <v>41</v>
       </c>
       <c r="B19" t="n">
-        <v>-1.51173410282127</v>
+        <v>0.926998935096022</v>
       </c>
       <c r="C19" t="n">
-        <v>2.53894442052189</v>
+        <v>1.12260466049169</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.10969198844006</v>
+        <v>0.898123776206348</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.23920352457752</v>
+        <v>0.843580093686068</v>
       </c>
       <c r="F19" t="n">
-        <v>2.81002182419985</v>
+        <v>1.13569488522299</v>
       </c>
       <c r="G19" t="n">
-        <v>0.666933109903468</v>
+        <v>1.0322059462387</v>
       </c>
       <c r="H19" t="n">
-        <v>0.995353337715404</v>
+        <v>1.04806523413962</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.56551684803041</v>
+        <v>0.924401786783763</v>
       </c>
       <c r="J19" t="n">
-        <v>4.08235842545415</v>
+        <v>1.19713553582056</v>
       </c>
       <c r="K19" t="n">
-        <v>-5.225387275075</v>
+        <v>0.747668035731763</v>
       </c>
       <c r="L19" t="n">
-        <v>-4.87063314294565</v>
+        <v>0.764798977857232</v>
       </c>
       <c r="M19" t="n">
-        <v>2.17218428036303</v>
+        <v>1.10489395280443</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.508220798739438</v>
+        <v>0.975458210908194</v>
       </c>
       <c r="O19" t="n">
-        <v>6.46695218820278</v>
+        <v>1.31228666174883</v>
       </c>
       <c r="P19" t="n">
-        <v>4.72785123133846</v>
+        <v>1.22830613793205</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.418315892284098</v>
+        <v>0.979799684649565</v>
       </c>
       <c r="R19" t="n">
-        <v>-1.22331951810246</v>
+        <v>0.940926365706351</v>
       </c>
       <c r="S19" t="n">
-        <v>4.89274411255593</v>
+        <v>1.23626875245632</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.146145554772113</v>
+        <v>0.992942686740058</v>
       </c>
       <c r="U19" t="n">
-        <v>0.268966253849494</v>
+        <v>1.01298827810896</v>
       </c>
       <c r="V19" t="n">
-        <v>4.4000288157528</v>
+        <v>1.21247571815618</v>
       </c>
       <c r="W19" t="n">
-        <v>-1.64774636509036</v>
+        <v>0.920430954677301</v>
       </c>
       <c r="X19" t="n">
-        <v>1.42046030984687</v>
+        <v>1.0685934881532</v>
       </c>
     </row>
     <row r="20">
@@ -1940,73 +1940,73 @@
         <v>42</v>
       </c>
       <c r="B20" t="n">
-        <v>-2.09913902630422</v>
+        <v>0.899938716171893</v>
       </c>
       <c r="C20" t="n">
-        <v>2.48706908233985</v>
+        <v>1.11855304590581</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.17474953963505</v>
+        <v>0.896334531341836</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.68416435298902</v>
+        <v>0.824384087773897</v>
       </c>
       <c r="F20" t="n">
-        <v>2.36886587878339</v>
+        <v>1.11291856236173</v>
       </c>
       <c r="G20" t="n">
-        <v>0.267078077566844</v>
+        <v>1.01273101733082</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.241341771291986</v>
+        <v>0.988495775089589</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.81506594108843</v>
+        <v>0.913479847679389</v>
       </c>
       <c r="J20" t="n">
-        <v>3.86691574972485</v>
+        <v>1.18432726442794</v>
       </c>
       <c r="K20" t="n">
-        <v>-6.24870067559156</v>
+        <v>0.702138350999036</v>
       </c>
       <c r="L20" t="n">
-        <v>-5.02629308435904</v>
+        <v>0.760407799285794</v>
       </c>
       <c r="M20" t="n">
-        <v>1.92317627084996</v>
+        <v>1.09167353104182</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.838954984110191</v>
+        <v>0.960008883769908</v>
       </c>
       <c r="O20" t="n">
-        <v>6.11520829830423</v>
+        <v>1.29149836458518</v>
       </c>
       <c r="P20" t="n">
-        <v>4.55289536164138</v>
+        <v>1.21702638525232</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.784647555818272</v>
+        <v>0.962597597965679</v>
       </c>
       <c r="R20" t="n">
-        <v>-1.37634785546732</v>
+        <v>0.93439256205217</v>
       </c>
       <c r="S20" t="n">
-        <v>4.56268858422954</v>
+        <v>1.21749320636931</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.230933308294645</v>
+        <v>0.988991923347108</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0419660213119893</v>
+        <v>1.00200042680214</v>
       </c>
       <c r="V20" t="n">
-        <v>4.47138495016145</v>
+        <v>1.21314096541312</v>
       </c>
       <c r="W20" t="n">
-        <v>-1.5575805624804</v>
+        <v>0.925753602408178</v>
       </c>
       <c r="X20" t="n">
-        <v>0.881873865774745</v>
+        <v>1.04203696376378</v>
       </c>
     </row>
     <row r="21">
@@ -2014,73 +2014,73 @@
         <v>43</v>
       </c>
       <c r="B21" t="n">
-        <v>-1.71621213917592</v>
+        <v>0.917200346487607</v>
       </c>
       <c r="C21" t="n">
-        <v>2.69473784754695</v>
+        <v>1.13000919582748</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.55497130018633</v>
+        <v>0.924979504608931</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.54732881325644</v>
+        <v>0.828857056812803</v>
       </c>
       <c r="F21" t="n">
-        <v>2.50751720840508</v>
+        <v>1.12097662712723</v>
       </c>
       <c r="G21" t="n">
-        <v>0.816820010379554</v>
+        <v>1.03940795680066</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.540681336265759</v>
+        <v>0.973914514248268</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.79765820156249</v>
+        <v>0.913270933805096</v>
       </c>
       <c r="J21" t="n">
-        <v>4.05696968425697</v>
+        <v>1.19573086362625</v>
       </c>
       <c r="K21" t="n">
-        <v>-5.886508560992</v>
+        <v>0.716001968450176</v>
       </c>
       <c r="L21" t="n">
-        <v>-5.01384626699257</v>
+        <v>0.758104068725016</v>
       </c>
       <c r="M21" t="n">
-        <v>2.04284968677136</v>
+        <v>1.09855847210345</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.265124740282623</v>
+        <v>0.987208902599008</v>
       </c>
       <c r="O21" t="n">
-        <v>6.48987333975277</v>
+        <v>1.31310771646731</v>
       </c>
       <c r="P21" t="n">
-        <v>4.79725806996947</v>
+        <v>1.23144650765245</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.153582905942272</v>
+        <v>0.992590303315561</v>
       </c>
       <c r="R21" t="n">
-        <v>-0.865451398814095</v>
+        <v>0.958245793560211</v>
       </c>
       <c r="S21" t="n">
-        <v>4.93509925575328</v>
+        <v>1.23809673588596</v>
       </c>
       <c r="T21" t="n">
-        <v>0.451256801170523</v>
+        <v>1.02177114700982</v>
       </c>
       <c r="U21" t="n">
-        <v>0.674398769604556</v>
+        <v>1.03253676114845</v>
       </c>
       <c r="V21" t="n">
-        <v>4.82590299398573</v>
+        <v>1.23282849868333</v>
       </c>
       <c r="W21" t="n">
-        <v>-1.27143755052391</v>
+        <v>0.938658755381735</v>
       </c>
       <c r="X21" t="n">
-        <v>1.39023392092637</v>
+        <v>1.06707264464937</v>
       </c>
     </row>
     <row r="22">
@@ -2088,73 +2088,73 @@
         <v>44</v>
       </c>
       <c r="B22" t="n">
-        <v>-2.17735418198601</v>
+        <v>0.894325540344786</v>
       </c>
       <c r="C22" t="n">
-        <v>2.45234343968535</v>
+        <v>1.11902063064512</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.3776192139463</v>
+        <v>0.884605992089695</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.43007391822927</v>
+        <v>0.833526758813441</v>
       </c>
       <c r="F22" t="n">
-        <v>2.8021008008686</v>
+        <v>1.13599555390715</v>
       </c>
       <c r="G22" t="n">
-        <v>0.520475305000125</v>
+        <v>1.02526045007965</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.10215930612633</v>
+        <v>0.946508432072071</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.78781911859572</v>
+        <v>0.913231011802343</v>
       </c>
       <c r="J22" t="n">
-        <v>3.91795635845319</v>
+        <v>1.19015184785169</v>
       </c>
       <c r="K22" t="n">
-        <v>-5.02009806628731</v>
+        <v>0.756357438325803</v>
       </c>
       <c r="L22" t="n">
-        <v>-4.94346868372932</v>
+        <v>0.760076524849496</v>
       </c>
       <c r="M22" t="n">
-        <v>2.0695670580432</v>
+        <v>1.10044318117297</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.490133220604054</v>
+        <v>0.976212155250204</v>
       </c>
       <c r="O22" t="n">
-        <v>6.46285425087833</v>
+        <v>1.31366446324733</v>
       </c>
       <c r="P22" t="n">
-        <v>4.63542096866186</v>
+        <v>1.22497286394214</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.475349708287739</v>
+        <v>0.97692964976201</v>
       </c>
       <c r="R22" t="n">
-        <v>-1.40747291889006</v>
+        <v>0.931690516217536</v>
       </c>
       <c r="S22" t="n">
-        <v>4.83957526174623</v>
+        <v>1.23488117136703</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.18079682211998</v>
+        <v>0.991225310680745</v>
       </c>
       <c r="U22" t="n">
-        <v>0.156657920400279</v>
+        <v>1.00760314570132</v>
       </c>
       <c r="V22" t="n">
-        <v>5.15397872338924</v>
+        <v>1.25014024873613</v>
       </c>
       <c r="W22" t="n">
-        <v>-2.06099555799735</v>
+        <v>0.899972823096465</v>
       </c>
       <c r="X22" t="n">
-        <v>1.37296555045195</v>
+        <v>1.06663472294475</v>
       </c>
     </row>
     <row r="23">
@@ -2162,73 +2162,73 @@
         <v>45</v>
       </c>
       <c r="B23" t="n">
-        <v>-2.2157561679949</v>
+        <v>0.891625643960068</v>
       </c>
       <c r="C23" t="n">
-        <v>2.80638965609793</v>
+        <v>1.13726269892412</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.55010643704968</v>
+        <v>0.875272312477128</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.34651666967745</v>
+        <v>0.836319269109206</v>
       </c>
       <c r="F23" t="n">
-        <v>2.83291828768708</v>
+        <v>1.13856023491053</v>
       </c>
       <c r="G23" t="n">
-        <v>0.467731377950295</v>
+        <v>1.02287710516943</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.311602353429252</v>
+        <v>0.984759286747701</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.71588388281351</v>
+        <v>0.916074785878859</v>
       </c>
       <c r="J23" t="n">
-        <v>4.12066632538861</v>
+        <v>1.20154499214304</v>
       </c>
       <c r="K23" t="n">
-        <v>-4.79184690991385</v>
+        <v>0.765627043893647</v>
       </c>
       <c r="L23" t="n">
-        <v>-4.90483990771253</v>
+        <v>0.760100468564497</v>
       </c>
       <c r="M23" t="n">
-        <v>2.01540554862851</v>
+        <v>1.09857505155433</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.644717759758069</v>
+        <v>0.9684663533603</v>
       </c>
       <c r="O23" t="n">
-        <v>6.61204540420406</v>
+        <v>1.32340027893767</v>
       </c>
       <c r="P23" t="n">
-        <v>4.84470896706714</v>
+        <v>1.2369584804008</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.765133567685137</v>
+        <v>0.962576722619507</v>
       </c>
       <c r="R23" t="n">
-        <v>-1.50055105832838</v>
+        <v>0.926606881659485</v>
       </c>
       <c r="S23" t="n">
-        <v>4.90660775366668</v>
+        <v>1.23998599815491</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.410314827077891</v>
+        <v>0.979931182952119</v>
       </c>
       <c r="U23" t="n">
-        <v>0.148368615432189</v>
+        <v>1.00725682427798</v>
       </c>
       <c r="V23" t="n">
-        <v>4.96480751652057</v>
+        <v>1.24283259378311</v>
       </c>
       <c r="W23" t="n">
-        <v>-2.21241349632496</v>
+        <v>0.891789136629034</v>
       </c>
       <c r="X23" t="n">
-        <v>1.2257013305735</v>
+        <v>1.0599500045704</v>
       </c>
     </row>
     <row r="24">
@@ -2236,73 +2236,73 @@
         <v>46</v>
       </c>
       <c r="B24" t="n">
-        <v>-2.12135432374306</v>
+        <v>0.897509729104336</v>
       </c>
       <c r="C24" t="n">
-        <v>2.49604092934571</v>
+        <v>1.12059273085692</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.62699819837928</v>
+        <v>0.87308025161999</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.85544711168218</v>
+        <v>0.81372945835706</v>
       </c>
       <c r="F24" t="n">
-        <v>2.70706462794174</v>
+        <v>1.13078804608194</v>
       </c>
       <c r="G24" t="n">
-        <v>0.51574920075701</v>
+        <v>1.02491770220005</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.0585393160558</v>
+        <v>0.948858151586462</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.04517188985118</v>
+        <v>0.901190376980874</v>
       </c>
       <c r="J24" t="n">
-        <v>4.00226036336622</v>
+        <v>1.19336361881904</v>
       </c>
       <c r="K24" t="n">
-        <v>-4.62001612105933</v>
+        <v>0.776790374672431</v>
       </c>
       <c r="L24" t="n">
-        <v>-4.92084905319844</v>
+        <v>0.762256051780595</v>
       </c>
       <c r="M24" t="n">
-        <v>1.66623738166458</v>
+        <v>1.0805019315783</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.676569932895721</v>
+        <v>0.967312468772311</v>
       </c>
       <c r="O24" t="n">
-        <v>6.38513867188765</v>
+        <v>1.3084890557243</v>
       </c>
       <c r="P24" t="n">
-        <v>4.72739430821147</v>
+        <v>1.22839745244647</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.530808739228129</v>
+        <v>0.974354717234938</v>
       </c>
       <c r="R24" t="n">
-        <v>-1.23086899577909</v>
+        <v>0.940532283832772</v>
       </c>
       <c r="S24" t="n">
-        <v>4.99563694813466</v>
+        <v>1.24135722089429</v>
       </c>
       <c r="T24" t="n">
-        <v>0.0809151845880316</v>
+        <v>1.00390930411539</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0909993841680571</v>
+        <v>1.00439650813178</v>
       </c>
       <c r="V24" t="n">
-        <v>4.73375092739142</v>
+        <v>1.22870456362278</v>
       </c>
       <c r="W24" t="n">
-        <v>-2.12383607536229</v>
+        <v>0.897389826741537</v>
       </c>
       <c r="X24" t="n">
-        <v>1.32384512218887</v>
+        <v>1.06395972783916</v>
       </c>
     </row>
     <row r="25">
@@ -2310,73 +2310,73 @@
         <v>47</v>
       </c>
       <c r="B25" t="n">
-        <v>-1.64563812044799</v>
+        <v>0.919480321383403</v>
       </c>
       <c r="C25" t="n">
-        <v>2.62593423098728</v>
+        <v>1.1284847365409</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.54005115302908</v>
+        <v>0.875717449680893</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.26014794357956</v>
+        <v>0.840483723974428</v>
       </c>
       <c r="F25" t="n">
-        <v>2.9579647342708</v>
+        <v>1.14473070768309</v>
       </c>
       <c r="G25" t="n">
-        <v>0.673297354894894</v>
+        <v>1.03294386898061</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.161240297306476</v>
+        <v>0.992110648897932</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.29476880986141</v>
+        <v>0.936648059401751</v>
       </c>
       <c r="J25" t="n">
-        <v>4.35558178480894</v>
+        <v>1.21311492553761</v>
       </c>
       <c r="K25" t="n">
-        <v>-3.86103722770667</v>
+        <v>0.811082720533343</v>
       </c>
       <c r="L25" t="n">
-        <v>-4.90019171052578</v>
+        <v>0.760237772333667</v>
       </c>
       <c r="M25" t="n">
-        <v>2.26484922442488</v>
+        <v>1.11081715317587</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.827368052922623</v>
+        <v>0.959517582334059</v>
       </c>
       <c r="O25" t="n">
-        <v>6.78410836976389</v>
+        <v>1.33194067325376</v>
       </c>
       <c r="P25" t="n">
-        <v>4.99969014663489</v>
+        <v>1.24463060182394</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.703764716602853</v>
+        <v>0.965565388830969</v>
       </c>
       <c r="R25" t="n">
-        <v>-1.49330738050835</v>
+        <v>0.92693373539403</v>
       </c>
       <c r="S25" t="n">
-        <v>5.32738985177963</v>
+        <v>1.26066467068339</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.153087024358029</v>
+        <v>0.992509581633705</v>
       </c>
       <c r="U25" t="n">
-        <v>0.096862040558167</v>
+        <v>1.00473937755754</v>
       </c>
       <c r="V25" t="n">
-        <v>5.22955445931337</v>
+        <v>1.25587766784187</v>
       </c>
       <c r="W25" t="n">
-        <v>-1.61535426144015</v>
+        <v>0.920962084940216</v>
       </c>
       <c r="X25" t="n">
-        <v>1.59898133238876</v>
+        <v>1.07823680151675</v>
       </c>
     </row>
     <row r="26">
@@ -2384,73 +2384,73 @@
         <v>48</v>
       </c>
       <c r="B26" t="n">
-        <v>-2.09773875999344</v>
+        <v>0.896950431637946</v>
       </c>
       <c r="C26" t="n">
-        <v>2.93469687384358</v>
+        <v>1.14416439829905</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.22647109289103</v>
+        <v>0.890626569204581</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.91368808400713</v>
+        <v>0.807743521046486</v>
       </c>
       <c r="F26" t="n">
-        <v>2.46560575842207</v>
+        <v>1.12112071054891</v>
       </c>
       <c r="G26" t="n">
-        <v>0.855629998023386</v>
+        <v>1.04203206979606</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.1681045156812</v>
+        <v>0.942617894831151</v>
       </c>
       <c r="I26" t="n">
-        <v>-2.09065914298063</v>
+        <v>0.89729821158617</v>
       </c>
       <c r="J26" t="n">
-        <v>4.00426570457616</v>
+        <v>1.19670602476013</v>
       </c>
       <c r="K26" t="n">
-        <v>-4.79510239997881</v>
+        <v>0.764444819348615</v>
       </c>
       <c r="L26" t="n">
-        <v>-5.44385016558531</v>
+        <v>0.732575656945473</v>
       </c>
       <c r="M26" t="n">
-        <v>2.2239082785612</v>
+        <v>1.10924753479945</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.26000241358165</v>
+        <v>0.987227610509154</v>
       </c>
       <c r="O26" t="n">
-        <v>6.76312845160517</v>
+        <v>1.3322327264989</v>
       </c>
       <c r="P26" t="n">
-        <v>4.66844880585877</v>
+        <v>1.22933343442898</v>
       </c>
       <c r="Q26" t="n">
-        <v>-0.0819719315813622</v>
+        <v>0.995973201082822</v>
       </c>
       <c r="R26" t="n">
-        <v>-0.988749362840584</v>
+        <v>0.951428558692744</v>
       </c>
       <c r="S26" t="n">
-        <v>5.17151398594558</v>
+        <v>1.2540460681728</v>
       </c>
       <c r="T26" t="n">
-        <v>0.0511498778126763</v>
+        <v>1.00251269268171</v>
       </c>
       <c r="U26" t="n">
-        <v>0.231558187827998</v>
+        <v>1.01137509196162</v>
       </c>
       <c r="V26" t="n">
-        <v>5.13581221308462</v>
+        <v>1.25229225003622</v>
       </c>
       <c r="W26" t="n">
-        <v>-1.79675161665617</v>
+        <v>0.911736159868248</v>
       </c>
       <c r="X26" t="n">
-        <v>1.86444415710819</v>
+        <v>1.09158917654063</v>
       </c>
     </row>
     <row r="27">
@@ -2458,73 +2458,73 @@
         <v>49</v>
       </c>
       <c r="B27" t="n">
-        <v>-1.43478816894562</v>
+        <v>0.930140376086692</v>
       </c>
       <c r="C27" t="n">
-        <v>2.84869266621361</v>
+        <v>1.13870242493882</v>
       </c>
       <c r="D27" t="n">
-        <v>-1.39115935088096</v>
+        <v>0.932264656790804</v>
       </c>
       <c r="E27" t="n">
-        <v>-2.85487115169453</v>
+        <v>0.860996745516174</v>
       </c>
       <c r="F27" t="n">
-        <v>3.22127849394244</v>
+        <v>1.15684357383029</v>
       </c>
       <c r="G27" t="n">
-        <v>0.812157164738551</v>
+        <v>1.03954381233073</v>
       </c>
       <c r="H27" t="n">
-        <v>1.01053395612141</v>
+        <v>1.04920274898708</v>
       </c>
       <c r="I27" t="n">
-        <v>-1.25940026691935</v>
+        <v>0.938679987117569</v>
       </c>
       <c r="J27" t="n">
-        <v>3.79794031489577</v>
+        <v>1.18492115267356</v>
       </c>
       <c r="K27" t="n">
-        <v>-4.38265048236469</v>
+        <v>0.78660939568071</v>
       </c>
       <c r="L27" t="n">
-        <v>-4.74709939307679</v>
+        <v>0.768864432076311</v>
       </c>
       <c r="M27" t="n">
-        <v>1.97348406331546</v>
+        <v>1.09608864740182</v>
       </c>
       <c r="N27" t="n">
-        <v>0.151035576790992</v>
+        <v>1.00735389991395</v>
       </c>
       <c r="O27" t="n">
-        <v>6.72621041163902</v>
+        <v>1.32749819094493</v>
       </c>
       <c r="P27" t="n">
-        <v>4.51492172807897</v>
+        <v>1.21983087172611</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.242519420196616</v>
+        <v>1.01180823472991</v>
       </c>
       <c r="R27" t="n">
-        <v>-1.15073002541761</v>
+        <v>0.943971125117026</v>
       </c>
       <c r="S27" t="n">
-        <v>4.95231634628476</v>
+        <v>1.24112755104847</v>
       </c>
       <c r="T27" t="n">
-        <v>0.886038080356452</v>
+        <v>1.04314106319406</v>
       </c>
       <c r="U27" t="n">
-        <v>0.711337818166475</v>
+        <v>1.03463493324519</v>
       </c>
       <c r="V27" t="n">
-        <v>5.02934454819583</v>
+        <v>1.24487804281631</v>
       </c>
       <c r="W27" t="n">
-        <v>-0.740180831340596</v>
+        <v>0.963960704705774</v>
       </c>
       <c r="X27" t="n">
-        <v>1.91936766506512</v>
+        <v>1.09345372796832</v>
       </c>
     </row>
     <row r="28">
@@ -2532,73 +2532,73 @@
         <v>50</v>
       </c>
       <c r="B28" t="n">
-        <v>-1.52329655778501</v>
+        <v>0.925633597952039</v>
       </c>
       <c r="C28" t="n">
-        <v>2.36567148637442</v>
+        <v>1.11549062851224</v>
       </c>
       <c r="D28" t="n">
-        <v>-2.51046215515803</v>
+        <v>0.877440779996155</v>
       </c>
       <c r="E28" t="n">
-        <v>-3.11848010053134</v>
+        <v>0.847757717465144</v>
       </c>
       <c r="F28" t="n">
-        <v>3.22198820394415</v>
+        <v>1.15729548454879</v>
       </c>
       <c r="G28" t="n">
-        <v>0.447957888622026</v>
+        <v>1.02186902890023</v>
       </c>
       <c r="H28" t="n">
-        <v>1.25349280389176</v>
+        <v>1.06119474854849</v>
       </c>
       <c r="I28" t="n">
-        <v>-1.41586163550351</v>
+        <v>0.930878504850532</v>
       </c>
       <c r="J28" t="n">
-        <v>3.90548948076372</v>
+        <v>1.19066359694456</v>
       </c>
       <c r="K28" t="n">
-        <v>-4.87241083469269</v>
+        <v>0.762131896626568</v>
       </c>
       <c r="L28" t="n">
-        <v>-5.22885903334012</v>
+        <v>0.744730314567963</v>
       </c>
       <c r="M28" t="n">
-        <v>1.72181055953033</v>
+        <v>1.08405773364751</v>
       </c>
       <c r="N28" t="n">
-        <v>-0.358681661634656</v>
+        <v>0.982489381650583</v>
       </c>
       <c r="O28" t="n">
-        <v>6.58771736000888</v>
+        <v>1.32160831406664</v>
       </c>
       <c r="P28" t="n">
-        <v>4.59767059771645</v>
+        <v>1.2244554538028</v>
       </c>
       <c r="Q28" t="n">
-        <v>-0.339149871401315</v>
+        <v>0.983442911649575</v>
       </c>
       <c r="R28" t="n">
-        <v>-1.64223086897851</v>
+        <v>0.919827297952009</v>
       </c>
       <c r="S28" t="n">
-        <v>4.82550790806643</v>
+        <v>1.23557833131238</v>
       </c>
       <c r="T28" t="n">
-        <v>0.0634542426224806</v>
+        <v>1.00309779713897</v>
       </c>
       <c r="U28" t="n">
-        <v>0.0656418460877767</v>
+        <v>1.0032045945961</v>
       </c>
       <c r="V28" t="n">
-        <v>4.88270565441925</v>
+        <v>1.23837069014742</v>
       </c>
       <c r="W28" t="n">
-        <v>-1.50649252902377</v>
+        <v>0.926453960311881</v>
       </c>
       <c r="X28" t="n">
-        <v>1.36616033511943</v>
+        <v>1.06669510820086</v>
       </c>
     </row>
     <row r="29">
@@ -2606,73 +2606,73 @@
         <v>51</v>
       </c>
       <c r="B29" t="n">
-        <v>-2.69657807373913</v>
+        <v>0.869741214017385</v>
       </c>
       <c r="C29" t="n">
-        <v>1.9907513030191</v>
+        <v>1.09616367145084</v>
       </c>
       <c r="D29" t="n">
-        <v>-2.70024051171189</v>
+        <v>0.869564299160473</v>
       </c>
       <c r="E29" t="n">
-        <v>-3.97053828646383</v>
+        <v>0.808202290922319</v>
       </c>
       <c r="F29" t="n">
-        <v>3.68684930205552</v>
+        <v>1.17809405144376</v>
       </c>
       <c r="G29" t="n">
-        <v>0.00735532576058291</v>
+        <v>1.00035530059871</v>
       </c>
       <c r="H29" t="n">
-        <v>-1.72654713418241</v>
+        <v>0.916598767960567</v>
       </c>
       <c r="I29" t="n">
-        <v>-2.10497337434229</v>
+        <v>0.898318806735917</v>
       </c>
       <c r="J29" t="n">
-        <v>3.49016813589864</v>
+        <v>1.1685933252535</v>
       </c>
       <c r="K29" t="n">
-        <v>-5.17049951286402</v>
+        <v>0.750237904836378</v>
       </c>
       <c r="L29" t="n">
-        <v>-5.82859056406206</v>
+        <v>0.718448674541178</v>
       </c>
       <c r="M29" t="n">
-        <v>1.53127102152399</v>
+        <v>1.07396837726174</v>
       </c>
       <c r="N29" t="n">
-        <v>-1.25602251155459</v>
+        <v>0.939327561432303</v>
       </c>
       <c r="O29" t="n">
-        <v>6.02843749279913</v>
+        <v>1.29120497449393</v>
       </c>
       <c r="P29" t="n">
-        <v>4.11407856579482</v>
+        <v>1.19873145325789</v>
       </c>
       <c r="Q29" t="n">
-        <v>-1.2050706293875</v>
+        <v>0.941788803099751</v>
       </c>
       <c r="R29" t="n">
-        <v>-1.86074512499035</v>
+        <v>0.910116305044257</v>
       </c>
       <c r="S29" t="n">
-        <v>4.42694593416963</v>
+        <v>1.21384457902827</v>
       </c>
       <c r="T29" t="n">
-        <v>-0.694777720706354</v>
+        <v>0.966438612214373</v>
       </c>
       <c r="U29" t="n">
-        <v>-0.236633049537749</v>
+        <v>0.988569389458318</v>
       </c>
       <c r="V29" t="n">
-        <v>4.31927526758778</v>
+        <v>1.20864352423536</v>
       </c>
       <c r="W29" t="n">
-        <v>-1.4986800372488</v>
+        <v>0.927605937269334</v>
       </c>
       <c r="X29" t="n">
-        <v>0.654859095316776</v>
+        <v>1.03163310996865</v>
       </c>
     </row>
     <row r="30">
@@ -2680,73 +2680,73 @@
         <v>52</v>
       </c>
       <c r="B30" t="n">
-        <v>-2.20346184171732</v>
+        <v>0.893507133328111</v>
       </c>
       <c r="C30" t="n">
-        <v>2.10366027671719</v>
+        <v>1.10166947715182</v>
       </c>
       <c r="D30" t="n">
-        <v>-3.2870330757412</v>
+        <v>0.841138353996554</v>
       </c>
       <c r="E30" t="n">
-        <v>-4.01497718420245</v>
+        <v>0.805956961961857</v>
       </c>
       <c r="F30" t="n">
-        <v>2.52119643402396</v>
+        <v>1.12184891547425</v>
       </c>
       <c r="G30" t="n">
-        <v>0.126432025261681</v>
+        <v>1.00611043429677</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.782632150341624</v>
+        <v>0.962175545924359</v>
       </c>
       <c r="I30" t="n">
-        <v>-2.21709416685746</v>
+        <v>0.892848285801872</v>
       </c>
       <c r="J30" t="n">
-        <v>3.56911217818307</v>
+        <v>1.1724944721675</v>
       </c>
       <c r="K30" t="n">
-        <v>-6.42848629529773</v>
+        <v>0.689312553098873</v>
       </c>
       <c r="L30" t="n">
-        <v>-5.54281102574264</v>
+        <v>0.732117060356331</v>
       </c>
       <c r="M30" t="n">
-        <v>1.89413317299123</v>
+        <v>1.09154307446184</v>
       </c>
       <c r="N30" t="n">
-        <v>-1.20934733105118</v>
+        <v>0.941552487251032</v>
       </c>
       <c r="O30" t="n">
-        <v>6.29104794138307</v>
+        <v>1.30404507895904</v>
       </c>
       <c r="P30" t="n">
-        <v>4.31239433768327</v>
+        <v>1.20841714911732</v>
       </c>
       <c r="Q30" t="n">
-        <v>-1.18566892571216</v>
+        <v>0.942696859808355</v>
       </c>
       <c r="R30" t="n">
-        <v>-1.81513418881954</v>
+        <v>0.912274930519834</v>
       </c>
       <c r="S30" t="n">
-        <v>4.50820886241533</v>
+        <v>1.21788082562848</v>
       </c>
       <c r="T30" t="n">
-        <v>-0.60642361959115</v>
+        <v>0.970691668698255</v>
       </c>
       <c r="U30" t="n">
-        <v>-0.184704914501751</v>
+        <v>0.991073248711969</v>
       </c>
       <c r="V30" t="n">
-        <v>4.24995472569641</v>
+        <v>1.20539945525556</v>
       </c>
       <c r="W30" t="n">
-        <v>-2.30036551894309</v>
+        <v>0.88882379814007</v>
       </c>
       <c r="X30" t="n">
-        <v>0.684573141922202</v>
+        <v>1.03308528196388</v>
       </c>
     </row>
     <row r="31">
@@ -2754,73 +2754,73 @@
         <v>53</v>
       </c>
       <c r="B31" t="n">
-        <v>-2.44039238504849</v>
+        <v>0.882921854695913</v>
       </c>
       <c r="C31" t="n">
-        <v>2.00703405663661</v>
+        <v>1.09628772256167</v>
       </c>
       <c r="D31" t="n">
-        <v>-2.23722862433857</v>
+        <v>0.892668662808679</v>
       </c>
       <c r="E31" t="n">
-        <v>-3.91832320565078</v>
+        <v>0.812017929399316</v>
       </c>
       <c r="F31" t="n">
-        <v>3.70926356241689</v>
+        <v>1.1779524067492</v>
       </c>
       <c r="G31" t="n">
-        <v>0.090187450686217</v>
+        <v>1.00432675479597</v>
       </c>
       <c r="H31" t="n">
-        <v>-1.99691310959639</v>
+        <v>0.904197831202331</v>
       </c>
       <c r="I31" t="n">
-        <v>-2.30092703871786</v>
+        <v>0.889612723009804</v>
       </c>
       <c r="J31" t="n">
-        <v>3.29937735994454</v>
+        <v>1.15828806233262</v>
       </c>
       <c r="K31" t="n">
-        <v>-5.75414426870024</v>
+        <v>0.723944172699843</v>
       </c>
       <c r="L31" t="n">
-        <v>-5.45050752059013</v>
+        <v>0.738511185583793</v>
       </c>
       <c r="M31" t="n">
-        <v>1.61790779493325</v>
+        <v>1.07761933903102</v>
       </c>
       <c r="N31" t="n">
-        <v>-1.29300264765211</v>
+        <v>0.937968028097508</v>
       </c>
       <c r="O31" t="n">
-        <v>5.94326864991427</v>
+        <v>1.28512909433704</v>
       </c>
       <c r="P31" t="n">
-        <v>3.94139520144613</v>
+        <v>1.18908895263028</v>
       </c>
       <c r="Q31" t="n">
-        <v>-1.20020772688743</v>
+        <v>0.942419876613071</v>
       </c>
       <c r="R31" t="n">
-        <v>-1.88788123892466</v>
+        <v>0.909428649522979</v>
       </c>
       <c r="S31" t="n">
-        <v>4.47676433322903</v>
+        <v>1.21477335706714</v>
       </c>
       <c r="T31" t="n">
-        <v>-0.553844828253681</v>
+        <v>0.973429221597529</v>
       </c>
       <c r="U31" t="n">
-        <v>-0.159178565945175</v>
+        <v>0.992363387385076</v>
       </c>
       <c r="V31" t="n">
-        <v>4.33729521243385</v>
+        <v>1.20808230767281</v>
       </c>
       <c r="W31" t="n">
-        <v>-1.5112240961925</v>
+        <v>0.927498825432719</v>
       </c>
       <c r="X31" t="n">
-        <v>0.443758980175629</v>
+        <v>1.02128939537728</v>
       </c>
     </row>
     <row r="32">
@@ -2828,73 +2828,73 @@
         <v>54</v>
       </c>
       <c r="B32" t="n">
-        <v>-1.95411730343769</v>
+        <v>0.904863264703898</v>
       </c>
       <c r="C32" t="n">
-        <v>2.6473062072816</v>
+        <v>1.12888482664107</v>
       </c>
       <c r="D32" t="n">
-        <v>-1.91593205746744</v>
+        <v>0.906722323846201</v>
       </c>
       <c r="E32" t="n">
-        <v>-3.94779565239266</v>
+        <v>0.807800489088317</v>
       </c>
       <c r="F32" t="n">
-        <v>2.55266328412725</v>
+        <v>1.12427711004599</v>
       </c>
       <c r="G32" t="n">
-        <v>0.69953907528433</v>
+        <v>1.03405725117808</v>
       </c>
       <c r="H32" t="n">
-        <v>-1.11183210980625</v>
+        <v>0.945870149689447</v>
       </c>
       <c r="I32" t="n">
-        <v>-1.98989392638434</v>
+        <v>0.903121470032168</v>
       </c>
       <c r="J32" t="n">
-        <v>3.87702799839041</v>
+        <v>1.18875416832427</v>
       </c>
       <c r="K32" t="n">
-        <v>-5.10211249448946</v>
+        <v>0.751602257968208</v>
       </c>
       <c r="L32" t="n">
-        <v>-4.99425278654535</v>
+        <v>0.756853437345076</v>
       </c>
       <c r="M32" t="n">
-        <v>1.95441441216103</v>
+        <v>1.09515120011555</v>
       </c>
       <c r="N32" t="n">
-        <v>-0.224123301464161</v>
+        <v>0.989088495778849</v>
       </c>
       <c r="O32" t="n">
-        <v>6.72032111687391</v>
+        <v>1.32718067133231</v>
       </c>
       <c r="P32" t="n">
-        <v>4.5399143861741</v>
+        <v>1.22102697338823</v>
       </c>
       <c r="Q32" t="n">
-        <v>-0.0157933318591103</v>
+        <v>0.999231097319552</v>
       </c>
       <c r="R32" t="n">
-        <v>-1.10167381497975</v>
+        <v>0.94636470905099</v>
       </c>
       <c r="S32" t="n">
-        <v>4.96713668022338</v>
+        <v>1.24182640760339</v>
       </c>
       <c r="T32" t="n">
-        <v>0.513098686749359</v>
+        <v>1.02498034987776</v>
       </c>
       <c r="U32" t="n">
-        <v>0.35460210208031</v>
+        <v>1.01726390031024</v>
       </c>
       <c r="V32" t="n">
-        <v>5.1055696750449</v>
+        <v>1.24856605581254</v>
       </c>
       <c r="W32" t="n">
-        <v>-0.671423232404481</v>
+        <v>0.967311576321163</v>
       </c>
       <c r="X32" t="n">
-        <v>1.64543822939217</v>
+        <v>1.08010861016398</v>
       </c>
     </row>
     <row r="33">
@@ -2902,73 +2902,73 @@
         <v>55</v>
       </c>
       <c r="B33" t="n">
-        <v>-2.41482360787326</v>
+        <v>0.882552034400464</v>
       </c>
       <c r="C33" t="n">
-        <v>2.42127263212618</v>
+        <v>1.11776162195776</v>
       </c>
       <c r="D33" t="n">
-        <v>-2.13453898153752</v>
+        <v>0.896184027662676</v>
       </c>
       <c r="E33" t="n">
-        <v>-3.88810778815743</v>
+        <v>0.810897016137351</v>
       </c>
       <c r="F33" t="n">
-        <v>2.17112669280557</v>
+        <v>1.10559546142314</v>
       </c>
       <c r="G33" t="n">
-        <v>0.574981365806831</v>
+        <v>1.02796493766728</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.788369811481954</v>
+        <v>0.961656648462125</v>
       </c>
       <c r="I33" t="n">
-        <v>-2.36853163100241</v>
+        <v>0.884803502577823</v>
       </c>
       <c r="J33" t="n">
-        <v>3.61830472940526</v>
+        <v>1.17598077474573</v>
       </c>
       <c r="K33" t="n">
-        <v>-4.97809489780177</v>
+        <v>0.757884130169174</v>
       </c>
       <c r="L33" t="n">
-        <v>-5.35115180253258</v>
+        <v>0.739740041147252</v>
       </c>
       <c r="M33" t="n">
-        <v>1.76489392474566</v>
+        <v>1.08583782280599</v>
       </c>
       <c r="N33" t="n">
-        <v>-0.596096507503637</v>
+        <v>0.971008101014488</v>
       </c>
       <c r="O33" t="n">
-        <v>6.58895939359571</v>
+        <v>1.32046227876549</v>
       </c>
       <c r="P33" t="n">
-        <v>4.30379354666346</v>
+        <v>1.2093203804899</v>
       </c>
       <c r="Q33" t="n">
-        <v>-0.267192556223433</v>
+        <v>0.987004755937673</v>
       </c>
       <c r="R33" t="n">
-        <v>-1.41243813312542</v>
+        <v>0.931304305320717</v>
       </c>
       <c r="S33" t="n">
-        <v>4.74543807114714</v>
+        <v>1.23080031415863</v>
       </c>
       <c r="T33" t="n">
-        <v>0.539945063054691</v>
+        <v>1.02626090327448</v>
       </c>
       <c r="U33" t="n">
-        <v>0.0617183780190178</v>
+        <v>1.00300175048596</v>
       </c>
       <c r="V33" t="n">
-        <v>4.73708387179434</v>
+        <v>1.23039399722724</v>
       </c>
       <c r="W33" t="n">
-        <v>-1.22718811278343</v>
+        <v>0.940314171691702</v>
       </c>
       <c r="X33" t="n">
-        <v>1.36599665860072</v>
+        <v>1.0664369554966</v>
       </c>
     </row>
     <row r="34">
@@ -2976,73 +2976,73 @@
         <v>56</v>
       </c>
       <c r="B34" t="n">
-        <v>-1.83326059805223</v>
+        <v>0.910885952519152</v>
       </c>
       <c r="C34" t="n">
-        <v>2.44266928508559</v>
+        <v>1.11873715438078</v>
       </c>
       <c r="D34" t="n">
-        <v>-2.33492270506377</v>
+        <v>0.886500362782993</v>
       </c>
       <c r="E34" t="n">
-        <v>-3.41224004010571</v>
+        <v>0.834132407976748</v>
       </c>
       <c r="F34" t="n">
-        <v>2.78055599393906</v>
+        <v>1.13516168903117</v>
       </c>
       <c r="G34" t="n">
-        <v>0.582727603950996</v>
+        <v>1.02832615036949</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.652644123167821</v>
+        <v>0.968275236241991</v>
       </c>
       <c r="I34" t="n">
-        <v>-1.75387677692288</v>
+        <v>0.914744767579514</v>
       </c>
       <c r="J34" t="n">
-        <v>3.94357433945348</v>
+        <v>1.19169553488669</v>
       </c>
       <c r="K34" t="n">
-        <v>-5.75264127753682</v>
+        <v>0.720366461543241</v>
       </c>
       <c r="L34" t="n">
-        <v>-4.72164092354239</v>
+        <v>0.770482966854185</v>
       </c>
       <c r="M34" t="n">
-        <v>1.73597953585791</v>
+        <v>1.08438525485607</v>
       </c>
       <c r="N34" t="n">
-        <v>-0.48919137643888</v>
+        <v>0.976220607373817</v>
       </c>
       <c r="O34" t="n">
-        <v>6.49551988722553</v>
+        <v>1.3157445636796</v>
       </c>
       <c r="P34" t="n">
-        <v>4.57970120595427</v>
+        <v>1.22261740155716</v>
       </c>
       <c r="Q34" t="n">
-        <v>-0.503697782552476</v>
+        <v>0.975515456908816</v>
       </c>
       <c r="R34" t="n">
-        <v>-1.72945153650252</v>
+        <v>0.91593206852127</v>
       </c>
       <c r="S34" t="n">
-        <v>4.74477200637328</v>
+        <v>1.23064142561673</v>
       </c>
       <c r="T34" t="n">
-        <v>-0.138823759756733</v>
+        <v>0.99325183384644</v>
       </c>
       <c r="U34" t="n">
-        <v>0.248551098821943</v>
+        <v>1.01208196720388</v>
       </c>
       <c r="V34" t="n">
-        <v>5.13310528283137</v>
+        <v>1.24951814727509</v>
       </c>
       <c r="W34" t="n">
-        <v>-1.85591566135952</v>
+        <v>0.909784699162487</v>
       </c>
       <c r="X34" t="n">
-        <v>1.21120807066299</v>
+        <v>1.05887632867522</v>
       </c>
     </row>
     <row r="35">
@@ -3050,73 +3050,73 @@
         <v>57</v>
       </c>
       <c r="B35" t="n">
-        <v>-2.16139492008286</v>
+        <v>0.894736540101924</v>
       </c>
       <c r="C35" t="n">
-        <v>2.69735290763087</v>
+        <v>1.1313654885487</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.62368936533203</v>
+        <v>0.920923678127268</v>
       </c>
       <c r="E35" t="n">
-        <v>-3.59133136932522</v>
+        <v>0.825096301437973</v>
       </c>
       <c r="F35" t="n">
-        <v>2.69753876283891</v>
+        <v>1.13137454000064</v>
       </c>
       <c r="G35" t="n">
-        <v>0.798539830901595</v>
+        <v>1.03889019294258</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.56140512834331</v>
+        <v>0.923957022113425</v>
       </c>
       <c r="I35" t="n">
-        <v>-2.06381333942258</v>
+        <v>0.899488922328413</v>
       </c>
       <c r="J35" t="n">
-        <v>4.02770770181772</v>
+        <v>1.19615593809909</v>
       </c>
       <c r="K35" t="n">
-        <v>-4.74751048935454</v>
+        <v>0.768788491465174</v>
       </c>
       <c r="L35" t="n">
-        <v>-5.36123421132845</v>
+        <v>0.738899144638162</v>
       </c>
       <c r="M35" t="n">
-        <v>2.26042000367761</v>
+        <v>1.1100861430732</v>
       </c>
       <c r="N35" t="n">
-        <v>-0.549454633870933</v>
+        <v>0.973240662647589</v>
       </c>
       <c r="O35" t="n">
-        <v>6.51743470303358</v>
+        <v>1.31740970617013</v>
       </c>
       <c r="P35" t="n">
-        <v>4.80594848087939</v>
+        <v>1.23405753409001</v>
       </c>
       <c r="Q35" t="n">
-        <v>-0.271742910608737</v>
+        <v>0.98676567678231</v>
       </c>
       <c r="R35" t="n">
-        <v>-1.05815411378299</v>
+        <v>0.948466167803379</v>
       </c>
       <c r="S35" t="n">
-        <v>4.90814833677279</v>
+        <v>1.23903483385715</v>
       </c>
       <c r="T35" t="n">
-        <v>0.341805771821884</v>
+        <v>1.01664649889791</v>
       </c>
       <c r="U35" t="n">
-        <v>0.522789241881401</v>
+        <v>1.02546068924591</v>
       </c>
       <c r="V35" t="n">
-        <v>5.24024761915532</v>
+        <v>1.25520861087885</v>
       </c>
       <c r="W35" t="n">
-        <v>-1.76130686511814</v>
+        <v>0.914221481302703</v>
       </c>
       <c r="X35" t="n">
-        <v>1.4597845640274</v>
+        <v>1.07109389056463</v>
       </c>
     </row>
     <row r="36">
@@ -3124,73 +3124,73 @@
         <v>58</v>
       </c>
       <c r="B36" t="n">
-        <v>-2.43074742878694</v>
+        <v>0.880770689186182</v>
       </c>
       <c r="C36" t="n">
-        <v>2.45433579241933</v>
+        <v>1.12038633120426</v>
       </c>
       <c r="D36" t="n">
-        <v>-2.63541657763932</v>
+        <v>0.870731570652711</v>
       </c>
       <c r="E36" t="n">
-        <v>-3.63551463322098</v>
+        <v>0.821676288108302</v>
       </c>
       <c r="F36" t="n">
-        <v>2.36941685074127</v>
+        <v>1.11622101695918</v>
       </c>
       <c r="G36" t="n">
-        <v>0.209819879374856</v>
+        <v>1.01029176430123</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.04977005229464</v>
+        <v>0.948508282528334</v>
       </c>
       <c r="I36" t="n">
-        <v>-2.09730199664847</v>
+        <v>0.897126345309502</v>
       </c>
       <c r="J36" t="n">
-        <v>3.77870823639774</v>
+        <v>1.18534742583973</v>
       </c>
       <c r="K36" t="n">
-        <v>-5.96207854903399</v>
+        <v>0.707557227871296</v>
       </c>
       <c r="L36" t="n">
-        <v>-5.58818530014484</v>
+        <v>0.725896868532868</v>
       </c>
       <c r="M36" t="n">
-        <v>1.70638387052662</v>
+        <v>1.08369893575008</v>
       </c>
       <c r="N36" t="n">
-        <v>-0.73291012488205</v>
+        <v>0.964050411802034</v>
       </c>
       <c r="O36" t="n">
-        <v>6.45145359869146</v>
+        <v>1.31644684972604</v>
       </c>
       <c r="P36" t="n">
-        <v>4.47643899117787</v>
+        <v>1.21957144929887</v>
       </c>
       <c r="Q36" t="n">
-        <v>-0.856840785608602</v>
+        <v>0.957971554290086</v>
       </c>
       <c r="R36" t="n">
-        <v>-1.69242793871686</v>
+        <v>0.916985609304557</v>
       </c>
       <c r="S36" t="n">
-        <v>4.85762714419332</v>
+        <v>1.23826890845739</v>
       </c>
       <c r="T36" t="n">
-        <v>-0.290884378125528</v>
+        <v>0.985731983701934</v>
       </c>
       <c r="U36" t="n">
-        <v>-0.0136120170387996</v>
+        <v>0.999332324127508</v>
       </c>
       <c r="V36" t="n">
-        <v>5.08414319070262</v>
+        <v>1.24937962765171</v>
       </c>
       <c r="W36" t="n">
-        <v>-2.37388424236532</v>
+        <v>0.883559855369157</v>
       </c>
       <c r="X36" t="n">
-        <v>1.09562398888631</v>
+        <v>1.05374087474452</v>
       </c>
     </row>
     <row r="37">
@@ -3198,73 +3198,73 @@
         <v>59</v>
       </c>
       <c r="B37" t="n">
-        <v>-1.33455905631518</v>
+        <v>0.933964957688173</v>
       </c>
       <c r="C37" t="n">
-        <v>2.60699876839358</v>
+        <v>1.12899637012174</v>
       </c>
       <c r="D37" t="n">
-        <v>-2.06339719096682</v>
+        <v>0.897901467779317</v>
       </c>
       <c r="E37" t="n">
-        <v>-3.40752180284501</v>
+        <v>0.831393114179128</v>
       </c>
       <c r="F37" t="n">
-        <v>3.36385494973905</v>
+        <v>1.16644621523921</v>
       </c>
       <c r="G37" t="n">
-        <v>0.854675421757357</v>
+        <v>1.04229001884297</v>
       </c>
       <c r="H37" t="n">
-        <v>0.080528694528167</v>
+        <v>1.00398462377916</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.31637030818897</v>
+        <v>0.93486495139503</v>
       </c>
       <c r="J37" t="n">
-        <v>4.69785547518991</v>
+        <v>1.23245362100016</v>
       </c>
       <c r="K37" t="n">
-        <v>-3.28545485951075</v>
+        <v>0.83743308350818</v>
       </c>
       <c r="L37" t="n">
-        <v>-4.9849176928337</v>
+        <v>0.753342312421798</v>
       </c>
       <c r="M37" t="n">
-        <v>2.45442913365537</v>
+        <v>1.12144710338996</v>
       </c>
       <c r="N37" t="n">
-        <v>-0.496234972078225</v>
+        <v>0.975445899360744</v>
       </c>
       <c r="O37" t="n">
-        <v>7.06638083429811</v>
+        <v>1.34965013738153</v>
       </c>
       <c r="P37" t="n">
-        <v>5.334787647977</v>
+        <v>1.26396953090368</v>
       </c>
       <c r="Q37" t="n">
-        <v>-0.707117041427164</v>
+        <v>0.965011287039643</v>
       </c>
       <c r="R37" t="n">
-        <v>-1.26009742616212</v>
+        <v>0.93764937830223</v>
       </c>
       <c r="S37" t="n">
-        <v>5.34263451150551</v>
+        <v>1.2643577999448</v>
       </c>
       <c r="T37" t="n">
-        <v>0.11401574323248</v>
+        <v>1.00564158955195</v>
       </c>
       <c r="U37" t="n">
-        <v>0.539715857284511</v>
+        <v>1.02670556938151</v>
       </c>
       <c r="V37" t="n">
-        <v>5.28683110216338</v>
+        <v>1.261596602919</v>
       </c>
       <c r="W37" t="n">
-        <v>-1.78713963437327</v>
+        <v>0.911570911145118</v>
       </c>
       <c r="X37" t="n">
-        <v>1.64487873838425</v>
+        <v>1.08138990670592</v>
       </c>
     </row>
     <row r="38">
@@ -3272,73 +3272,73 @@
         <v>60</v>
       </c>
       <c r="B38" t="n">
-        <v>-1.85186799622893</v>
+        <v>0.90934824513505</v>
       </c>
       <c r="C38" t="n">
-        <v>2.74879957138096</v>
+        <v>1.13455791958451</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.88189446303803</v>
+        <v>0.907878403918408</v>
       </c>
       <c r="E38" t="n">
-        <v>-3.11061742224722</v>
+        <v>0.847730546337851</v>
       </c>
       <c r="F38" t="n">
-        <v>3.13771068439662</v>
+        <v>1.15359571004968</v>
       </c>
       <c r="G38" t="n">
-        <v>0.869537561481435</v>
+        <v>1.04256518608767</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.2782751893974</v>
+        <v>0.937426485389256</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.92028184425882</v>
+        <v>0.905999283225453</v>
       </c>
       <c r="J38" t="n">
-        <v>3.88480458614531</v>
+        <v>1.1901670927726</v>
       </c>
       <c r="K38" t="n">
-        <v>-4.18646579644606</v>
+        <v>0.795066132195845</v>
       </c>
       <c r="L38" t="n">
-        <v>-5.66464340707511</v>
+        <v>0.722707090040317</v>
       </c>
       <c r="M38" t="n">
-        <v>2.03884968986586</v>
+        <v>1.09980479314323</v>
       </c>
       <c r="N38" t="n">
-        <v>-0.0653262980229282</v>
+        <v>0.996802178359004</v>
       </c>
       <c r="O38" t="n">
-        <v>6.8827178472836</v>
+        <v>1.33691950634015</v>
       </c>
       <c r="P38" t="n">
-        <v>4.57764334490061</v>
+        <v>1.22408260373101</v>
       </c>
       <c r="Q38" t="n">
-        <v>-0.0981239182163469</v>
+        <v>0.995196684969636</v>
       </c>
       <c r="R38" t="n">
-        <v>-0.525347340922766</v>
+        <v>0.974283448677086</v>
       </c>
       <c r="S38" t="n">
-        <v>4.8955290927529</v>
+        <v>1.23964359455111</v>
       </c>
       <c r="T38" t="n">
-        <v>0.623601102149069</v>
+        <v>1.03052622236609</v>
       </c>
       <c r="U38" t="n">
-        <v>0.632619548684292</v>
+        <v>1.03096768903987</v>
       </c>
       <c r="V38" t="n">
-        <v>5.23492339203864</v>
+        <v>1.25625746167559</v>
       </c>
       <c r="W38" t="n">
-        <v>-1.50879243270831</v>
+        <v>0.926142315742544</v>
       </c>
       <c r="X38" t="n">
-        <v>2.09427217186439</v>
+        <v>1.10251780792742</v>
       </c>
     </row>
     <row r="39">
@@ -3346,73 +3346,73 @@
         <v>61</v>
       </c>
       <c r="B39" t="n">
-        <v>-2.5240360656132</v>
+        <v>0.877274732302003</v>
       </c>
       <c r="C39" t="n">
-        <v>2.35809490240892</v>
+        <v>1.1146567721825</v>
       </c>
       <c r="D39" t="n">
-        <v>-2.56030643000793</v>
+        <v>0.875511171851941</v>
       </c>
       <c r="E39" t="n">
-        <v>-3.54547822792153</v>
+        <v>0.827609529607344</v>
       </c>
       <c r="F39" t="n">
-        <v>3.09243010297436</v>
+        <v>1.15036207976397</v>
       </c>
       <c r="G39" t="n">
-        <v>0.260243258726843</v>
+        <v>1.01265371126386</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.183090906136122</v>
+        <v>0.991097638906691</v>
       </c>
       <c r="I39" t="n">
-        <v>-2.20033177926865</v>
+        <v>0.893014085529895</v>
       </c>
       <c r="J39" t="n">
-        <v>3.88967565069187</v>
+        <v>1.18912625377782</v>
       </c>
       <c r="K39" t="n">
-        <v>-5.03813220911747</v>
+        <v>0.75503276974308</v>
       </c>
       <c r="L39" t="n">
-        <v>-5.91152826967334</v>
+        <v>0.712565957640672</v>
       </c>
       <c r="M39" t="n">
-        <v>1.88073607357475</v>
+        <v>1.09144633123246</v>
       </c>
       <c r="N39" t="n">
-        <v>-0.593951760070443</v>
+        <v>0.971120504279866</v>
       </c>
       <c r="O39" t="n">
-        <v>6.37234912862723</v>
+        <v>1.30984036374531</v>
       </c>
       <c r="P39" t="n">
-        <v>4.48959980977176</v>
+        <v>1.21829614323568</v>
       </c>
       <c r="Q39" t="n">
-        <v>-0.768786628629731</v>
+        <v>0.962619573433749</v>
       </c>
       <c r="R39" t="n">
-        <v>-1.48458352493832</v>
+        <v>0.927815646931405</v>
       </c>
       <c r="S39" t="n">
-        <v>4.62400686555432</v>
+        <v>1.22483136756394</v>
       </c>
       <c r="T39" t="n">
-        <v>-0.186918310389096</v>
+        <v>0.990911540451944</v>
       </c>
       <c r="U39" t="n">
-        <v>0.132520117404623</v>
+        <v>1.00644347642469</v>
       </c>
       <c r="V39" t="n">
-        <v>4.91800834848916</v>
+        <v>1.23912649241907</v>
       </c>
       <c r="W39" t="n">
-        <v>-1.8670002860464</v>
+        <v>0.909221538860375</v>
       </c>
       <c r="X39" t="n">
-        <v>1.12628825908098</v>
+        <v>1.0547630954977</v>
       </c>
     </row>
     <row r="40">
@@ -3420,73 +3420,73 @@
         <v>62</v>
       </c>
       <c r="B40" t="n">
-        <v>-2.30933596978497</v>
+        <v>0.88783869602889</v>
       </c>
       <c r="C40" t="n">
-        <v>2.11888500302019</v>
+        <v>1.10291135980777</v>
       </c>
       <c r="D40" t="n">
-        <v>-2.06487244926632</v>
+        <v>0.899711956391822</v>
       </c>
       <c r="E40" t="n">
-        <v>-4.19383365044779</v>
+        <v>0.796311209357752</v>
       </c>
       <c r="F40" t="n">
-        <v>2.48698450400509</v>
+        <v>1.12078945141582</v>
       </c>
       <c r="G40" t="n">
-        <v>0.590485634333196</v>
+        <v>1.02867908333372</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.493651408602843</v>
+        <v>0.976024023173542</v>
       </c>
       <c r="I40" t="n">
-        <v>-2.62772525940205</v>
+        <v>0.872374961708235</v>
       </c>
       <c r="J40" t="n">
-        <v>3.61013087752728</v>
+        <v>1.17533914165271</v>
       </c>
       <c r="K40" t="n">
-        <v>-4.44161683634239</v>
+        <v>0.78427671736712</v>
       </c>
       <c r="L40" t="n">
-        <v>-5.51611321192767</v>
+        <v>0.732089891294733</v>
       </c>
       <c r="M40" t="n">
-        <v>1.56689442791986</v>
+        <v>1.0761019290913</v>
       </c>
       <c r="N40" t="n">
-        <v>-0.0264694342593851</v>
+        <v>0.998714415615244</v>
       </c>
       <c r="O40" t="n">
-        <v>6.65474864208093</v>
+        <v>1.32321208133491</v>
       </c>
       <c r="P40" t="n">
-        <v>4.09667399532019</v>
+        <v>1.19896987847222</v>
       </c>
       <c r="Q40" t="n">
-        <v>-0.146137495143312</v>
+        <v>0.992902300822053</v>
       </c>
       <c r="R40" t="n">
-        <v>-0.926834793257148</v>
+        <v>0.954984895945134</v>
       </c>
       <c r="S40" t="n">
-        <v>5.00078052560255</v>
+        <v>1.24288110173815</v>
       </c>
       <c r="T40" t="n">
-        <v>0.526557837835886</v>
+        <v>1.02557419729334</v>
       </c>
       <c r="U40" t="n">
-        <v>0.116516389349978</v>
+        <v>1.00565904239768</v>
       </c>
       <c r="V40" t="n">
-        <v>4.91764998208522</v>
+        <v>1.23884356441888</v>
       </c>
       <c r="W40" t="n">
-        <v>-1.10248479203721</v>
+        <v>0.946453814645807</v>
       </c>
       <c r="X40" t="n">
-        <v>1.99246135309379</v>
+        <v>1.09677113525229</v>
       </c>
     </row>
   </sheetData>

--- a/example1-metabolomics/results-A/report/normalized_data.xlsx
+++ b/example1-metabolomics/results-A/report/normalized_data.xlsx
@@ -608,73 +608,73 @@
         <v>24</v>
       </c>
       <c r="B2" t="n">
-        <v>0.968556057526809</v>
+        <v>-0.652379038394408</v>
       </c>
       <c r="C2" t="n">
-        <v>1.18239859585372</v>
+        <v>3.78429074754196</v>
       </c>
       <c r="D2" t="n">
-        <v>0.924644671508796</v>
+        <v>-1.5634247130715</v>
       </c>
       <c r="E2" t="n">
-        <v>0.838649531070503</v>
+        <v>-3.34759751753318</v>
       </c>
       <c r="F2" t="n">
-        <v>1.15682836733682</v>
+        <v>3.25377581273048</v>
       </c>
       <c r="G2" t="n">
-        <v>1.07781129467108</v>
+        <v>1.61437954661777</v>
       </c>
       <c r="H2" t="n">
-        <v>1.02328112920002</v>
+        <v>0.483022149439317</v>
       </c>
       <c r="I2" t="n">
-        <v>0.952299003011462</v>
+        <v>-0.989670127159433</v>
       </c>
       <c r="J2" t="n">
-        <v>1.22190360381466</v>
+        <v>4.60391567616835</v>
       </c>
       <c r="K2" t="n">
-        <v>0.808493782843469</v>
+        <v>-3.97324991615303</v>
       </c>
       <c r="L2" t="n">
-        <v>0.807302317986294</v>
+        <v>-3.99796967572093</v>
       </c>
       <c r="M2" t="n">
-        <v>1.14485605774408</v>
+        <v>3.00538190264335</v>
       </c>
       <c r="N2" t="n">
-        <v>1.01535504919231</v>
+        <v>0.318576852604286</v>
       </c>
       <c r="O2" t="n">
-        <v>1.32628949329205</v>
+        <v>6.76964811437209</v>
       </c>
       <c r="P2" t="n">
-        <v>1.25908484772584</v>
+        <v>5.37532861746097</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.03824262516412</v>
+        <v>0.793433808483783</v>
       </c>
       <c r="R2" t="n">
-        <v>0.990971632261867</v>
+        <v>-0.187314865758203</v>
       </c>
       <c r="S2" t="n">
-        <v>1.26654101623018</v>
+        <v>5.53002448751979</v>
       </c>
       <c r="T2" t="n">
-        <v>1.03868207819783</v>
+        <v>0.802551302188487</v>
       </c>
       <c r="U2" t="n">
-        <v>1.03203312150951</v>
+        <v>0.664602952538775</v>
       </c>
       <c r="V2" t="n">
-        <v>1.26701788681162</v>
+        <v>5.53991829684804</v>
       </c>
       <c r="W2" t="n">
-        <v>0.972278692900302</v>
+        <v>-0.575144153254828</v>
       </c>
       <c r="X2" t="n">
-        <v>1.10405312726492</v>
+        <v>2.15882849820424</v>
       </c>
     </row>
     <row r="3">
@@ -682,73 +682,73 @@
         <v>25</v>
       </c>
       <c r="B3" t="n">
-        <v>0.938319769072406</v>
+        <v>-1.28821519068625</v>
       </c>
       <c r="C3" t="n">
-        <v>1.1582507204401</v>
+        <v>3.3051267633431</v>
       </c>
       <c r="D3" t="n">
-        <v>0.909871311265531</v>
+        <v>-1.88237210202196</v>
       </c>
       <c r="E3" t="n">
-        <v>0.857725727201505</v>
+        <v>-2.97145254981312</v>
       </c>
       <c r="F3" t="n">
-        <v>1.15116005152157</v>
+        <v>3.15703543366421</v>
       </c>
       <c r="G3" t="n">
-        <v>1.0658990400906</v>
+        <v>1.37632663204536</v>
       </c>
       <c r="H3" t="n">
-        <v>1.00570549308245</v>
+        <v>0.119161403072439</v>
       </c>
       <c r="I3" t="n">
-        <v>0.944195802822282</v>
+        <v>-1.16549198061169</v>
       </c>
       <c r="J3" t="n">
-        <v>1.21069546310485</v>
+        <v>4.40045525281779</v>
       </c>
       <c r="K3" t="n">
-        <v>0.74019730459299</v>
+        <v>-5.42607856312055</v>
       </c>
       <c r="L3" t="n">
-        <v>0.78422976479876</v>
+        <v>-4.50644380710046</v>
       </c>
       <c r="M3" t="n">
-        <v>1.12309409226077</v>
+        <v>2.57086715061429</v>
       </c>
       <c r="N3" t="n">
-        <v>0.995653427924741</v>
+        <v>-0.0907798185991521</v>
       </c>
       <c r="O3" t="n">
-        <v>1.31081752467816</v>
+        <v>6.49154276500563</v>
       </c>
       <c r="P3" t="n">
-        <v>1.2480946393503</v>
+        <v>5.18155133877589</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.99607664783231</v>
+        <v>-0.0819407091189893</v>
       </c>
       <c r="R3" t="n">
-        <v>0.960516935532751</v>
+        <v>-0.824618887715601</v>
       </c>
       <c r="S3" t="n">
-        <v>1.25178071020815</v>
+        <v>5.25853633707465</v>
       </c>
       <c r="T3" t="n">
-        <v>1.01541362535463</v>
+        <v>0.321919455014598</v>
       </c>
       <c r="U3" t="n">
-        <v>1.02187110852091</v>
+        <v>0.456786458320108</v>
       </c>
       <c r="V3" t="n">
-        <v>1.25567840049707</v>
+        <v>5.33994108805021</v>
       </c>
       <c r="W3" t="n">
-        <v>0.934213836670579</v>
+        <v>-1.37396915775834</v>
       </c>
       <c r="X3" t="n">
-        <v>1.07020853013645</v>
+        <v>1.46633197829146</v>
       </c>
     </row>
     <row r="4">
@@ -756,73 +756,73 @@
         <v>26</v>
       </c>
       <c r="B4" t="n">
-        <v>0.953773026167992</v>
+        <v>-0.965102530560669</v>
       </c>
       <c r="C4" t="n">
-        <v>1.1698078220365</v>
+        <v>3.54515870651582</v>
       </c>
       <c r="D4" t="n">
-        <v>0.950886592637439</v>
+        <v>-1.02536397693515</v>
       </c>
       <c r="E4" t="n">
-        <v>0.865919495297036</v>
+        <v>-2.79926250110888</v>
       </c>
       <c r="F4" t="n">
-        <v>1.11545159115377</v>
+        <v>2.41033780806573</v>
       </c>
       <c r="G4" t="n">
-        <v>1.06213161007331</v>
+        <v>1.29715118985454</v>
       </c>
       <c r="H4" t="n">
-        <v>0.989686724506203</v>
+        <v>-0.21531516022666</v>
       </c>
       <c r="I4" t="n">
-        <v>0.946403879628932</v>
+        <v>-1.11895170958685</v>
       </c>
       <c r="J4" t="n">
-        <v>1.210513308538</v>
+        <v>4.39498651858633</v>
       </c>
       <c r="K4" t="n">
-        <v>0.778938035937712</v>
+        <v>-4.61521581971912</v>
       </c>
       <c r="L4" t="n">
-        <v>0.798897890936425</v>
+        <v>-4.19850442868396</v>
       </c>
       <c r="M4" t="n">
-        <v>1.13116165901229</v>
+        <v>2.73832437064371</v>
       </c>
       <c r="N4" t="n">
-        <v>1.01833532685671</v>
+        <v>0.382795343955929</v>
       </c>
       <c r="O4" t="n">
-        <v>1.30993479351791</v>
+        <v>6.47065617186956</v>
       </c>
       <c r="P4" t="n">
-        <v>1.25229980231139</v>
+        <v>5.26738303388735</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.01462833852379</v>
+        <v>0.305402784497943</v>
       </c>
       <c r="R4" t="n">
-        <v>0.983027646905237</v>
+        <v>-0.354339892134212</v>
       </c>
       <c r="S4" t="n">
-        <v>1.24622910202038</v>
+        <v>5.14064213506886</v>
       </c>
       <c r="T4" t="n">
-        <v>1.03271482551491</v>
+        <v>0.683002980165478</v>
       </c>
       <c r="U4" t="n">
-        <v>1.0545793281201</v>
+        <v>1.13947860563912</v>
       </c>
       <c r="V4" t="n">
-        <v>1.2571986655588</v>
+        <v>5.3696589331087</v>
       </c>
       <c r="W4" t="n">
-        <v>0.966343463295968</v>
+        <v>-0.702663532789551</v>
       </c>
       <c r="X4" t="n">
-        <v>1.07702133228078</v>
+        <v>1.60801100590035</v>
       </c>
     </row>
     <row r="5">
@@ -830,73 +830,73 @@
         <v>27</v>
       </c>
       <c r="B5" t="n">
-        <v>0.951099859358375</v>
+        <v>-1.00927357411425</v>
       </c>
       <c r="C5" t="n">
-        <v>1.16306231060317</v>
+        <v>3.36552162972092</v>
       </c>
       <c r="D5" t="n">
-        <v>0.960647119412049</v>
+        <v>-0.812223071785667</v>
       </c>
       <c r="E5" t="n">
-        <v>0.881909134913522</v>
+        <v>-2.43733428804534</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1500142152382</v>
+        <v>3.09621569988949</v>
       </c>
       <c r="G5" t="n">
-        <v>1.07318966650603</v>
+        <v>1.51059680674799</v>
       </c>
       <c r="H5" t="n">
-        <v>1.02039732787411</v>
+        <v>0.420990282149718</v>
       </c>
       <c r="I5" t="n">
-        <v>0.956177927820972</v>
+        <v>-0.904464871325361</v>
       </c>
       <c r="J5" t="n">
-        <v>1.21306618606543</v>
+        <v>4.39757571883329</v>
       </c>
       <c r="K5" t="n">
-        <v>0.771917821450355</v>
+        <v>-4.70749802589754</v>
       </c>
       <c r="L5" t="n">
-        <v>0.805911962315303</v>
+        <v>-4.00587656633667</v>
       </c>
       <c r="M5" t="n">
-        <v>1.1295938757901</v>
+        <v>2.67475047077174</v>
       </c>
       <c r="N5" t="n">
-        <v>1.01075741516882</v>
+        <v>0.222027477082963</v>
       </c>
       <c r="O5" t="n">
-        <v>1.33155514569579</v>
+        <v>6.84312647206405</v>
       </c>
       <c r="P5" t="n">
-        <v>1.26017303687984</v>
+        <v>5.36983671978147</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.0140787512356</v>
+        <v>0.290578133154177</v>
       </c>
       <c r="R5" t="n">
-        <v>0.989993086854488</v>
+        <v>-0.206537504058318</v>
       </c>
       <c r="S5" t="n">
-        <v>1.26002727303269</v>
+        <v>5.36682822947733</v>
       </c>
       <c r="T5" t="n">
-        <v>1.04812682032123</v>
+        <v>0.993312643256831</v>
       </c>
       <c r="U5" t="n">
-        <v>1.05369775391274</v>
+        <v>1.10829382701783</v>
       </c>
       <c r="V5" t="n">
-        <v>1.2703402297884</v>
+        <v>5.57968231512914</v>
       </c>
       <c r="W5" t="n">
-        <v>0.956657850010816</v>
+        <v>-0.894559525911521</v>
       </c>
       <c r="X5" t="n">
-        <v>1.09507739273611</v>
+        <v>1.96234813898585</v>
       </c>
     </row>
     <row r="6">
@@ -904,73 +904,73 @@
         <v>28</v>
       </c>
       <c r="B6" t="n">
-        <v>0.960227216578863</v>
+        <v>-0.828852558311626</v>
       </c>
       <c r="C6" t="n">
-        <v>1.16467574361273</v>
+        <v>3.43179178434718</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9429185122049</v>
+        <v>-1.18956062718153</v>
       </c>
       <c r="E6" t="n">
-        <v>0.834843598328167</v>
+        <v>-3.44180855027845</v>
       </c>
       <c r="F6" t="n">
-        <v>1.12176017716404</v>
+        <v>2.53744459557374</v>
       </c>
       <c r="G6" t="n">
-        <v>1.06948781099796</v>
+        <v>1.4481045821532</v>
       </c>
       <c r="H6" t="n">
-        <v>1.02416190929623</v>
+        <v>0.503526748978642</v>
       </c>
       <c r="I6" t="n">
-        <v>0.937946300214876</v>
+        <v>-1.29317999384142</v>
       </c>
       <c r="J6" t="n">
-        <v>1.21715234305344</v>
+        <v>4.52538795631673</v>
       </c>
       <c r="K6" t="n">
-        <v>0.810239241965978</v>
+        <v>-3.9545557598583</v>
       </c>
       <c r="L6" t="n">
-        <v>0.790099912516926</v>
+        <v>-4.37425318359094</v>
       </c>
       <c r="M6" t="n">
-        <v>1.12525838637037</v>
+        <v>2.61034619814646</v>
       </c>
       <c r="N6" t="n">
-        <v>1.00213621106897</v>
+        <v>0.0445179808227575</v>
       </c>
       <c r="O6" t="n">
-        <v>1.31004689038617</v>
+        <v>6.46128171549007</v>
       </c>
       <c r="P6" t="n">
-        <v>1.2550926030681</v>
+        <v>5.31605129117021</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.00099617431436</v>
+        <v>0.0207599659354373</v>
       </c>
       <c r="R6" t="n">
-        <v>0.968771932505211</v>
+        <v>-0.650783309785377</v>
       </c>
       <c r="S6" t="n">
-        <v>1.25192561000358</v>
+        <v>5.25005213099349</v>
       </c>
       <c r="T6" t="n">
-        <v>1.0316205915241</v>
+        <v>0.65896338967694</v>
       </c>
       <c r="U6" t="n">
-        <v>1.04022584437833</v>
+        <v>0.838294209137673</v>
       </c>
       <c r="V6" t="n">
-        <v>1.25880919805125</v>
+        <v>5.3935039860791</v>
       </c>
       <c r="W6" t="n">
-        <v>0.957213997063082</v>
+        <v>-0.891647125087724</v>
       </c>
       <c r="X6" t="n">
-        <v>1.06542641025036</v>
+        <v>1.36346624129759</v>
       </c>
     </row>
     <row r="7">
@@ -978,73 +978,73 @@
         <v>29</v>
       </c>
       <c r="B7" t="n">
-        <v>0.910976573014892</v>
+        <v>-1.86571909107103</v>
       </c>
       <c r="C7" t="n">
-        <v>1.12471157465436</v>
+        <v>2.6136577032593</v>
       </c>
       <c r="D7" t="n">
-        <v>0.90681031384675</v>
+        <v>-1.95303396460036</v>
       </c>
       <c r="E7" t="n">
-        <v>0.843820127955362</v>
+        <v>-3.27315829981986</v>
       </c>
       <c r="F7" t="n">
-        <v>1.10804856872339</v>
+        <v>2.2644407686513</v>
       </c>
       <c r="G7" t="n">
-        <v>1.02094477226452</v>
+        <v>0.438952563335833</v>
       </c>
       <c r="H7" t="n">
-        <v>0.942207484209394</v>
+        <v>-1.21119354402741</v>
       </c>
       <c r="I7" t="n">
-        <v>0.927290602820339</v>
+        <v>-1.52381586524469</v>
       </c>
       <c r="J7" t="n">
-        <v>1.20339336500755</v>
+        <v>4.26264071091359</v>
       </c>
       <c r="K7" t="n">
-        <v>0.774191343430905</v>
+        <v>-4.73241185784208</v>
       </c>
       <c r="L7" t="n">
-        <v>0.73466864440177</v>
+        <v>-5.56071353759707</v>
       </c>
       <c r="M7" t="n">
-        <v>1.1197452398184</v>
+        <v>2.50957514847689</v>
       </c>
       <c r="N7" t="n">
-        <v>1.00391444403436</v>
+        <v>0.0820374278228387</v>
       </c>
       <c r="O7" t="n">
-        <v>1.30252123693475</v>
+        <v>6.34012491226609</v>
       </c>
       <c r="P7" t="n">
-        <v>1.24334108932223</v>
+        <v>5.09984990879377</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.983332753435304</v>
+        <v>-0.349305808195227</v>
       </c>
       <c r="R7" t="n">
-        <v>0.954961033159914</v>
+        <v>-0.943909520464983</v>
       </c>
       <c r="S7" t="n">
-        <v>1.24518042592346</v>
+        <v>5.13839802503718</v>
       </c>
       <c r="T7" t="n">
-        <v>1.01076180144664</v>
+        <v>0.225541737644699</v>
       </c>
       <c r="U7" t="n">
-        <v>1.02193268606528</v>
+        <v>0.459656884668265</v>
       </c>
       <c r="V7" t="n">
-        <v>1.25286204425161</v>
+        <v>5.29938645752652</v>
       </c>
       <c r="W7" t="n">
-        <v>0.950302764356552</v>
+        <v>-1.04153574461862</v>
       </c>
       <c r="X7" t="n">
-        <v>1.0823934437726</v>
+        <v>1.72677042697241</v>
       </c>
     </row>
     <row r="8">
@@ -1052,73 +1052,73 @@
         <v>30</v>
       </c>
       <c r="B8" t="n">
-        <v>0.882821361427627</v>
+        <v>-2.42878761543349</v>
       </c>
       <c r="C8" t="n">
-        <v>1.12228549422289</v>
+        <v>2.53463854448421</v>
       </c>
       <c r="D8" t="n">
-        <v>0.894681360631673</v>
+        <v>-2.18296278305121</v>
       </c>
       <c r="E8" t="n">
-        <v>0.85660196564067</v>
+        <v>-2.97224284368467</v>
       </c>
       <c r="F8" t="n">
-        <v>1.14679726233718</v>
+        <v>3.04269939545228</v>
       </c>
       <c r="G8" t="n">
-        <v>1.03296598866977</v>
+        <v>0.683293354378846</v>
       </c>
       <c r="H8" t="n">
-        <v>0.982528898060146</v>
+        <v>-0.362127402540913</v>
       </c>
       <c r="I8" t="n">
-        <v>0.953665500099286</v>
+        <v>-0.960385449918447</v>
       </c>
       <c r="J8" t="n">
-        <v>1.2154597144691</v>
+        <v>4.46588126046689</v>
       </c>
       <c r="K8" t="n">
-        <v>0.781918363938614</v>
+        <v>-4.52022641048376</v>
       </c>
       <c r="L8" t="n">
-        <v>0.749608880097057</v>
+        <v>-5.18991224376773</v>
       </c>
       <c r="M8" t="n">
-        <v>1.11521113936419</v>
+        <v>2.38800682323081</v>
       </c>
       <c r="N8" t="n">
-        <v>0.987187700817481</v>
+        <v>-0.265563365122318</v>
       </c>
       <c r="O8" t="n">
-        <v>1.30909543406334</v>
+        <v>6.40668957573187</v>
       </c>
       <c r="P8" t="n">
-        <v>1.24942581718806</v>
+        <v>5.16990420042795</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.946717180397563</v>
+        <v>-1.10440481253626</v>
       </c>
       <c r="R8" t="n">
-        <v>0.971209704016976</v>
+        <v>-0.596742846479183</v>
       </c>
       <c r="S8" t="n">
-        <v>1.24599950376422</v>
+        <v>5.0988862426176</v>
       </c>
       <c r="T8" t="n">
-        <v>1.00068267047444</v>
+        <v>0.0141498622441042</v>
       </c>
       <c r="U8" t="n">
-        <v>1.01807820995948</v>
+        <v>0.374711065034985</v>
       </c>
       <c r="V8" t="n">
-        <v>1.26294572773942</v>
+        <v>5.45013438324095</v>
       </c>
       <c r="W8" t="n">
-        <v>0.958606549218001</v>
+        <v>-0.857971229604971</v>
       </c>
       <c r="X8" t="n">
-        <v>1.06132358190384</v>
+        <v>1.27106747506781</v>
       </c>
     </row>
     <row r="9">
@@ -1126,73 +1126,73 @@
         <v>31</v>
       </c>
       <c r="B9" t="n">
-        <v>0.909167271411014</v>
+        <v>-1.85625845559378</v>
       </c>
       <c r="C9" t="n">
-        <v>1.15655611343031</v>
+        <v>3.19938213730098</v>
       </c>
       <c r="D9" t="n">
-        <v>0.922746766588402</v>
+        <v>-1.57874777043335</v>
       </c>
       <c r="E9" t="n">
-        <v>0.874437051519632</v>
+        <v>-2.56600554058697</v>
       </c>
       <c r="F9" t="n">
-        <v>1.16381127376059</v>
+        <v>3.34764865883978</v>
       </c>
       <c r="G9" t="n">
-        <v>1.03794663417074</v>
+        <v>0.775477756035489</v>
       </c>
       <c r="H9" t="n">
-        <v>0.984815011867599</v>
+        <v>-0.310320553579398</v>
       </c>
       <c r="I9" t="n">
-        <v>0.95409980338417</v>
+        <v>-0.938016829452417</v>
       </c>
       <c r="J9" t="n">
-        <v>1.21985522731583</v>
+        <v>4.49296339602638</v>
       </c>
       <c r="K9" t="n">
-        <v>0.774951377999539</v>
+        <v>-4.59909565635069</v>
       </c>
       <c r="L9" t="n">
-        <v>0.744789724340071</v>
+        <v>-5.21547948087964</v>
       </c>
       <c r="M9" t="n">
-        <v>1.15378757884085</v>
+        <v>3.142804339616</v>
       </c>
       <c r="N9" t="n">
-        <v>1.02509886907184</v>
+        <v>0.512920713317605</v>
       </c>
       <c r="O9" t="n">
-        <v>1.33688043750923</v>
+        <v>6.88449164045562</v>
       </c>
       <c r="P9" t="n">
-        <v>1.25813865752134</v>
+        <v>5.27532391884706</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.993243867864422</v>
+        <v>-0.138068376879038</v>
       </c>
       <c r="R9" t="n">
-        <v>0.99120500420997</v>
+        <v>-0.1797346127961</v>
       </c>
       <c r="S9" t="n">
-        <v>1.2692820753746</v>
+        <v>5.50305090597656</v>
       </c>
       <c r="T9" t="n">
-        <v>1.05325241490959</v>
+        <v>1.08826682840284</v>
       </c>
       <c r="U9" t="n">
-        <v>1.02872606850072</v>
+        <v>0.587046193357446</v>
       </c>
       <c r="V9" t="n">
-        <v>1.27623680943914</v>
+        <v>5.64517791365595</v>
       </c>
       <c r="W9" t="n">
-        <v>0.994168163996838</v>
+        <v>-0.119179452832354</v>
       </c>
       <c r="X9" t="n">
-        <v>1.1123364067367</v>
+        <v>2.29570781496161</v>
       </c>
     </row>
     <row r="10">
@@ -1200,73 +1200,73 @@
         <v>32</v>
       </c>
       <c r="B10" t="n">
-        <v>0.904943734951395</v>
+        <v>-1.9775094277565</v>
       </c>
       <c r="C10" t="n">
-        <v>1.13319734373038</v>
+        <v>2.77097993324548</v>
       </c>
       <c r="D10" t="n">
-        <v>0.915441039895415</v>
+        <v>-1.75912803561764</v>
       </c>
       <c r="E10" t="n">
-        <v>0.854459677184308</v>
+        <v>-3.02775793199524</v>
       </c>
       <c r="F10" t="n">
-        <v>1.1021541422963</v>
+        <v>2.1251705962991</v>
       </c>
       <c r="G10" t="n">
-        <v>1.02459490020226</v>
+        <v>0.511661666906716</v>
       </c>
       <c r="H10" t="n">
-        <v>0.945456145325136</v>
+        <v>-1.13470676331089</v>
       </c>
       <c r="I10" t="n">
-        <v>0.930969827996261</v>
+        <v>-1.43607384392018</v>
       </c>
       <c r="J10" t="n">
-        <v>1.19110365754597</v>
+        <v>3.97563784231026</v>
       </c>
       <c r="K10" t="n">
-        <v>0.737648342421592</v>
+        <v>-5.4578504213643</v>
       </c>
       <c r="L10" t="n">
-        <v>0.738918979548617</v>
+        <v>-5.43141663610391</v>
       </c>
       <c r="M10" t="n">
-        <v>1.12095869923008</v>
+        <v>2.5163724660794</v>
       </c>
       <c r="N10" t="n">
-        <v>1.01459287095762</v>
+        <v>0.303583776218906</v>
       </c>
       <c r="O10" t="n">
-        <v>1.31084869701852</v>
+        <v>6.46676185568231</v>
       </c>
       <c r="P10" t="n">
-        <v>1.22759080345658</v>
+        <v>4.73470064572732</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.991088506741645</v>
+        <v>-0.185390851668473</v>
       </c>
       <c r="R10" t="n">
-        <v>0.935255319896978</v>
+        <v>-1.3469203238244</v>
       </c>
       <c r="S10" t="n">
-        <v>1.23508258861237</v>
+        <v>4.89055650403112</v>
       </c>
       <c r="T10" t="n">
-        <v>1.01619360307482</v>
+        <v>0.336884714894185</v>
       </c>
       <c r="U10" t="n">
-        <v>1.01895561661093</v>
+        <v>0.394344449972807</v>
       </c>
       <c r="V10" t="n">
-        <v>1.27123098860377</v>
+        <v>5.64257218384729</v>
       </c>
       <c r="W10" t="n">
-        <v>0.975482092505249</v>
+        <v>-0.510059943917846</v>
       </c>
       <c r="X10" t="n">
-        <v>1.10076190203434</v>
+        <v>2.09620703201106</v>
       </c>
     </row>
     <row r="11">
@@ -1274,73 +1274,73 @@
         <v>33</v>
       </c>
       <c r="B11" t="n">
-        <v>0.891296886001386</v>
+        <v>-2.26079061761116</v>
       </c>
       <c r="C11" t="n">
-        <v>1.10463692738572</v>
+        <v>2.17622269489268</v>
       </c>
       <c r="D11" t="n">
-        <v>0.869460113059458</v>
+        <v>-2.71494845697762</v>
       </c>
       <c r="E11" t="n">
-        <v>0.827833930331754</v>
+        <v>-3.58068339221566</v>
       </c>
       <c r="F11" t="n">
-        <v>1.14372278660943</v>
+        <v>2.98912437326928</v>
       </c>
       <c r="G11" t="n">
-        <v>1.01668305497575</v>
+        <v>0.346971607112837</v>
       </c>
       <c r="H11" t="n">
-        <v>0.990834999929795</v>
+        <v>-0.190612259455498</v>
       </c>
       <c r="I11" t="n">
-        <v>0.933996902526592</v>
+        <v>-1.37272225249277</v>
       </c>
       <c r="J11" t="n">
-        <v>1.19917738570956</v>
+        <v>4.14246058174786</v>
       </c>
       <c r="K11" t="n">
-        <v>0.804584498389743</v>
+        <v>-4.0642214958247</v>
       </c>
       <c r="L11" t="n">
-        <v>0.747034216353794</v>
+        <v>-5.26114339513119</v>
       </c>
       <c r="M11" t="n">
-        <v>1.10577059924584</v>
+        <v>2.19980062758041</v>
       </c>
       <c r="N11" t="n">
-        <v>0.972658996169779</v>
+        <v>-0.568633985372511</v>
       </c>
       <c r="O11" t="n">
-        <v>1.30092462098498</v>
+        <v>6.25858390533067</v>
       </c>
       <c r="P11" t="n">
-        <v>1.23523345651579</v>
+        <v>4.89234918740154</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.92829143575518</v>
+        <v>-1.49138367139256</v>
       </c>
       <c r="R11" t="n">
-        <v>0.920215817673225</v>
+        <v>-1.65933913209194</v>
       </c>
       <c r="S11" t="n">
-        <v>1.23644471754025</v>
+        <v>4.91754080757562</v>
       </c>
       <c r="T11" t="n">
-        <v>0.962074283864442</v>
+        <v>-0.788773201166506</v>
       </c>
       <c r="U11" t="n">
-        <v>0.999695676209198</v>
+        <v>-0.00632927931549819</v>
       </c>
       <c r="V11" t="n">
-        <v>1.24665582644496</v>
+        <v>5.12990987740256</v>
       </c>
       <c r="W11" t="n">
-        <v>0.932900703694004</v>
+        <v>-1.39552082692719</v>
       </c>
       <c r="X11" t="n">
-        <v>1.05490453736238</v>
+        <v>1.14189610920197</v>
       </c>
     </row>
     <row r="12">
@@ -1348,73 +1348,73 @@
         <v>34</v>
       </c>
       <c r="B12" t="n">
-        <v>0.883158049423952</v>
+        <v>-2.43581736785159</v>
       </c>
       <c r="C12" t="n">
-        <v>1.11317537571883</v>
+        <v>2.35937986681958</v>
       </c>
       <c r="D12" t="n">
-        <v>0.878843140109701</v>
+        <v>-2.52577077068797</v>
       </c>
       <c r="E12" t="n">
-        <v>0.845123167897937</v>
+        <v>-3.22873484781906</v>
       </c>
       <c r="F12" t="n">
-        <v>1.09535228918374</v>
+        <v>1.98781996460251</v>
       </c>
       <c r="G12" t="n">
-        <v>1.01883475329199</v>
+        <v>0.392650233598875</v>
       </c>
       <c r="H12" t="n">
-        <v>0.939284123393476</v>
+        <v>-1.2657507514499</v>
       </c>
       <c r="I12" t="n">
-        <v>0.941104580466182</v>
+        <v>-1.22779947681554</v>
       </c>
       <c r="J12" t="n">
-        <v>1.1982268296323</v>
+        <v>4.13245715269228</v>
       </c>
       <c r="K12" t="n">
-        <v>0.779517378841952</v>
+        <v>-4.59642615754403</v>
       </c>
       <c r="L12" t="n">
-        <v>0.716597167376015</v>
+        <v>-5.90813092729513</v>
       </c>
       <c r="M12" t="n">
-        <v>1.1100400465004</v>
+        <v>2.29401730374574</v>
       </c>
       <c r="N12" t="n">
-        <v>0.990802620383602</v>
+        <v>-0.191738813824106</v>
       </c>
       <c r="O12" t="n">
-        <v>1.29634910787442</v>
+        <v>6.17802339270271</v>
       </c>
       <c r="P12" t="n">
-        <v>1.23240021896649</v>
+        <v>4.84487366789247</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.94518044043386</v>
+        <v>-1.14282956276281</v>
       </c>
       <c r="R12" t="n">
-        <v>0.951594682452022</v>
+        <v>-1.00911113344514</v>
       </c>
       <c r="S12" t="n">
-        <v>1.23279090601731</v>
+        <v>4.85301836505902</v>
       </c>
       <c r="T12" t="n">
-        <v>0.996643455023104</v>
+        <v>-0.0699742730277113</v>
       </c>
       <c r="U12" t="n">
-        <v>1.00252641971121</v>
+        <v>0.0526685576603285</v>
       </c>
       <c r="V12" t="n">
-        <v>1.24141344861486</v>
+        <v>5.03277348649106</v>
       </c>
       <c r="W12" t="n">
-        <v>0.928210416436551</v>
+        <v>-1.49660557370503</v>
       </c>
       <c r="X12" t="n">
-        <v>1.05656477934051</v>
+        <v>1.1792123569233</v>
       </c>
     </row>
     <row r="13">
@@ -1422,73 +1422,73 @@
         <v>35</v>
       </c>
       <c r="B13" t="n">
-        <v>0.889594870681349</v>
+        <v>-2.27086798821491</v>
       </c>
       <c r="C13" t="n">
-        <v>1.11375623770203</v>
+        <v>2.33979526360348</v>
       </c>
       <c r="D13" t="n">
-        <v>0.875034322664441</v>
+        <v>-2.57035663141944</v>
       </c>
       <c r="E13" t="n">
-        <v>0.832445239785091</v>
+        <v>-3.4463502157303</v>
       </c>
       <c r="F13" t="n">
-        <v>1.1111951391455</v>
+        <v>2.28711730595267</v>
       </c>
       <c r="G13" t="n">
-        <v>1.0168378266528</v>
+        <v>0.346328850597221</v>
       </c>
       <c r="H13" t="n">
-        <v>0.938222805401775</v>
+        <v>-1.27066427511655</v>
       </c>
       <c r="I13" t="n">
-        <v>0.922069216259248</v>
+        <v>-1.60291938595173</v>
       </c>
       <c r="J13" t="n">
-        <v>1.20429267535878</v>
+        <v>4.20199405192554</v>
       </c>
       <c r="K13" t="n">
-        <v>0.815876659906988</v>
+        <v>-3.78714106383276</v>
       </c>
       <c r="L13" t="n">
-        <v>0.734286130510518</v>
+        <v>-5.46533593114906</v>
       </c>
       <c r="M13" t="n">
-        <v>1.09991185933273</v>
+        <v>2.05503715635253</v>
       </c>
       <c r="N13" t="n">
-        <v>0.995119919245382</v>
+        <v>-0.100375944794932</v>
       </c>
       <c r="O13" t="n">
-        <v>1.31679218594048</v>
+        <v>6.51594032277745</v>
       </c>
       <c r="P13" t="n">
-        <v>1.23850477726761</v>
+        <v>4.90568569663239</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.954620576064563</v>
+        <v>-0.933386716492059</v>
       </c>
       <c r="R13" t="n">
-        <v>0.948675325896787</v>
+        <v>-1.05567159918955</v>
       </c>
       <c r="S13" t="n">
-        <v>1.24660572304488</v>
+        <v>5.07231000614947</v>
       </c>
       <c r="T13" t="n">
-        <v>0.987896223234486</v>
+        <v>-0.248956541810443</v>
       </c>
       <c r="U13" t="n">
-        <v>1.01701730188708</v>
+        <v>0.350020387092893</v>
       </c>
       <c r="V13" t="n">
-        <v>1.27467375604538</v>
+        <v>5.64962736473916</v>
       </c>
       <c r="W13" t="n">
-        <v>0.950601227301488</v>
+        <v>-1.01605869464985</v>
       </c>
       <c r="X13" t="n">
-        <v>1.0859555023801</v>
+        <v>1.76797581752325</v>
       </c>
     </row>
     <row r="14">
@@ -1496,73 +1496,73 @@
         <v>36</v>
       </c>
       <c r="B14" t="n">
-        <v>0.932389862164701</v>
+        <v>-1.39454921015205</v>
       </c>
       <c r="C14" t="n">
-        <v>1.12700492227071</v>
+        <v>2.6196458062177</v>
       </c>
       <c r="D14" t="n">
-        <v>0.929178732753145</v>
+        <v>-1.46078303436774</v>
       </c>
       <c r="E14" t="n">
-        <v>0.835592102742072</v>
+        <v>-3.39113201961406</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1023206630775</v>
+        <v>2.11050005880132</v>
       </c>
       <c r="G14" t="n">
-        <v>1.03365405475463</v>
+        <v>0.69415973667761</v>
       </c>
       <c r="H14" t="n">
-        <v>1.00460078513981</v>
+        <v>0.094897325877794</v>
       </c>
       <c r="I14" t="n">
-        <v>0.920465510672136</v>
+        <v>-1.64050485360956</v>
       </c>
       <c r="J14" t="n">
-        <v>1.2137581369571</v>
+        <v>4.40904649215887</v>
       </c>
       <c r="K14" t="n">
-        <v>0.775318951053878</v>
+        <v>-4.63434611104076</v>
       </c>
       <c r="L14" t="n">
-        <v>0.751127751278993</v>
+        <v>-5.13332185075717</v>
       </c>
       <c r="M14" t="n">
-        <v>1.13599264302877</v>
+        <v>2.80502952655187</v>
       </c>
       <c r="N14" t="n">
-        <v>1.02983782435665</v>
+        <v>0.615444898079969</v>
       </c>
       <c r="O14" t="n">
-        <v>1.32463567428281</v>
+        <v>6.69604348775502</v>
       </c>
       <c r="P14" t="n">
-        <v>1.25102208194662</v>
+        <v>5.17766502654013</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.995913930098293</v>
+        <v>-0.0842806380299407</v>
       </c>
       <c r="R14" t="n">
-        <v>0.936706406841803</v>
+        <v>-1.30551472268061</v>
       </c>
       <c r="S14" t="n">
-        <v>1.25046036521462</v>
+        <v>5.16607887023238</v>
       </c>
       <c r="T14" t="n">
-        <v>1.03928246022237</v>
+        <v>0.81025310153017</v>
       </c>
       <c r="U14" t="n">
-        <v>1.03810460907381</v>
+        <v>0.785958351637724</v>
       </c>
       <c r="V14" t="n">
-        <v>1.27162981150781</v>
+        <v>5.60272691670507</v>
       </c>
       <c r="W14" t="n">
-        <v>0.969046044458388</v>
+        <v>-0.638466591456933</v>
       </c>
       <c r="X14" t="n">
-        <v>1.11083495389594</v>
+        <v>2.28611865559795</v>
       </c>
     </row>
     <row r="15">
@@ -1570,73 +1570,73 @@
         <v>37</v>
       </c>
       <c r="B15" t="n">
-        <v>0.898435584719669</v>
+        <v>-2.12002538249201</v>
       </c>
       <c r="C15" t="n">
-        <v>1.13854683023891</v>
+        <v>2.8919853076452</v>
       </c>
       <c r="D15" t="n">
-        <v>0.906094634647757</v>
+        <v>-1.96015265336239</v>
       </c>
       <c r="E15" t="n">
-        <v>0.836229934832691</v>
+        <v>-3.41848760797527</v>
       </c>
       <c r="F15" t="n">
-        <v>1.09423077133429</v>
+        <v>1.9669450810021</v>
       </c>
       <c r="G15" t="n">
-        <v>1.03436187859921</v>
+        <v>0.717259628969196</v>
       </c>
       <c r="H15" t="n">
-        <v>1.01480772168669</v>
+        <v>0.309091976220276</v>
       </c>
       <c r="I15" t="n">
-        <v>0.931368375487297</v>
+        <v>-1.43259610767206</v>
       </c>
       <c r="J15" t="n">
-        <v>1.19306482187991</v>
+        <v>4.02997764248423</v>
       </c>
       <c r="K15" t="n">
-        <v>0.759422945712937</v>
+        <v>-5.02173384374818</v>
       </c>
       <c r="L15" t="n">
-        <v>0.756743546499397</v>
+        <v>-5.07766282563474</v>
       </c>
       <c r="M15" t="n">
-        <v>1.09154050392095</v>
+        <v>1.91078923954683</v>
       </c>
       <c r="N15" t="n">
-        <v>0.972402938266376</v>
+        <v>-0.57605285469321</v>
       </c>
       <c r="O15" t="n">
-        <v>1.29249402325886</v>
+        <v>6.10543320536469</v>
       </c>
       <c r="P15" t="n">
-        <v>1.22605704113972</v>
+        <v>4.71864740996595</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.968257527105256</v>
+        <v>-0.662582933738947</v>
       </c>
       <c r="R15" t="n">
-        <v>0.935912396603155</v>
+        <v>-1.33774556304372</v>
       </c>
       <c r="S15" t="n">
-        <v>1.22775432337364</v>
+        <v>4.75407597426426</v>
       </c>
       <c r="T15" t="n">
-        <v>0.999985429807266</v>
+        <v>-0.000304133867552792</v>
       </c>
       <c r="U15" t="n">
-        <v>0.99998766050503</v>
+        <v>-0.000257570946198993</v>
       </c>
       <c r="V15" t="n">
-        <v>1.23920446031578</v>
+        <v>4.99308272562822</v>
       </c>
       <c r="W15" t="n">
-        <v>0.930435876902414</v>
+        <v>-1.45206080565347</v>
       </c>
       <c r="X15" t="n">
-        <v>1.04366310899972</v>
+        <v>0.911410744623712</v>
       </c>
     </row>
     <row r="16">
@@ -1644,73 +1644,73 @@
         <v>38</v>
       </c>
       <c r="B16" t="n">
-        <v>0.946127317224263</v>
+        <v>-1.13036473061501</v>
       </c>
       <c r="C16" t="n">
-        <v>1.13940364449285</v>
+        <v>2.9249882303037</v>
       </c>
       <c r="D16" t="n">
-        <v>0.90241291044503</v>
+        <v>-2.04758698681307</v>
       </c>
       <c r="E16" t="n">
-        <v>0.825800076176086</v>
+        <v>-3.65508899540194</v>
       </c>
       <c r="F16" t="n">
-        <v>1.11503191776596</v>
+        <v>2.41361699544346</v>
       </c>
       <c r="G16" t="n">
-        <v>1.04201466459421</v>
+        <v>0.881558010088659</v>
       </c>
       <c r="H16" t="n">
-        <v>0.976468830716458</v>
+        <v>-0.49373453219275</v>
       </c>
       <c r="I16" t="n">
-        <v>0.931962157139206</v>
+        <v>-1.42758024947674</v>
       </c>
       <c r="J16" t="n">
-        <v>1.18440506551071</v>
+        <v>3.86921481277962</v>
       </c>
       <c r="K16" t="n">
-        <v>0.754118076042208</v>
+        <v>-5.15913150073953</v>
       </c>
       <c r="L16" t="n">
-        <v>0.775119441077806</v>
+        <v>-4.71847770167342</v>
       </c>
       <c r="M16" t="n">
-        <v>1.07850922220791</v>
+        <v>1.64729230547642</v>
       </c>
       <c r="N16" t="n">
-        <v>0.976664489804646</v>
+        <v>-0.489629183783938</v>
       </c>
       <c r="O16" t="n">
-        <v>1.29237700332631</v>
+        <v>6.13469824732419</v>
       </c>
       <c r="P16" t="n">
-        <v>1.22180390922868</v>
+        <v>4.653922975181</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.966370823171694</v>
+        <v>-0.705612444892995</v>
       </c>
       <c r="R16" t="n">
-        <v>0.917668334082932</v>
+        <v>-1.72749539414708</v>
       </c>
       <c r="S16" t="n">
-        <v>1.22132651004199</v>
+        <v>4.64390611366128</v>
       </c>
       <c r="T16" t="n">
-        <v>0.971297807435231</v>
+        <v>-0.602233720225048</v>
       </c>
       <c r="U16" t="n">
-        <v>1.00612169684456</v>
+        <v>0.128446363686993</v>
       </c>
       <c r="V16" t="n">
-        <v>1.23977897961218</v>
+        <v>5.03107860480509</v>
       </c>
       <c r="W16" t="n">
-        <v>0.920874961022716</v>
+        <v>-1.66021346552919</v>
       </c>
       <c r="X16" t="n">
-        <v>1.0488024409631</v>
+        <v>1.02398015451084</v>
       </c>
     </row>
     <row r="17">
@@ -1718,73 +1718,73 @@
         <v>39</v>
       </c>
       <c r="B17" t="n">
-        <v>0.893770426116347</v>
+        <v>-2.21962274601345</v>
       </c>
       <c r="C17" t="n">
-        <v>1.14023789151557</v>
+        <v>2.93021239266056</v>
       </c>
       <c r="D17" t="n">
-        <v>0.874305059384755</v>
+        <v>-2.62634348466816</v>
       </c>
       <c r="E17" t="n">
-        <v>0.828207274746978</v>
+        <v>-3.58953751418488</v>
       </c>
       <c r="F17" t="n">
-        <v>1.11940373947665</v>
+        <v>2.49489145453697</v>
       </c>
       <c r="G17" t="n">
-        <v>1.01744367363932</v>
+        <v>0.364478302683168</v>
       </c>
       <c r="H17" t="n">
-        <v>0.949217205088752</v>
+        <v>-1.06108536982928</v>
       </c>
       <c r="I17" t="n">
-        <v>0.910505898617878</v>
+        <v>-1.86994201143415</v>
       </c>
       <c r="J17" t="n">
-        <v>1.17774669447196</v>
+        <v>3.71394322367107</v>
       </c>
       <c r="K17" t="n">
-        <v>0.736311318109988</v>
+        <v>-5.50966529179912</v>
       </c>
       <c r="L17" t="n">
-        <v>0.754360299479197</v>
+        <v>-5.132539335958</v>
       </c>
       <c r="M17" t="n">
-        <v>1.08673381699837</v>
+        <v>1.81226701774227</v>
       </c>
       <c r="N17" t="n">
-        <v>0.968611746788413</v>
+        <v>-0.65584449074768</v>
       </c>
       <c r="O17" t="n">
-        <v>1.29920783255745</v>
+        <v>6.25182316609197</v>
       </c>
       <c r="P17" t="n">
-        <v>1.21212312739773</v>
+        <v>4.43222448621694</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.958286042391736</v>
+        <v>-0.871595787769521</v>
       </c>
       <c r="R17" t="n">
-        <v>0.916048767644299</v>
+        <v>-1.75412606941886</v>
       </c>
       <c r="S17" t="n">
-        <v>1.22084529948631</v>
+        <v>4.61447064286299</v>
       </c>
       <c r="T17" t="n">
-        <v>0.977765450252273</v>
+        <v>-0.464581665567765</v>
       </c>
       <c r="U17" t="n">
-        <v>0.990051708763466</v>
+        <v>-0.207865406075726</v>
       </c>
       <c r="V17" t="n">
-        <v>1.21459716433065</v>
+        <v>4.48391845852631</v>
       </c>
       <c r="W17" t="n">
-        <v>0.923926712191292</v>
+        <v>-1.58951969598571</v>
       </c>
       <c r="X17" t="n">
-        <v>1.05334080540309</v>
+        <v>1.11453393471246</v>
       </c>
     </row>
     <row r="18">
@@ -1792,73 +1792,73 @@
         <v>40</v>
       </c>
       <c r="B18" t="n">
-        <v>0.904498832977043</v>
+        <v>-1.99945083836405</v>
       </c>
       <c r="C18" t="n">
-        <v>1.13846431387032</v>
+        <v>2.89894455828976</v>
       </c>
       <c r="D18" t="n">
-        <v>0.883550757819728</v>
+        <v>-2.43802816407712</v>
       </c>
       <c r="E18" t="n">
-        <v>0.841295606787601</v>
+        <v>-3.3226989988961</v>
       </c>
       <c r="F18" t="n">
-        <v>1.12855534848183</v>
+        <v>2.69148647404892</v>
       </c>
       <c r="G18" t="n">
-        <v>1.02536142669299</v>
+        <v>0.530977028282893</v>
       </c>
       <c r="H18" t="n">
-        <v>0.986615324009108</v>
+        <v>-0.280226959161529</v>
       </c>
       <c r="I18" t="n">
-        <v>0.9185365570108</v>
+        <v>-1.70555140275536</v>
       </c>
       <c r="J18" t="n">
-        <v>1.19281031149717</v>
+        <v>4.03675421972156</v>
       </c>
       <c r="K18" t="n">
-        <v>0.715517529894936</v>
+        <v>-5.95603939808097</v>
       </c>
       <c r="L18" t="n">
-        <v>0.751127086895108</v>
+        <v>-5.21050339242514</v>
       </c>
       <c r="M18" t="n">
-        <v>1.10573708741585</v>
+        <v>2.21375418406112</v>
       </c>
       <c r="N18" t="n">
-        <v>0.954033652367286</v>
+        <v>-0.962369939297909</v>
       </c>
       <c r="O18" t="n">
-        <v>1.29433665021125</v>
+        <v>6.16235047561952</v>
       </c>
       <c r="P18" t="n">
-        <v>1.22442559667836</v>
+        <v>4.69866454428807</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.940748353394899</v>
+        <v>-1.24051630123578</v>
       </c>
       <c r="R18" t="n">
-        <v>0.938653261568379</v>
+        <v>-1.2843799862521</v>
       </c>
       <c r="S18" t="n">
-        <v>1.22037457710776</v>
+        <v>4.61385076944982</v>
       </c>
       <c r="T18" t="n">
-        <v>0.978994878845702</v>
+        <v>-0.439771663646826</v>
       </c>
       <c r="U18" t="n">
-        <v>1.00346004398732</v>
+        <v>0.072440872367218</v>
       </c>
       <c r="V18" t="n">
-        <v>1.2069823956264</v>
+        <v>4.33346667232153</v>
       </c>
       <c r="W18" t="n">
-        <v>0.882027325919346</v>
+        <v>-2.4699233469881</v>
       </c>
       <c r="X18" t="n">
-        <v>1.03914142064266</v>
+        <v>0.819480523205625</v>
       </c>
     </row>
     <row r="19">
@@ -1866,73 +1866,73 @@
         <v>41</v>
       </c>
       <c r="B19" t="n">
-        <v>0.926998935096022</v>
+        <v>-1.51173410282127</v>
       </c>
       <c r="C19" t="n">
-        <v>1.12260466049169</v>
+        <v>2.53894442052189</v>
       </c>
       <c r="D19" t="n">
-        <v>0.898123776206348</v>
+        <v>-2.10969198844006</v>
       </c>
       <c r="E19" t="n">
-        <v>0.843580093686068</v>
+        <v>-3.23920352457752</v>
       </c>
       <c r="F19" t="n">
-        <v>1.13569488522299</v>
+        <v>2.81002182419985</v>
       </c>
       <c r="G19" t="n">
-        <v>1.0322059462387</v>
+        <v>0.666933109903468</v>
       </c>
       <c r="H19" t="n">
-        <v>1.04806523413962</v>
+        <v>0.995353337715404</v>
       </c>
       <c r="I19" t="n">
-        <v>0.924401786783763</v>
+        <v>-1.56551684803041</v>
       </c>
       <c r="J19" t="n">
-        <v>1.19713553582056</v>
+        <v>4.08235842545415</v>
       </c>
       <c r="K19" t="n">
-        <v>0.747668035731763</v>
+        <v>-5.225387275075</v>
       </c>
       <c r="L19" t="n">
-        <v>0.764798977857232</v>
+        <v>-4.87063314294565</v>
       </c>
       <c r="M19" t="n">
-        <v>1.10489395280443</v>
+        <v>2.17218428036303</v>
       </c>
       <c r="N19" t="n">
-        <v>0.975458210908194</v>
+        <v>-0.508220798739438</v>
       </c>
       <c r="O19" t="n">
-        <v>1.31228666174883</v>
+        <v>6.46695218820278</v>
       </c>
       <c r="P19" t="n">
-        <v>1.22830613793205</v>
+        <v>4.72785123133846</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.979799684649565</v>
+        <v>-0.418315892284098</v>
       </c>
       <c r="R19" t="n">
-        <v>0.940926365706351</v>
+        <v>-1.22331951810246</v>
       </c>
       <c r="S19" t="n">
-        <v>1.23626875245632</v>
+        <v>4.89274411255593</v>
       </c>
       <c r="T19" t="n">
-        <v>0.992942686740058</v>
+        <v>-0.146145554772113</v>
       </c>
       <c r="U19" t="n">
-        <v>1.01298827810896</v>
+        <v>0.268966253849494</v>
       </c>
       <c r="V19" t="n">
-        <v>1.21247571815618</v>
+        <v>4.4000288157528</v>
       </c>
       <c r="W19" t="n">
-        <v>0.920430954677301</v>
+        <v>-1.64774636509036</v>
       </c>
       <c r="X19" t="n">
-        <v>1.0685934881532</v>
+        <v>1.42046030984687</v>
       </c>
     </row>
     <row r="20">
@@ -1940,73 +1940,73 @@
         <v>42</v>
       </c>
       <c r="B20" t="n">
-        <v>0.899938716171893</v>
+        <v>-2.09913902630422</v>
       </c>
       <c r="C20" t="n">
-        <v>1.11855304590581</v>
+        <v>2.48706908233985</v>
       </c>
       <c r="D20" t="n">
-        <v>0.896334531341836</v>
+        <v>-2.17474953963505</v>
       </c>
       <c r="E20" t="n">
-        <v>0.824384087773897</v>
+        <v>-3.68416435298902</v>
       </c>
       <c r="F20" t="n">
-        <v>1.11291856236173</v>
+        <v>2.36886587878339</v>
       </c>
       <c r="G20" t="n">
-        <v>1.01273101733082</v>
+        <v>0.267078077566844</v>
       </c>
       <c r="H20" t="n">
-        <v>0.988495775089589</v>
+        <v>-0.241341771291986</v>
       </c>
       <c r="I20" t="n">
-        <v>0.913479847679389</v>
+        <v>-1.81506594108843</v>
       </c>
       <c r="J20" t="n">
-        <v>1.18432726442794</v>
+        <v>3.86691574972485</v>
       </c>
       <c r="K20" t="n">
-        <v>0.702138350999036</v>
+        <v>-6.24870067559156</v>
       </c>
       <c r="L20" t="n">
-        <v>0.760407799285794</v>
+        <v>-5.02629308435904</v>
       </c>
       <c r="M20" t="n">
-        <v>1.09167353104182</v>
+        <v>1.92317627084996</v>
       </c>
       <c r="N20" t="n">
-        <v>0.960008883769908</v>
+        <v>-0.838954984110191</v>
       </c>
       <c r="O20" t="n">
-        <v>1.29149836458518</v>
+        <v>6.11520829830423</v>
       </c>
       <c r="P20" t="n">
-        <v>1.21702638525232</v>
+        <v>4.55289536164138</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.962597597965679</v>
+        <v>-0.784647555818272</v>
       </c>
       <c r="R20" t="n">
-        <v>0.93439256205217</v>
+        <v>-1.37634785546732</v>
       </c>
       <c r="S20" t="n">
-        <v>1.21749320636931</v>
+        <v>4.56268858422954</v>
       </c>
       <c r="T20" t="n">
-        <v>0.988991923347108</v>
+        <v>-0.230933308294645</v>
       </c>
       <c r="U20" t="n">
-        <v>1.00200042680214</v>
+        <v>0.0419660213119893</v>
       </c>
       <c r="V20" t="n">
-        <v>1.21314096541312</v>
+        <v>4.47138495016145</v>
       </c>
       <c r="W20" t="n">
-        <v>0.925753602408178</v>
+        <v>-1.5575805624804</v>
       </c>
       <c r="X20" t="n">
-        <v>1.04203696376378</v>
+        <v>0.881873865774745</v>
       </c>
     </row>
     <row r="21">
@@ -2014,73 +2014,73 @@
         <v>43</v>
       </c>
       <c r="B21" t="n">
-        <v>0.917200346487607</v>
+        <v>-1.71621213917592</v>
       </c>
       <c r="C21" t="n">
-        <v>1.13000919582748</v>
+        <v>2.69473784754695</v>
       </c>
       <c r="D21" t="n">
-        <v>0.924979504608931</v>
+        <v>-1.55497130018633</v>
       </c>
       <c r="E21" t="n">
-        <v>0.828857056812803</v>
+        <v>-3.54732881325644</v>
       </c>
       <c r="F21" t="n">
-        <v>1.12097662712723</v>
+        <v>2.50751720840508</v>
       </c>
       <c r="G21" t="n">
-        <v>1.03940795680066</v>
+        <v>0.816820010379554</v>
       </c>
       <c r="H21" t="n">
-        <v>0.973914514248268</v>
+        <v>-0.540681336265759</v>
       </c>
       <c r="I21" t="n">
-        <v>0.913270933805096</v>
+        <v>-1.79765820156249</v>
       </c>
       <c r="J21" t="n">
-        <v>1.19573086362625</v>
+        <v>4.05696968425697</v>
       </c>
       <c r="K21" t="n">
-        <v>0.716001968450176</v>
+        <v>-5.886508560992</v>
       </c>
       <c r="L21" t="n">
-        <v>0.758104068725016</v>
+        <v>-5.01384626699257</v>
       </c>
       <c r="M21" t="n">
-        <v>1.09855847210345</v>
+        <v>2.04284968677136</v>
       </c>
       <c r="N21" t="n">
-        <v>0.987208902599008</v>
+        <v>-0.265124740282623</v>
       </c>
       <c r="O21" t="n">
-        <v>1.31310771646731</v>
+        <v>6.48987333975277</v>
       </c>
       <c r="P21" t="n">
-        <v>1.23144650765245</v>
+        <v>4.79725806996947</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.992590303315561</v>
+        <v>-0.153582905942272</v>
       </c>
       <c r="R21" t="n">
-        <v>0.958245793560211</v>
+        <v>-0.865451398814095</v>
       </c>
       <c r="S21" t="n">
-        <v>1.23809673588596</v>
+        <v>4.93509925575328</v>
       </c>
       <c r="T21" t="n">
-        <v>1.02177114700982</v>
+        <v>0.451256801170523</v>
       </c>
       <c r="U21" t="n">
-        <v>1.03253676114845</v>
+        <v>0.674398769604556</v>
       </c>
       <c r="V21" t="n">
-        <v>1.23282849868333</v>
+        <v>4.82590299398573</v>
       </c>
       <c r="W21" t="n">
-        <v>0.938658755381735</v>
+        <v>-1.27143755052391</v>
       </c>
       <c r="X21" t="n">
-        <v>1.06707264464937</v>
+        <v>1.39023392092637</v>
       </c>
     </row>
     <row r="22">
@@ -2088,73 +2088,73 @@
         <v>44</v>
       </c>
       <c r="B22" t="n">
-        <v>0.894325540344786</v>
+        <v>-2.17735418198601</v>
       </c>
       <c r="C22" t="n">
-        <v>1.11902063064512</v>
+        <v>2.45234343968535</v>
       </c>
       <c r="D22" t="n">
-        <v>0.884605992089695</v>
+        <v>-2.3776192139463</v>
       </c>
       <c r="E22" t="n">
-        <v>0.833526758813441</v>
+        <v>-3.43007391822927</v>
       </c>
       <c r="F22" t="n">
-        <v>1.13599555390715</v>
+        <v>2.8021008008686</v>
       </c>
       <c r="G22" t="n">
-        <v>1.02526045007965</v>
+        <v>0.520475305000125</v>
       </c>
       <c r="H22" t="n">
-        <v>0.946508432072071</v>
+        <v>-1.10215930612633</v>
       </c>
       <c r="I22" t="n">
-        <v>0.913231011802343</v>
+        <v>-1.78781911859572</v>
       </c>
       <c r="J22" t="n">
-        <v>1.19015184785169</v>
+        <v>3.91795635845319</v>
       </c>
       <c r="K22" t="n">
-        <v>0.756357438325803</v>
+        <v>-5.02009806628731</v>
       </c>
       <c r="L22" t="n">
-        <v>0.760076524849496</v>
+        <v>-4.94346868372932</v>
       </c>
       <c r="M22" t="n">
-        <v>1.10044318117297</v>
+        <v>2.0695670580432</v>
       </c>
       <c r="N22" t="n">
-        <v>0.976212155250204</v>
+        <v>-0.490133220604054</v>
       </c>
       <c r="O22" t="n">
-        <v>1.31366446324733</v>
+        <v>6.46285425087833</v>
       </c>
       <c r="P22" t="n">
-        <v>1.22497286394214</v>
+        <v>4.63542096866186</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.97692964976201</v>
+        <v>-0.475349708287739</v>
       </c>
       <c r="R22" t="n">
-        <v>0.931690516217536</v>
+        <v>-1.40747291889006</v>
       </c>
       <c r="S22" t="n">
-        <v>1.23488117136703</v>
+        <v>4.83957526174623</v>
       </c>
       <c r="T22" t="n">
-        <v>0.991225310680745</v>
+        <v>-0.18079682211998</v>
       </c>
       <c r="U22" t="n">
-        <v>1.00760314570132</v>
+        <v>0.156657920400279</v>
       </c>
       <c r="V22" t="n">
-        <v>1.25014024873613</v>
+        <v>5.15397872338924</v>
       </c>
       <c r="W22" t="n">
-        <v>0.899972823096465</v>
+        <v>-2.06099555799735</v>
       </c>
       <c r="X22" t="n">
-        <v>1.06663472294475</v>
+        <v>1.37296555045195</v>
       </c>
     </row>
     <row r="23">
@@ -2162,73 +2162,73 @@
         <v>45</v>
       </c>
       <c r="B23" t="n">
-        <v>0.891625643960068</v>
+        <v>-2.2157561679949</v>
       </c>
       <c r="C23" t="n">
-        <v>1.13726269892412</v>
+        <v>2.80638965609793</v>
       </c>
       <c r="D23" t="n">
-        <v>0.875272312477128</v>
+        <v>-2.55010643704968</v>
       </c>
       <c r="E23" t="n">
-        <v>0.836319269109206</v>
+        <v>-3.34651666967745</v>
       </c>
       <c r="F23" t="n">
-        <v>1.13856023491053</v>
+        <v>2.83291828768708</v>
       </c>
       <c r="G23" t="n">
-        <v>1.02287710516943</v>
+        <v>0.467731377950295</v>
       </c>
       <c r="H23" t="n">
-        <v>0.984759286747701</v>
+        <v>-0.311602353429252</v>
       </c>
       <c r="I23" t="n">
-        <v>0.916074785878859</v>
+        <v>-1.71588388281351</v>
       </c>
       <c r="J23" t="n">
-        <v>1.20154499214304</v>
+        <v>4.12066632538861</v>
       </c>
       <c r="K23" t="n">
-        <v>0.765627043893647</v>
+        <v>-4.79184690991385</v>
       </c>
       <c r="L23" t="n">
-        <v>0.760100468564497</v>
+        <v>-4.90483990771253</v>
       </c>
       <c r="M23" t="n">
-        <v>1.09857505155433</v>
+        <v>2.01540554862851</v>
       </c>
       <c r="N23" t="n">
-        <v>0.9684663533603</v>
+        <v>-0.644717759758069</v>
       </c>
       <c r="O23" t="n">
-        <v>1.32340027893767</v>
+        <v>6.61204540420406</v>
       </c>
       <c r="P23" t="n">
-        <v>1.2369584804008</v>
+        <v>4.84470896706714</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.962576722619507</v>
+        <v>-0.765133567685137</v>
       </c>
       <c r="R23" t="n">
-        <v>0.926606881659485</v>
+        <v>-1.50055105832838</v>
       </c>
       <c r="S23" t="n">
-        <v>1.23998599815491</v>
+        <v>4.90660775366668</v>
       </c>
       <c r="T23" t="n">
-        <v>0.979931182952119</v>
+        <v>-0.410314827077891</v>
       </c>
       <c r="U23" t="n">
-        <v>1.00725682427798</v>
+        <v>0.148368615432189</v>
       </c>
       <c r="V23" t="n">
-        <v>1.24283259378311</v>
+        <v>4.96480751652057</v>
       </c>
       <c r="W23" t="n">
-        <v>0.891789136629034</v>
+        <v>-2.21241349632496</v>
       </c>
       <c r="X23" t="n">
-        <v>1.0599500045704</v>
+        <v>1.2257013305735</v>
       </c>
     </row>
     <row r="24">
@@ -2236,73 +2236,73 @@
         <v>46</v>
       </c>
       <c r="B24" t="n">
-        <v>0.897509729104336</v>
+        <v>-2.12135432374306</v>
       </c>
       <c r="C24" t="n">
-        <v>1.12059273085692</v>
+        <v>2.49604092934571</v>
       </c>
       <c r="D24" t="n">
-        <v>0.87308025161999</v>
+        <v>-2.62699819837928</v>
       </c>
       <c r="E24" t="n">
-        <v>0.81372945835706</v>
+        <v>-3.85544711168218</v>
       </c>
       <c r="F24" t="n">
-        <v>1.13078804608194</v>
+        <v>2.70706462794174</v>
       </c>
       <c r="G24" t="n">
-        <v>1.02491770220005</v>
+        <v>0.51574920075701</v>
       </c>
       <c r="H24" t="n">
-        <v>0.948858151586462</v>
+        <v>-1.0585393160558</v>
       </c>
       <c r="I24" t="n">
-        <v>0.901190376980874</v>
+        <v>-2.04517188985118</v>
       </c>
       <c r="J24" t="n">
-        <v>1.19336361881904</v>
+        <v>4.00226036336622</v>
       </c>
       <c r="K24" t="n">
-        <v>0.776790374672431</v>
+        <v>-4.62001612105933</v>
       </c>
       <c r="L24" t="n">
-        <v>0.762256051780595</v>
+        <v>-4.92084905319844</v>
       </c>
       <c r="M24" t="n">
-        <v>1.0805019315783</v>
+        <v>1.66623738166458</v>
       </c>
       <c r="N24" t="n">
-        <v>0.967312468772311</v>
+        <v>-0.676569932895721</v>
       </c>
       <c r="O24" t="n">
-        <v>1.3084890557243</v>
+        <v>6.38513867188765</v>
       </c>
       <c r="P24" t="n">
-        <v>1.22839745244647</v>
+        <v>4.72739430821147</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.974354717234938</v>
+        <v>-0.530808739228129</v>
       </c>
       <c r="R24" t="n">
-        <v>0.940532283832772</v>
+        <v>-1.23086899577909</v>
       </c>
       <c r="S24" t="n">
-        <v>1.24135722089429</v>
+        <v>4.99563694813466</v>
       </c>
       <c r="T24" t="n">
-        <v>1.00390930411539</v>
+        <v>0.0809151845880316</v>
       </c>
       <c r="U24" t="n">
-        <v>1.00439650813178</v>
+        <v>0.0909993841680571</v>
       </c>
       <c r="V24" t="n">
-        <v>1.22870456362278</v>
+        <v>4.73375092739142</v>
       </c>
       <c r="W24" t="n">
-        <v>0.897389826741537</v>
+        <v>-2.12383607536229</v>
       </c>
       <c r="X24" t="n">
-        <v>1.06395972783916</v>
+        <v>1.32384512218887</v>
       </c>
     </row>
     <row r="25">
@@ -2310,73 +2310,73 @@
         <v>47</v>
       </c>
       <c r="B25" t="n">
-        <v>0.919480321383403</v>
+        <v>-1.64563812044799</v>
       </c>
       <c r="C25" t="n">
-        <v>1.1284847365409</v>
+        <v>2.62593423098728</v>
       </c>
       <c r="D25" t="n">
-        <v>0.875717449680893</v>
+        <v>-2.54005115302908</v>
       </c>
       <c r="E25" t="n">
-        <v>0.840483723974428</v>
+        <v>-3.26014794357956</v>
       </c>
       <c r="F25" t="n">
-        <v>1.14473070768309</v>
+        <v>2.9579647342708</v>
       </c>
       <c r="G25" t="n">
-        <v>1.03294386898061</v>
+        <v>0.673297354894894</v>
       </c>
       <c r="H25" t="n">
-        <v>0.992110648897932</v>
+        <v>-0.161240297306476</v>
       </c>
       <c r="I25" t="n">
-        <v>0.936648059401751</v>
+        <v>-1.29476880986141</v>
       </c>
       <c r="J25" t="n">
-        <v>1.21311492553761</v>
+        <v>4.35558178480894</v>
       </c>
       <c r="K25" t="n">
-        <v>0.811082720533343</v>
+        <v>-3.86103722770667</v>
       </c>
       <c r="L25" t="n">
-        <v>0.760237772333667</v>
+        <v>-4.90019171052578</v>
       </c>
       <c r="M25" t="n">
-        <v>1.11081715317587</v>
+        <v>2.26484922442488</v>
       </c>
       <c r="N25" t="n">
-        <v>0.959517582334059</v>
+        <v>-0.827368052922623</v>
       </c>
       <c r="O25" t="n">
-        <v>1.33194067325376</v>
+        <v>6.78410836976389</v>
       </c>
       <c r="P25" t="n">
-        <v>1.24463060182394</v>
+        <v>4.99969014663489</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.965565388830969</v>
+        <v>-0.703764716602853</v>
       </c>
       <c r="R25" t="n">
-        <v>0.92693373539403</v>
+        <v>-1.49330738050835</v>
       </c>
       <c r="S25" t="n">
-        <v>1.26066467068339</v>
+        <v>5.32738985177963</v>
       </c>
       <c r="T25" t="n">
-        <v>0.992509581633705</v>
+        <v>-0.153087024358029</v>
       </c>
       <c r="U25" t="n">
-        <v>1.00473937755754</v>
+        <v>0.096862040558167</v>
       </c>
       <c r="V25" t="n">
-        <v>1.25587766784187</v>
+        <v>5.22955445931337</v>
       </c>
       <c r="W25" t="n">
-        <v>0.920962084940216</v>
+        <v>-1.61535426144015</v>
       </c>
       <c r="X25" t="n">
-        <v>1.07823680151675</v>
+        <v>1.59898133238876</v>
       </c>
     </row>
     <row r="26">
@@ -2384,73 +2384,73 @@
         <v>48</v>
       </c>
       <c r="B26" t="n">
-        <v>0.896950431637946</v>
+        <v>-2.09773875999344</v>
       </c>
       <c r="C26" t="n">
-        <v>1.14416439829905</v>
+        <v>2.93469687384358</v>
       </c>
       <c r="D26" t="n">
-        <v>0.890626569204581</v>
+        <v>-2.22647109289103</v>
       </c>
       <c r="E26" t="n">
-        <v>0.807743521046486</v>
+        <v>-3.91368808400713</v>
       </c>
       <c r="F26" t="n">
-        <v>1.12112071054891</v>
+        <v>2.46560575842207</v>
       </c>
       <c r="G26" t="n">
-        <v>1.04203206979606</v>
+        <v>0.855629998023386</v>
       </c>
       <c r="H26" t="n">
-        <v>0.942617894831151</v>
+        <v>-1.1681045156812</v>
       </c>
       <c r="I26" t="n">
-        <v>0.89729821158617</v>
+        <v>-2.09065914298063</v>
       </c>
       <c r="J26" t="n">
-        <v>1.19670602476013</v>
+        <v>4.00426570457616</v>
       </c>
       <c r="K26" t="n">
-        <v>0.764444819348615</v>
+        <v>-4.79510239997881</v>
       </c>
       <c r="L26" t="n">
-        <v>0.732575656945473</v>
+        <v>-5.44385016558531</v>
       </c>
       <c r="M26" t="n">
-        <v>1.10924753479945</v>
+        <v>2.2239082785612</v>
       </c>
       <c r="N26" t="n">
-        <v>0.987227610509154</v>
+        <v>-0.26000241358165</v>
       </c>
       <c r="O26" t="n">
-        <v>1.3322327264989</v>
+        <v>6.76312845160517</v>
       </c>
       <c r="P26" t="n">
-        <v>1.22933343442898</v>
+        <v>4.66844880585877</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.995973201082822</v>
+        <v>-0.0819719315813622</v>
       </c>
       <c r="R26" t="n">
-        <v>0.951428558692744</v>
+        <v>-0.988749362840584</v>
       </c>
       <c r="S26" t="n">
-        <v>1.2540460681728</v>
+        <v>5.17151398594558</v>
       </c>
       <c r="T26" t="n">
-        <v>1.00251269268171</v>
+        <v>0.0511498778126763</v>
       </c>
       <c r="U26" t="n">
-        <v>1.01137509196162</v>
+        <v>0.231558187827998</v>
       </c>
       <c r="V26" t="n">
-        <v>1.25229225003622</v>
+        <v>5.13581221308462</v>
       </c>
       <c r="W26" t="n">
-        <v>0.911736159868248</v>
+        <v>-1.79675161665617</v>
       </c>
       <c r="X26" t="n">
-        <v>1.09158917654063</v>
+        <v>1.86444415710819</v>
       </c>
     </row>
     <row r="27">
@@ -2458,73 +2458,73 @@
         <v>49</v>
       </c>
       <c r="B27" t="n">
-        <v>0.930140376086692</v>
+        <v>-1.43478816894562</v>
       </c>
       <c r="C27" t="n">
-        <v>1.13870242493882</v>
+        <v>2.84869266621361</v>
       </c>
       <c r="D27" t="n">
-        <v>0.932264656790804</v>
+        <v>-1.39115935088096</v>
       </c>
       <c r="E27" t="n">
-        <v>0.860996745516174</v>
+        <v>-2.85487115169453</v>
       </c>
       <c r="F27" t="n">
-        <v>1.15684357383029</v>
+        <v>3.22127849394244</v>
       </c>
       <c r="G27" t="n">
-        <v>1.03954381233073</v>
+        <v>0.812157164738551</v>
       </c>
       <c r="H27" t="n">
-        <v>1.04920274898708</v>
+        <v>1.01053395612141</v>
       </c>
       <c r="I27" t="n">
-        <v>0.938679987117569</v>
+        <v>-1.25940026691935</v>
       </c>
       <c r="J27" t="n">
-        <v>1.18492115267356</v>
+        <v>3.79794031489577</v>
       </c>
       <c r="K27" t="n">
-        <v>0.78660939568071</v>
+        <v>-4.38265048236469</v>
       </c>
       <c r="L27" t="n">
-        <v>0.768864432076311</v>
+        <v>-4.74709939307679</v>
       </c>
       <c r="M27" t="n">
-        <v>1.09608864740182</v>
+        <v>1.97348406331546</v>
       </c>
       <c r="N27" t="n">
-        <v>1.00735389991395</v>
+        <v>0.151035576790992</v>
       </c>
       <c r="O27" t="n">
-        <v>1.32749819094493</v>
+        <v>6.72621041163902</v>
       </c>
       <c r="P27" t="n">
-        <v>1.21983087172611</v>
+        <v>4.51492172807897</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.01180823472991</v>
+        <v>0.242519420196616</v>
       </c>
       <c r="R27" t="n">
-        <v>0.943971125117026</v>
+        <v>-1.15073002541761</v>
       </c>
       <c r="S27" t="n">
-        <v>1.24112755104847</v>
+        <v>4.95231634628476</v>
       </c>
       <c r="T27" t="n">
-        <v>1.04314106319406</v>
+        <v>0.886038080356452</v>
       </c>
       <c r="U27" t="n">
-        <v>1.03463493324519</v>
+        <v>0.711337818166475</v>
       </c>
       <c r="V27" t="n">
-        <v>1.24487804281631</v>
+        <v>5.02934454819583</v>
       </c>
       <c r="W27" t="n">
-        <v>0.963960704705774</v>
+        <v>-0.740180831340596</v>
       </c>
       <c r="X27" t="n">
-        <v>1.09345372796832</v>
+        <v>1.91936766506512</v>
       </c>
     </row>
     <row r="28">
@@ -2532,73 +2532,73 @@
         <v>50</v>
       </c>
       <c r="B28" t="n">
-        <v>0.925633597952039</v>
+        <v>-1.52329655778501</v>
       </c>
       <c r="C28" t="n">
-        <v>1.11549062851224</v>
+        <v>2.36567148637442</v>
       </c>
       <c r="D28" t="n">
-        <v>0.877440779996155</v>
+        <v>-2.51046215515803</v>
       </c>
       <c r="E28" t="n">
-        <v>0.847757717465144</v>
+        <v>-3.11848010053134</v>
       </c>
       <c r="F28" t="n">
-        <v>1.15729548454879</v>
+        <v>3.22198820394415</v>
       </c>
       <c r="G28" t="n">
-        <v>1.02186902890023</v>
+        <v>0.447957888622026</v>
       </c>
       <c r="H28" t="n">
-        <v>1.06119474854849</v>
+        <v>1.25349280389176</v>
       </c>
       <c r="I28" t="n">
-        <v>0.930878504850532</v>
+        <v>-1.41586163550351</v>
       </c>
       <c r="J28" t="n">
-        <v>1.19066359694456</v>
+        <v>3.90548948076372</v>
       </c>
       <c r="K28" t="n">
-        <v>0.762131896626568</v>
+        <v>-4.87241083469269</v>
       </c>
       <c r="L28" t="n">
-        <v>0.744730314567963</v>
+        <v>-5.22885903334012</v>
       </c>
       <c r="M28" t="n">
-        <v>1.08405773364751</v>
+        <v>1.72181055953033</v>
       </c>
       <c r="N28" t="n">
-        <v>0.982489381650583</v>
+        <v>-0.358681661634656</v>
       </c>
       <c r="O28" t="n">
-        <v>1.32160831406664</v>
+        <v>6.58771736000888</v>
       </c>
       <c r="P28" t="n">
-        <v>1.2244554538028</v>
+        <v>4.59767059771645</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.983442911649575</v>
+        <v>-0.339149871401315</v>
       </c>
       <c r="R28" t="n">
-        <v>0.919827297952009</v>
+        <v>-1.64223086897851</v>
       </c>
       <c r="S28" t="n">
-        <v>1.23557833131238</v>
+        <v>4.82550790806643</v>
       </c>
       <c r="T28" t="n">
-        <v>1.00309779713897</v>
+        <v>0.0634542426224806</v>
       </c>
       <c r="U28" t="n">
-        <v>1.0032045945961</v>
+        <v>0.0656418460877767</v>
       </c>
       <c r="V28" t="n">
-        <v>1.23837069014742</v>
+        <v>4.88270565441925</v>
       </c>
       <c r="W28" t="n">
-        <v>0.926453960311881</v>
+        <v>-1.50649252902377</v>
       </c>
       <c r="X28" t="n">
-        <v>1.06669510820086</v>
+        <v>1.36616033511943</v>
       </c>
     </row>
     <row r="29">
@@ -2606,73 +2606,73 @@
         <v>51</v>
       </c>
       <c r="B29" t="n">
-        <v>0.869741214017385</v>
+        <v>-2.69657807373913</v>
       </c>
       <c r="C29" t="n">
-        <v>1.09616367145084</v>
+        <v>1.9907513030191</v>
       </c>
       <c r="D29" t="n">
-        <v>0.869564299160473</v>
+        <v>-2.70024051171189</v>
       </c>
       <c r="E29" t="n">
-        <v>0.808202290922319</v>
+        <v>-3.97053828646383</v>
       </c>
       <c r="F29" t="n">
-        <v>1.17809405144376</v>
+        <v>3.68684930205552</v>
       </c>
       <c r="G29" t="n">
-        <v>1.00035530059871</v>
+        <v>0.00735532576058291</v>
       </c>
       <c r="H29" t="n">
-        <v>0.916598767960567</v>
+        <v>-1.72654713418241</v>
       </c>
       <c r="I29" t="n">
-        <v>0.898318806735917</v>
+        <v>-2.10497337434229</v>
       </c>
       <c r="J29" t="n">
-        <v>1.1685933252535</v>
+        <v>3.49016813589864</v>
       </c>
       <c r="K29" t="n">
-        <v>0.750237904836378</v>
+        <v>-5.17049951286402</v>
       </c>
       <c r="L29" t="n">
-        <v>0.718448674541178</v>
+        <v>-5.82859056406206</v>
       </c>
       <c r="M29" t="n">
-        <v>1.07396837726174</v>
+        <v>1.53127102152399</v>
       </c>
       <c r="N29" t="n">
-        <v>0.939327561432303</v>
+        <v>-1.25602251155459</v>
       </c>
       <c r="O29" t="n">
-        <v>1.29120497449393</v>
+        <v>6.02843749279913</v>
       </c>
       <c r="P29" t="n">
-        <v>1.19873145325789</v>
+        <v>4.11407856579482</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.941788803099751</v>
+        <v>-1.2050706293875</v>
       </c>
       <c r="R29" t="n">
-        <v>0.910116305044257</v>
+        <v>-1.86074512499035</v>
       </c>
       <c r="S29" t="n">
-        <v>1.21384457902827</v>
+        <v>4.42694593416963</v>
       </c>
       <c r="T29" t="n">
-        <v>0.966438612214373</v>
+        <v>-0.694777720706354</v>
       </c>
       <c r="U29" t="n">
-        <v>0.988569389458318</v>
+        <v>-0.236633049537749</v>
       </c>
       <c r="V29" t="n">
-        <v>1.20864352423536</v>
+        <v>4.31927526758778</v>
       </c>
       <c r="W29" t="n">
-        <v>0.927605937269334</v>
+        <v>-1.4986800372488</v>
       </c>
       <c r="X29" t="n">
-        <v>1.03163310996865</v>
+        <v>0.654859095316776</v>
       </c>
     </row>
     <row r="30">
@@ -2680,73 +2680,73 @@
         <v>52</v>
       </c>
       <c r="B30" t="n">
-        <v>0.893507133328111</v>
+        <v>-2.20346184171732</v>
       </c>
       <c r="C30" t="n">
-        <v>1.10166947715182</v>
+        <v>2.10366027671719</v>
       </c>
       <c r="D30" t="n">
-        <v>0.841138353996554</v>
+        <v>-3.2870330757412</v>
       </c>
       <c r="E30" t="n">
-        <v>0.805956961961857</v>
+        <v>-4.01497718420245</v>
       </c>
       <c r="F30" t="n">
-        <v>1.12184891547425</v>
+        <v>2.52119643402396</v>
       </c>
       <c r="G30" t="n">
-        <v>1.00611043429677</v>
+        <v>0.126432025261681</v>
       </c>
       <c r="H30" t="n">
-        <v>0.962175545924359</v>
+        <v>-0.782632150341624</v>
       </c>
       <c r="I30" t="n">
-        <v>0.892848285801872</v>
+        <v>-2.21709416685746</v>
       </c>
       <c r="J30" t="n">
-        <v>1.1724944721675</v>
+        <v>3.56911217818307</v>
       </c>
       <c r="K30" t="n">
-        <v>0.689312553098873</v>
+        <v>-6.42848629529773</v>
       </c>
       <c r="L30" t="n">
-        <v>0.732117060356331</v>
+        <v>-5.54281102574264</v>
       </c>
       <c r="M30" t="n">
-        <v>1.09154307446184</v>
+        <v>1.89413317299123</v>
       </c>
       <c r="N30" t="n">
-        <v>0.941552487251032</v>
+        <v>-1.20934733105118</v>
       </c>
       <c r="O30" t="n">
-        <v>1.30404507895904</v>
+        <v>6.29104794138307</v>
       </c>
       <c r="P30" t="n">
-        <v>1.20841714911732</v>
+        <v>4.31239433768327</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.942696859808355</v>
+        <v>-1.18566892571216</v>
       </c>
       <c r="R30" t="n">
-        <v>0.912274930519834</v>
+        <v>-1.81513418881954</v>
       </c>
       <c r="S30" t="n">
-        <v>1.21788082562848</v>
+        <v>4.50820886241533</v>
       </c>
       <c r="T30" t="n">
-        <v>0.970691668698255</v>
+        <v>-0.60642361959115</v>
       </c>
       <c r="U30" t="n">
-        <v>0.991073248711969</v>
+        <v>-0.184704914501751</v>
       </c>
       <c r="V30" t="n">
-        <v>1.20539945525556</v>
+        <v>4.24995472569641</v>
       </c>
       <c r="W30" t="n">
-        <v>0.88882379814007</v>
+        <v>-2.30036551894309</v>
       </c>
       <c r="X30" t="n">
-        <v>1.03308528196388</v>
+        <v>0.684573141922202</v>
       </c>
     </row>
     <row r="31">
@@ -2754,73 +2754,73 @@
         <v>53</v>
       </c>
       <c r="B31" t="n">
-        <v>0.882921854695913</v>
+        <v>-2.44039238504849</v>
       </c>
       <c r="C31" t="n">
-        <v>1.09628772256167</v>
+        <v>2.00703405663661</v>
       </c>
       <c r="D31" t="n">
-        <v>0.892668662808679</v>
+        <v>-2.23722862433857</v>
       </c>
       <c r="E31" t="n">
-        <v>0.812017929399316</v>
+        <v>-3.91832320565078</v>
       </c>
       <c r="F31" t="n">
-        <v>1.1779524067492</v>
+        <v>3.70926356241689</v>
       </c>
       <c r="G31" t="n">
-        <v>1.00432675479597</v>
+        <v>0.090187450686217</v>
       </c>
       <c r="H31" t="n">
-        <v>0.904197831202331</v>
+        <v>-1.99691310959639</v>
       </c>
       <c r="I31" t="n">
-        <v>0.889612723009804</v>
+        <v>-2.30092703871786</v>
       </c>
       <c r="J31" t="n">
-        <v>1.15828806233262</v>
+        <v>3.29937735994454</v>
       </c>
       <c r="K31" t="n">
-        <v>0.723944172699843</v>
+        <v>-5.75414426870024</v>
       </c>
       <c r="L31" t="n">
-        <v>0.738511185583793</v>
+        <v>-5.45050752059013</v>
       </c>
       <c r="M31" t="n">
-        <v>1.07761933903102</v>
+        <v>1.61790779493325</v>
       </c>
       <c r="N31" t="n">
-        <v>0.937968028097508</v>
+        <v>-1.29300264765211</v>
       </c>
       <c r="O31" t="n">
-        <v>1.28512909433704</v>
+        <v>5.94326864991427</v>
       </c>
       <c r="P31" t="n">
-        <v>1.18908895263028</v>
+        <v>3.94139520144613</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.942419876613071</v>
+        <v>-1.20020772688743</v>
       </c>
       <c r="R31" t="n">
-        <v>0.909428649522979</v>
+        <v>-1.88788123892466</v>
       </c>
       <c r="S31" t="n">
-        <v>1.21477335706714</v>
+        <v>4.47676433322903</v>
       </c>
       <c r="T31" t="n">
-        <v>0.973429221597529</v>
+        <v>-0.553844828253681</v>
       </c>
       <c r="U31" t="n">
-        <v>0.992363387385076</v>
+        <v>-0.159178565945175</v>
       </c>
       <c r="V31" t="n">
-        <v>1.20808230767281</v>
+        <v>4.33729521243385</v>
       </c>
       <c r="W31" t="n">
-        <v>0.927498825432719</v>
+        <v>-1.5112240961925</v>
       </c>
       <c r="X31" t="n">
-        <v>1.02128939537728</v>
+        <v>0.443758980175629</v>
       </c>
     </row>
     <row r="32">
@@ -2828,73 +2828,73 @@
         <v>54</v>
       </c>
       <c r="B32" t="n">
-        <v>0.904863264703898</v>
+        <v>-1.95411730343769</v>
       </c>
       <c r="C32" t="n">
-        <v>1.12888482664107</v>
+        <v>2.6473062072816</v>
       </c>
       <c r="D32" t="n">
-        <v>0.906722323846201</v>
+        <v>-1.91593205746744</v>
       </c>
       <c r="E32" t="n">
-        <v>0.807800489088317</v>
+        <v>-3.94779565239266</v>
       </c>
       <c r="F32" t="n">
-        <v>1.12427711004599</v>
+        <v>2.55266328412725</v>
       </c>
       <c r="G32" t="n">
-        <v>1.03405725117808</v>
+        <v>0.69953907528433</v>
       </c>
       <c r="H32" t="n">
-        <v>0.945870149689447</v>
+        <v>-1.11183210980625</v>
       </c>
       <c r="I32" t="n">
-        <v>0.903121470032168</v>
+        <v>-1.98989392638434</v>
       </c>
       <c r="J32" t="n">
-        <v>1.18875416832427</v>
+        <v>3.87702799839041</v>
       </c>
       <c r="K32" t="n">
-        <v>0.751602257968208</v>
+        <v>-5.10211249448946</v>
       </c>
       <c r="L32" t="n">
-        <v>0.756853437345076</v>
+        <v>-4.99425278654535</v>
       </c>
       <c r="M32" t="n">
-        <v>1.09515120011555</v>
+        <v>1.95441441216103</v>
       </c>
       <c r="N32" t="n">
-        <v>0.989088495778849</v>
+        <v>-0.224123301464161</v>
       </c>
       <c r="O32" t="n">
-        <v>1.32718067133231</v>
+        <v>6.72032111687391</v>
       </c>
       <c r="P32" t="n">
-        <v>1.22102697338823</v>
+        <v>4.5399143861741</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.999231097319552</v>
+        <v>-0.0157933318591103</v>
       </c>
       <c r="R32" t="n">
-        <v>0.94636470905099</v>
+        <v>-1.10167381497975</v>
       </c>
       <c r="S32" t="n">
-        <v>1.24182640760339</v>
+        <v>4.96713668022338</v>
       </c>
       <c r="T32" t="n">
-        <v>1.02498034987776</v>
+        <v>0.513098686749359</v>
       </c>
       <c r="U32" t="n">
-        <v>1.01726390031024</v>
+        <v>0.35460210208031</v>
       </c>
       <c r="V32" t="n">
-        <v>1.24856605581254</v>
+        <v>5.1055696750449</v>
       </c>
       <c r="W32" t="n">
-        <v>0.967311576321163</v>
+        <v>-0.671423232404481</v>
       </c>
       <c r="X32" t="n">
-        <v>1.08010861016398</v>
+        <v>1.64543822939217</v>
       </c>
     </row>
     <row r="33">
@@ -2902,73 +2902,73 @@
         <v>55</v>
       </c>
       <c r="B33" t="n">
-        <v>0.882552034400464</v>
+        <v>-2.41482360787326</v>
       </c>
       <c r="C33" t="n">
-        <v>1.11776162195776</v>
+        <v>2.42127263212618</v>
       </c>
       <c r="D33" t="n">
-        <v>0.896184027662676</v>
+        <v>-2.13453898153752</v>
       </c>
       <c r="E33" t="n">
-        <v>0.810897016137351</v>
+        <v>-3.88810778815743</v>
       </c>
       <c r="F33" t="n">
-        <v>1.10559546142314</v>
+        <v>2.17112669280557</v>
       </c>
       <c r="G33" t="n">
-        <v>1.02796493766728</v>
+        <v>0.574981365806831</v>
       </c>
       <c r="H33" t="n">
-        <v>0.961656648462125</v>
+        <v>-0.788369811481954</v>
       </c>
       <c r="I33" t="n">
-        <v>0.884803502577823</v>
+        <v>-2.36853163100241</v>
       </c>
       <c r="J33" t="n">
-        <v>1.17598077474573</v>
+        <v>3.61830472940526</v>
       </c>
       <c r="K33" t="n">
-        <v>0.757884130169174</v>
+        <v>-4.97809489780177</v>
       </c>
       <c r="L33" t="n">
-        <v>0.739740041147252</v>
+        <v>-5.35115180253258</v>
       </c>
       <c r="M33" t="n">
-        <v>1.08583782280599</v>
+        <v>1.76489392474566</v>
       </c>
       <c r="N33" t="n">
-        <v>0.971008101014488</v>
+        <v>-0.596096507503637</v>
       </c>
       <c r="O33" t="n">
-        <v>1.32046227876549</v>
+        <v>6.58895939359571</v>
       </c>
       <c r="P33" t="n">
-        <v>1.2093203804899</v>
+        <v>4.30379354666346</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.987004755937673</v>
+        <v>-0.267192556223433</v>
       </c>
       <c r="R33" t="n">
-        <v>0.931304305320717</v>
+        <v>-1.41243813312542</v>
       </c>
       <c r="S33" t="n">
-        <v>1.23080031415863</v>
+        <v>4.74543807114714</v>
       </c>
       <c r="T33" t="n">
-        <v>1.02626090327448</v>
+        <v>0.539945063054691</v>
       </c>
       <c r="U33" t="n">
-        <v>1.00300175048596</v>
+        <v>0.0617183780190178</v>
       </c>
       <c r="V33" t="n">
-        <v>1.23039399722724</v>
+        <v>4.73708387179434</v>
       </c>
       <c r="W33" t="n">
-        <v>0.940314171691702</v>
+        <v>-1.22718811278343</v>
       </c>
       <c r="X33" t="n">
-        <v>1.0664369554966</v>
+        <v>1.36599665860072</v>
       </c>
     </row>
     <row r="34">
@@ -2976,73 +2976,73 @@
         <v>56</v>
       </c>
       <c r="B34" t="n">
-        <v>0.910885952519152</v>
+        <v>-1.83326059805223</v>
       </c>
       <c r="C34" t="n">
-        <v>1.11873715438078</v>
+        <v>2.44266928508559</v>
       </c>
       <c r="D34" t="n">
-        <v>0.886500362782993</v>
+        <v>-2.33492270506377</v>
       </c>
       <c r="E34" t="n">
-        <v>0.834132407976748</v>
+        <v>-3.41224004010571</v>
       </c>
       <c r="F34" t="n">
-        <v>1.13516168903117</v>
+        <v>2.78055599393906</v>
       </c>
       <c r="G34" t="n">
-        <v>1.02832615036949</v>
+        <v>0.582727603950996</v>
       </c>
       <c r="H34" t="n">
-        <v>0.968275236241991</v>
+        <v>-0.652644123167821</v>
       </c>
       <c r="I34" t="n">
-        <v>0.914744767579514</v>
+        <v>-1.75387677692288</v>
       </c>
       <c r="J34" t="n">
-        <v>1.19169553488669</v>
+        <v>3.94357433945348</v>
       </c>
       <c r="K34" t="n">
-        <v>0.720366461543241</v>
+        <v>-5.75264127753682</v>
       </c>
       <c r="L34" t="n">
-        <v>0.770482966854185</v>
+        <v>-4.72164092354239</v>
       </c>
       <c r="M34" t="n">
-        <v>1.08438525485607</v>
+        <v>1.73597953585791</v>
       </c>
       <c r="N34" t="n">
-        <v>0.976220607373817</v>
+        <v>-0.48919137643888</v>
       </c>
       <c r="O34" t="n">
-        <v>1.3157445636796</v>
+        <v>6.49551988722553</v>
       </c>
       <c r="P34" t="n">
-        <v>1.22261740155716</v>
+        <v>4.57970120595427</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.975515456908816</v>
+        <v>-0.503697782552476</v>
       </c>
       <c r="R34" t="n">
-        <v>0.91593206852127</v>
+        <v>-1.72945153650252</v>
       </c>
       <c r="S34" t="n">
-        <v>1.23064142561673</v>
+        <v>4.74477200637328</v>
       </c>
       <c r="T34" t="n">
-        <v>0.99325183384644</v>
+        <v>-0.138823759756733</v>
       </c>
       <c r="U34" t="n">
-        <v>1.01208196720388</v>
+        <v>0.248551098821943</v>
       </c>
       <c r="V34" t="n">
-        <v>1.24951814727509</v>
+        <v>5.13310528283137</v>
       </c>
       <c r="W34" t="n">
-        <v>0.909784699162487</v>
+        <v>-1.85591566135952</v>
       </c>
       <c r="X34" t="n">
-        <v>1.05887632867522</v>
+        <v>1.21120807066299</v>
       </c>
     </row>
     <row r="35">
@@ -3050,73 +3050,73 @@
         <v>57</v>
       </c>
       <c r="B35" t="n">
-        <v>0.894736540101924</v>
+        <v>-2.16139492008286</v>
       </c>
       <c r="C35" t="n">
-        <v>1.1313654885487</v>
+        <v>2.69735290763087</v>
       </c>
       <c r="D35" t="n">
-        <v>0.920923678127268</v>
+        <v>-1.62368936533203</v>
       </c>
       <c r="E35" t="n">
-        <v>0.825096301437973</v>
+        <v>-3.59133136932522</v>
       </c>
       <c r="F35" t="n">
-        <v>1.13137454000064</v>
+        <v>2.69753876283891</v>
       </c>
       <c r="G35" t="n">
-        <v>1.03889019294258</v>
+        <v>0.798539830901595</v>
       </c>
       <c r="H35" t="n">
-        <v>0.923957022113425</v>
+        <v>-1.56140512834331</v>
       </c>
       <c r="I35" t="n">
-        <v>0.899488922328413</v>
+        <v>-2.06381333942258</v>
       </c>
       <c r="J35" t="n">
-        <v>1.19615593809909</v>
+        <v>4.02770770181772</v>
       </c>
       <c r="K35" t="n">
-        <v>0.768788491465174</v>
+        <v>-4.74751048935454</v>
       </c>
       <c r="L35" t="n">
-        <v>0.738899144638162</v>
+        <v>-5.36123421132845</v>
       </c>
       <c r="M35" t="n">
-        <v>1.1100861430732</v>
+        <v>2.26042000367761</v>
       </c>
       <c r="N35" t="n">
-        <v>0.973240662647589</v>
+        <v>-0.549454633870933</v>
       </c>
       <c r="O35" t="n">
-        <v>1.31740970617013</v>
+        <v>6.51743470303358</v>
       </c>
       <c r="P35" t="n">
-        <v>1.23405753409001</v>
+        <v>4.80594848087939</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.98676567678231</v>
+        <v>-0.271742910608737</v>
       </c>
       <c r="R35" t="n">
-        <v>0.948466167803379</v>
+        <v>-1.05815411378299</v>
       </c>
       <c r="S35" t="n">
-        <v>1.23903483385715</v>
+        <v>4.90814833677279</v>
       </c>
       <c r="T35" t="n">
-        <v>1.01664649889791</v>
+        <v>0.341805771821884</v>
       </c>
       <c r="U35" t="n">
-        <v>1.02546068924591</v>
+        <v>0.522789241881401</v>
       </c>
       <c r="V35" t="n">
-        <v>1.25520861087885</v>
+        <v>5.24024761915532</v>
       </c>
       <c r="W35" t="n">
-        <v>0.914221481302703</v>
+        <v>-1.76130686511814</v>
       </c>
       <c r="X35" t="n">
-        <v>1.07109389056463</v>
+        <v>1.4597845640274</v>
       </c>
     </row>
     <row r="36">
@@ -3124,73 +3124,73 @@
         <v>58</v>
       </c>
       <c r="B36" t="n">
-        <v>0.880770689186182</v>
+        <v>-2.43074742878694</v>
       </c>
       <c r="C36" t="n">
-        <v>1.12038633120426</v>
+        <v>2.45433579241933</v>
       </c>
       <c r="D36" t="n">
-        <v>0.870731570652711</v>
+        <v>-2.63541657763932</v>
       </c>
       <c r="E36" t="n">
-        <v>0.821676288108302</v>
+        <v>-3.63551463322098</v>
       </c>
       <c r="F36" t="n">
-        <v>1.11622101695918</v>
+        <v>2.36941685074127</v>
       </c>
       <c r="G36" t="n">
-        <v>1.01029176430123</v>
+        <v>0.209819879374856</v>
       </c>
       <c r="H36" t="n">
-        <v>0.948508282528334</v>
+        <v>-1.04977005229464</v>
       </c>
       <c r="I36" t="n">
-        <v>0.897126345309502</v>
+        <v>-2.09730199664847</v>
       </c>
       <c r="J36" t="n">
-        <v>1.18534742583973</v>
+        <v>3.77870823639774</v>
       </c>
       <c r="K36" t="n">
-        <v>0.707557227871296</v>
+        <v>-5.96207854903399</v>
       </c>
       <c r="L36" t="n">
-        <v>0.725896868532868</v>
+        <v>-5.58818530014484</v>
       </c>
       <c r="M36" t="n">
-        <v>1.08369893575008</v>
+        <v>1.70638387052662</v>
       </c>
       <c r="N36" t="n">
-        <v>0.964050411802034</v>
+        <v>-0.73291012488205</v>
       </c>
       <c r="O36" t="n">
-        <v>1.31644684972604</v>
+        <v>6.45145359869146</v>
       </c>
       <c r="P36" t="n">
-        <v>1.21957144929887</v>
+        <v>4.47643899117787</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.957971554290086</v>
+        <v>-0.856840785608602</v>
       </c>
       <c r="R36" t="n">
-        <v>0.916985609304557</v>
+        <v>-1.69242793871686</v>
       </c>
       <c r="S36" t="n">
-        <v>1.23826890845739</v>
+        <v>4.85762714419332</v>
       </c>
       <c r="T36" t="n">
-        <v>0.985731983701934</v>
+        <v>-0.290884378125528</v>
       </c>
       <c r="U36" t="n">
-        <v>0.999332324127508</v>
+        <v>-0.0136120170387996</v>
       </c>
       <c r="V36" t="n">
-        <v>1.24937962765171</v>
+        <v>5.08414319070262</v>
       </c>
       <c r="W36" t="n">
-        <v>0.883559855369157</v>
+        <v>-2.37388424236532</v>
       </c>
       <c r="X36" t="n">
-        <v>1.05374087474452</v>
+        <v>1.09562398888631</v>
       </c>
     </row>
     <row r="37">
@@ -3198,73 +3198,73 @@
         <v>59</v>
       </c>
       <c r="B37" t="n">
-        <v>0.933964957688173</v>
+        <v>-1.33455905631518</v>
       </c>
       <c r="C37" t="n">
-        <v>1.12899637012174</v>
+        <v>2.60699876839358</v>
       </c>
       <c r="D37" t="n">
-        <v>0.897901467779317</v>
+        <v>-2.06339719096682</v>
       </c>
       <c r="E37" t="n">
-        <v>0.831393114179128</v>
+        <v>-3.40752180284501</v>
       </c>
       <c r="F37" t="n">
-        <v>1.16644621523921</v>
+        <v>3.36385494973905</v>
       </c>
       <c r="G37" t="n">
-        <v>1.04229001884297</v>
+        <v>0.854675421757357</v>
       </c>
       <c r="H37" t="n">
-        <v>1.00398462377916</v>
+        <v>0.080528694528167</v>
       </c>
       <c r="I37" t="n">
-        <v>0.93486495139503</v>
+        <v>-1.31637030818897</v>
       </c>
       <c r="J37" t="n">
-        <v>1.23245362100016</v>
+        <v>4.69785547518991</v>
       </c>
       <c r="K37" t="n">
-        <v>0.83743308350818</v>
+        <v>-3.28545485951075</v>
       </c>
       <c r="L37" t="n">
-        <v>0.753342312421798</v>
+        <v>-4.9849176928337</v>
       </c>
       <c r="M37" t="n">
-        <v>1.12144710338996</v>
+        <v>2.45442913365537</v>
       </c>
       <c r="N37" t="n">
-        <v>0.975445899360744</v>
+        <v>-0.496234972078225</v>
       </c>
       <c r="O37" t="n">
-        <v>1.34965013738153</v>
+        <v>7.06638083429811</v>
       </c>
       <c r="P37" t="n">
-        <v>1.26396953090368</v>
+        <v>5.334787647977</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.965011287039643</v>
+        <v>-0.707117041427164</v>
       </c>
       <c r="R37" t="n">
-        <v>0.93764937830223</v>
+        <v>-1.26009742616212</v>
       </c>
       <c r="S37" t="n">
-        <v>1.2643577999448</v>
+        <v>5.34263451150551</v>
       </c>
       <c r="T37" t="n">
-        <v>1.00564158955195</v>
+        <v>0.11401574323248</v>
       </c>
       <c r="U37" t="n">
-        <v>1.02670556938151</v>
+        <v>0.539715857284511</v>
       </c>
       <c r="V37" t="n">
-        <v>1.261596602919</v>
+        <v>5.28683110216338</v>
       </c>
       <c r="W37" t="n">
-        <v>0.911570911145118</v>
+        <v>-1.78713963437327</v>
       </c>
       <c r="X37" t="n">
-        <v>1.08138990670592</v>
+        <v>1.64487873838425</v>
       </c>
     </row>
     <row r="38">
@@ -3272,73 +3272,73 @@
         <v>60</v>
       </c>
       <c r="B38" t="n">
-        <v>0.90934824513505</v>
+        <v>-1.85186799622893</v>
       </c>
       <c r="C38" t="n">
-        <v>1.13455791958451</v>
+        <v>2.74879957138096</v>
       </c>
       <c r="D38" t="n">
-        <v>0.907878403918408</v>
+        <v>-1.88189446303803</v>
       </c>
       <c r="E38" t="n">
-        <v>0.847730546337851</v>
+        <v>-3.11061742224722</v>
       </c>
       <c r="F38" t="n">
-        <v>1.15359571004968</v>
+        <v>3.13771068439662</v>
       </c>
       <c r="G38" t="n">
-        <v>1.04256518608767</v>
+        <v>0.869537561481435</v>
       </c>
       <c r="H38" t="n">
-        <v>0.937426485389256</v>
+        <v>-1.2782751893974</v>
       </c>
       <c r="I38" t="n">
-        <v>0.905999283225453</v>
+        <v>-1.92028184425882</v>
       </c>
       <c r="J38" t="n">
-        <v>1.1901670927726</v>
+        <v>3.88480458614531</v>
       </c>
       <c r="K38" t="n">
-        <v>0.795066132195845</v>
+        <v>-4.18646579644606</v>
       </c>
       <c r="L38" t="n">
-        <v>0.722707090040317</v>
+        <v>-5.66464340707511</v>
       </c>
       <c r="M38" t="n">
-        <v>1.09980479314323</v>
+        <v>2.03884968986586</v>
       </c>
       <c r="N38" t="n">
-        <v>0.996802178359004</v>
+        <v>-0.0653262980229282</v>
       </c>
       <c r="O38" t="n">
-        <v>1.33691950634015</v>
+        <v>6.8827178472836</v>
       </c>
       <c r="P38" t="n">
-        <v>1.22408260373101</v>
+        <v>4.57764334490061</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.995196684969636</v>
+        <v>-0.0981239182163469</v>
       </c>
       <c r="R38" t="n">
-        <v>0.974283448677086</v>
+        <v>-0.525347340922766</v>
       </c>
       <c r="S38" t="n">
-        <v>1.23964359455111</v>
+        <v>4.8955290927529</v>
       </c>
       <c r="T38" t="n">
-        <v>1.03052622236609</v>
+        <v>0.623601102149069</v>
       </c>
       <c r="U38" t="n">
-        <v>1.03096768903987</v>
+        <v>0.632619548684292</v>
       </c>
       <c r="V38" t="n">
-        <v>1.25625746167559</v>
+        <v>5.23492339203864</v>
       </c>
       <c r="W38" t="n">
-        <v>0.926142315742544</v>
+        <v>-1.50879243270831</v>
       </c>
       <c r="X38" t="n">
-        <v>1.10251780792742</v>
+        <v>2.09427217186439</v>
       </c>
     </row>
     <row r="39">
@@ -3346,73 +3346,73 @@
         <v>61</v>
       </c>
       <c r="B39" t="n">
-        <v>0.877274732302003</v>
+        <v>-2.5240360656132</v>
       </c>
       <c r="C39" t="n">
-        <v>1.1146567721825</v>
+        <v>2.35809490240892</v>
       </c>
       <c r="D39" t="n">
-        <v>0.875511171851941</v>
+        <v>-2.56030643000793</v>
       </c>
       <c r="E39" t="n">
-        <v>0.827609529607344</v>
+        <v>-3.54547822792153</v>
       </c>
       <c r="F39" t="n">
-        <v>1.15036207976397</v>
+        <v>3.09243010297436</v>
       </c>
       <c r="G39" t="n">
-        <v>1.01265371126386</v>
+        <v>0.260243258726843</v>
       </c>
       <c r="H39" t="n">
-        <v>0.991097638906691</v>
+        <v>-0.183090906136122</v>
       </c>
       <c r="I39" t="n">
-        <v>0.893014085529895</v>
+        <v>-2.20033177926865</v>
       </c>
       <c r="J39" t="n">
-        <v>1.18912625377782</v>
+        <v>3.88967565069187</v>
       </c>
       <c r="K39" t="n">
-        <v>0.75503276974308</v>
+        <v>-5.03813220911747</v>
       </c>
       <c r="L39" t="n">
-        <v>0.712565957640672</v>
+        <v>-5.91152826967334</v>
       </c>
       <c r="M39" t="n">
-        <v>1.09144633123246</v>
+        <v>1.88073607357475</v>
       </c>
       <c r="N39" t="n">
-        <v>0.971120504279866</v>
+        <v>-0.593951760070443</v>
       </c>
       <c r="O39" t="n">
-        <v>1.30984036374531</v>
+        <v>6.37234912862723</v>
       </c>
       <c r="P39" t="n">
-        <v>1.21829614323568</v>
+        <v>4.48959980977176</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.962619573433749</v>
+        <v>-0.768786628629731</v>
       </c>
       <c r="R39" t="n">
-        <v>0.927815646931405</v>
+        <v>-1.48458352493832</v>
       </c>
       <c r="S39" t="n">
-        <v>1.22483136756394</v>
+        <v>4.62400686555432</v>
       </c>
       <c r="T39" t="n">
-        <v>0.990911540451944</v>
+        <v>-0.186918310389096</v>
       </c>
       <c r="U39" t="n">
-        <v>1.00644347642469</v>
+        <v>0.132520117404623</v>
       </c>
       <c r="V39" t="n">
-        <v>1.23912649241907</v>
+        <v>4.91800834848916</v>
       </c>
       <c r="W39" t="n">
-        <v>0.909221538860375</v>
+        <v>-1.8670002860464</v>
       </c>
       <c r="X39" t="n">
-        <v>1.0547630954977</v>
+        <v>1.12628825908098</v>
       </c>
     </row>
     <row r="40">
@@ -3420,73 +3420,73 @@
         <v>62</v>
       </c>
       <c r="B40" t="n">
-        <v>0.88783869602889</v>
+        <v>-2.30933596978497</v>
       </c>
       <c r="C40" t="n">
-        <v>1.10291135980777</v>
+        <v>2.11888500302019</v>
       </c>
       <c r="D40" t="n">
-        <v>0.899711956391822</v>
+        <v>-2.06487244926632</v>
       </c>
       <c r="E40" t="n">
-        <v>0.796311209357752</v>
+        <v>-4.19383365044779</v>
       </c>
       <c r="F40" t="n">
-        <v>1.12078945141582</v>
+        <v>2.48698450400509</v>
       </c>
       <c r="G40" t="n">
-        <v>1.02867908333372</v>
+        <v>0.590485634333196</v>
       </c>
       <c r="H40" t="n">
-        <v>0.976024023173542</v>
+        <v>-0.493651408602843</v>
       </c>
       <c r="I40" t="n">
-        <v>0.872374961708235</v>
+        <v>-2.62772525940205</v>
       </c>
       <c r="J40" t="n">
-        <v>1.17533914165271</v>
+        <v>3.61013087752728</v>
       </c>
       <c r="K40" t="n">
-        <v>0.78427671736712</v>
+        <v>-4.44161683634239</v>
       </c>
       <c r="L40" t="n">
-        <v>0.732089891294733</v>
+        <v>-5.51611321192767</v>
       </c>
       <c r="M40" t="n">
-        <v>1.0761019290913</v>
+        <v>1.56689442791986</v>
       </c>
       <c r="N40" t="n">
-        <v>0.998714415615244</v>
+        <v>-0.0264694342593851</v>
       </c>
       <c r="O40" t="n">
-        <v>1.32321208133491</v>
+        <v>6.65474864208093</v>
       </c>
       <c r="P40" t="n">
-        <v>1.19896987847222</v>
+        <v>4.09667399532019</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.992902300822053</v>
+        <v>-0.146137495143312</v>
       </c>
       <c r="R40" t="n">
-        <v>0.954984895945134</v>
+        <v>-0.926834793257148</v>
       </c>
       <c r="S40" t="n">
-        <v>1.24288110173815</v>
+        <v>5.00078052560255</v>
       </c>
       <c r="T40" t="n">
-        <v>1.02557419729334</v>
+        <v>0.526557837835886</v>
       </c>
       <c r="U40" t="n">
-        <v>1.00565904239768</v>
+        <v>0.116516389349978</v>
       </c>
       <c r="V40" t="n">
-        <v>1.23884356441888</v>
+        <v>4.91764998208522</v>
       </c>
       <c r="W40" t="n">
-        <v>0.946453814645807</v>
+        <v>-1.10248479203721</v>
       </c>
       <c r="X40" t="n">
-        <v>1.09677113525229</v>
+        <v>1.99246135309379</v>
       </c>
     </row>
   </sheetData>
